--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_5.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_5.xlsx
@@ -625,158 +625,158 @@
         <v>29</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.360121162921047</v>
+        <v>-5.32712751409975</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.156229367772056</v>
+        <v>1.189683235716295</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2742769776373208</v>
+        <v>-0.2391530182193975</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.72662855624225</v>
+        <v>12.76269120853269</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>19.22386408309391</v>
+        <v>19.28928726145367</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>22.84510565986547</v>
+        <v>22.91036894284997</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.08298808500914</v>
+        <v>22.14917119404611</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>25.24445797401312</v>
+        <v>25.31101235852924</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>28.72638439818539</v>
+        <v>28.79293953283306</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>24.53070119129266</v>
+        <v>24.59816074162357</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.94168620335162</v>
+        <v>18.0088282452509</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>17.66888656031612</v>
+        <v>17.7363849885752</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.242465356312614</v>
+        <v>6.311258038602482</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>16.33732853040365</v>
+        <v>16.40645382094685</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>15.68515836162806</v>
+        <v>15.75508243260324</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>16.28349480405753</v>
+        <v>16.35276494196559</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>9.272649326327553</v>
+        <v>9.342093003316322</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>5.728616934656159</v>
+        <v>5.798213275825674</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.9401135441914406</v>
+        <v>-0.8707412144203772</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.7535478736591656</v>
+        <v>-0.6843514226676319</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.296518016285958</v>
+        <v>-1.226646888088247</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.07344092222975</v>
+        <v>2.143445338817919</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.348797776028277</v>
+        <v>2.418522621808819</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.273643879815253</v>
+        <v>2.343498227522531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01934</t>
+          <t>X ≈ -0.01933</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-15.10569792589321</v>
+        <v>-16.48738365925391</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.44379161893314</v>
+        <v>-13.14636290621302</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.235623365632435</v>
+        <v>-7.21888598054533</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-9.948513376219985</v>
+        <v>-7.930333118580201</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-14.13973456430212</v>
+        <v>-11.9500237106215</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-6.30786614701853</v>
+        <v>-4.400999088755931</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.400546847022746</v>
+        <v>5.883798536746099</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2973948932637427</v>
+        <v>1.923178503505817</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.318391974516643</v>
+        <v>-5.408568342200823</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.090872570414476</v>
+        <v>-6.179556838486853</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.988771572017761</v>
+        <v>-2.219049419974638</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-15.76464756883126</v>
+        <v>-13.56828479202913</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-13.05677267113495</v>
+        <v>-11.00038369039635</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-17.11622411382458</v>
+        <v>-14.91692297906503</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-13.94275470262502</v>
+        <v>-11.88405099771138</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-17.19017152456522</v>
+        <v>-14.98941348547821</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-13.49093229573694</v>
+        <v>-11.43146748152734</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-13.5997145329627</v>
+        <v>-11.53947921140099</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-21.06866279948598</v>
+        <v>-18.723571860304</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-13.20524439170185</v>
+        <v>-11.14417975432195</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-13.75199080386785</v>
+        <v>-11.68964349059275</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-13.83203527792103</v>
+        <v>-11.7689488959657</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-21.25147128523854</v>
+        <v>-18.90324297876744</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-21.33378317588843</v>
+        <v>-18.98472654897888</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.8674041880829435</v>
+        <v>3.479830440981722</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-13.0110844298214</v>
+        <v>-15.77291258330426</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.136172071410392</v>
+        <v>6.450705412696152</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.910762828495358</v>
+        <v>1.010447960658873</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.490700422127219</v>
+        <v>-8.792752654494862</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.78682071477818</v>
+        <v>-3.874463261530515</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.96530391331757</v>
+        <v>0.09330234099367374</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.212461640854578</v>
+        <v>4.555658342188586</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.731467170232641</v>
+        <v>-0.1413552429332228</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.01390485286917</v>
+        <v>8.572532527635488</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.29033372233154</v>
+        <v>8.848226063807921</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.01568006257948</v>
+        <v>8.573475912144261</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.42816852814349</v>
+        <v>12.20259110589469</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.21133639212517</v>
+        <v>11.98566219645464</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3.492313022919419</v>
+        <v>1.835305276876355</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>8.621392812112511</v>
+        <v>7.17914902815636</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>8.49038760777114</v>
+        <v>7.047881005673815</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>12.92538854171768</v>
+        <v>11.69864982624973</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>17.68372103235063</v>
+        <v>16.67250506671098</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>17.87583902762125</v>
+        <v>16.86411514618766</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>21.87982665712544</v>
+        <v>21.08470224548898</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>17.26794012140385</v>
+        <v>16.25635684216484</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>22.09200667174409</v>
+        <v>21.29619797295052</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>22.02286018075285</v>
+        <v>21.2269136626624</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>35</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.227537153717861</v>
+        <v>-2.194533005756441</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.398959144151064</v>
+        <v>-5.365574159082385</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-18.18730506170493</v>
+        <v>-18.15233563572219</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-18.90269422964717</v>
+        <v>-18.86687723372596</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.069818306096586</v>
+        <v>-5.004582259262961</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.637684628010291</v>
+        <v>3.702808392472733</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.869433393163831</v>
+        <v>2.935485511423977</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-8.778861548329076</v>
+        <v>-8.712519461958834</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.739598559619331</v>
+        <v>-8.673261892775493</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.667889115155496</v>
+        <v>-6.600601340421917</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.396561516599775</v>
+        <v>-6.329546880166042</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.829697555079413</v>
+        <v>-3.762304799032137</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.799128486965891</v>
+        <v>-7.730404474862361</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.022424676786756</v>
+        <v>-7.953398839175506</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.681774038684722</v>
+        <v>-8.611940068098967</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-8.090888534193631</v>
+        <v>-8.02169827264656</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.376024018516041</v>
+        <v>-5.306625440111304</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>3.073119442351135</v>
+        <v>3.142704125073514</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>8.995379921097829</v>
+        <v>9.06476562133593</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.331290655175508</v>
+        <v>6.400493679903306</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>5.790500484476134</v>
+        <v>5.860376538472828</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.71645495263531</v>
+        <v>5.786460144796955</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>11.70548818446472</v>
+        <v>11.7752155947766</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.2046783625737518</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="10">
@@ -953,76 +953,76 @@
         <v>61</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.714153634463145</v>
+        <v>-7.681207985335639</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.09108492069337615</v>
+        <v>0.1245073867916133</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.225406880472612</v>
+        <v>-6.190354486884814</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.19524953804723</v>
+        <v>-10.15937962227407</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.303787110349958</v>
+        <v>-7.238582055191202</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.751696534202651</v>
+        <v>-8.686670491623694</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.370652982125002</v>
+        <v>-1.304638894041538</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.647275033931479</v>
+        <v>-1.58090131103139</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.02578802863334317</v>
+        <v>0.09216399519507235</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.51959235267622</v>
+        <v>2.586919694838684</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.161057144270316</v>
+        <v>1.22810026865583</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.382756795252938</v>
+        <v>-2.315366080559798</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.50409327730268</v>
+        <v>-3.43535989074077</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.457710691324543</v>
+        <v>-0.3886634485380469</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.11469532217621</v>
+        <v>-1.044842300190062</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.156778387907352</v>
+        <v>-2.087576189410953</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.291148432515293</v>
+        <v>-2.221746890881953</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.511942523967825</v>
+        <v>2.581522251437974</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.36524999757129</v>
+        <v>4.434624202650816</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.916150266401395</v>
+        <v>2.985345786703888</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>5.649949179773763</v>
+        <v>5.719823450706663</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>8.852540325571816</v>
+        <v>8.922546921151032</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>9.130075403541433</v>
+        <v>9.199801394012724</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>7.417793116671454</v>
+        <v>7.487647464378362</v>
       </c>
     </row>
     <row r="11">
@@ -1035,76 +1035,76 @@
         <v>59</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8.975052695126429</v>
+        <v>9.008139903549605</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.644239647410892</v>
+        <v>8.677729416374611</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4828967522370462</v>
+        <v>0.5179931228692425</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.510222402769593</v>
+        <v>6.546213464589336</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5911749709480105</v>
+        <v>-0.5259377523994289</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.648668279868204</v>
+        <v>4.713773587650969</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.880134318562632</v>
+        <v>3.946170247849615</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.919012776932156</v>
+        <v>1.985395683366178</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.648221152680698</v>
+        <v>3.714606764668098</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.191416273104608</v>
+        <v>1.258725108793072</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.910505047314771</v>
+        <v>-1.84348891556823</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.877071827430214</v>
+        <v>-3.809699655443055</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.998765348411617</v>
+        <v>-4.930049535543155</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.910964943819032</v>
+        <v>-6.841953111478794</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.879910368642051</v>
+        <v>-5.810083288183861</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-3.59771955318665</v>
+        <v>-3.528529670784735</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.3503343590344912</v>
+        <v>-0.2809339261104711</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.4555793942192494</v>
+        <v>-0.3860118290644934</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.932220894836568</v>
+        <v>-1.862863367978626</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.745975965917047</v>
+        <v>-1.676791262904324</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.5959867395450473</v>
+        <v>-0.5261223003198623</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.021837725065886</v>
+        <v>1.091836652869141</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.296965254648583</v>
+        <v>1.366687426139727</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4732877391218224</v>
+        <v>-0.4034333914145449</v>
       </c>
     </row>
     <row r="12">
@@ -1117,76 +1117,76 @@
         <v>76</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.561769429098682</v>
+        <v>-7.528850213869489</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.672476007819292</v>
+        <v>-2.639097914594579</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.488325995169482</v>
+        <v>-1.453258774405967</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.813034815378792</v>
+        <v>-4.777147812791121</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.17868998265714</v>
+        <v>-5.113509748801661</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-15.46087604218421</v>
+        <v>-15.39594118519906</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-12.3103983629387</v>
+        <v>-12.24449527899927</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.045759870743574</v>
+        <v>-5.979446766058871</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8.624716989427775</v>
+        <v>-8.558423789644209</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.158859362622685</v>
+        <v>-4.091596466240766</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.506914014300719</v>
+        <v>-6.439937789793618</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.854573870632109</v>
+        <v>-2.787210490945284</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.975808163301366</v>
+        <v>-3.907101106592023</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.198137259041467</v>
+        <v>-4.129126774037935</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-7.480125687210737</v>
+        <v>-7.410316381405664</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-5.576935279689906</v>
+        <v>-5.507761751865758</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-7.025372808117297</v>
+        <v>-6.956000083094914</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-8.446018230318153</v>
+        <v>-8.376477811175583</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-6.919432371641172</v>
+        <v>-6.850091220289812</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-8.048921656901612</v>
+        <v>-7.979752292156448</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-8.594324882555114</v>
+        <v>-8.524474029444661</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.413286773336132</v>
+        <v>-3.343293701481009</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.139602993499302</v>
+        <v>-3.069883730755983</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.216374269005854</v>
+        <v>-3.146519921298577</v>
       </c>
     </row>
     <row r="13">
@@ -1196,1145 +1196,1145 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-8.411766254196124</v>
+        <v>-7.94355280680368</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.931574283510592</v>
+        <v>-4.425687733769884</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.276104634270446</v>
+        <v>1.858058613911126</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.207789273717403</v>
+        <v>-3.671228594250664</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.573262972409026</v>
+        <v>-4.007251237746893</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.389639521646984</v>
+        <v>-3.823623588698702</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-8.029501957299068</v>
+        <v>-7.490252432964226</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.308858869873703</v>
+        <v>-7.769082133040236</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.18300728129043</v>
+        <v>-9.661662977465333</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.215441428846177</v>
+        <v>-4.637208565869216</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.757753555625705</v>
+        <v>2.400999629785389</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.438257779081098</v>
+        <v>3.091367927800938</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.319019777852837</v>
+        <v>1.973668555607389</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.973246848946886</v>
+        <v>4.656324295020653</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>7.152479391482025</v>
+        <v>7.87381703247015</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7.747963357277605</v>
+        <v>8.46887745574206</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.616802751504082</v>
+        <v>8.338135636523717</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>8.473825792454903</v>
+        <v>9.204864952782046</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>7.732388807325059</v>
+        <v>8.454121906488204</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.001380323754375</v>
+        <v>6.70451008495202</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5.460625989821473</v>
+        <v>6.164647231234959</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.386500623678494</v>
+        <v>6.0908702355919</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.624326544555338</v>
+        <v>7.337967836729817</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.704678362573098</v>
+        <v>3.381328826785449</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.008622</t>
+          <t>X ≈ -0.008624</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>111</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.277275708626505</v>
+        <v>0.4164531941149932</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.517872122076227</v>
+        <v>4.551150503010433</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.08996919888552</v>
+        <v>3.124910949362707</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3002624728296936</v>
+        <v>-0.26451720052426</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.810013266050589</v>
+        <v>3.875082131936701</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.374838303639159</v>
+        <v>-1.309989656837629</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.040465214234359</v>
+        <v>-2.974685809848033</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.422301946263076</v>
+        <v>-2.356141737866821</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5886234114904809</v>
+        <v>-0.5224425982049397</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.121730172625853</v>
+        <v>3.188896686141419</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.395528093541806</v>
+        <v>3.462433107045015</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.913169534690105</v>
+        <v>4.980459876481049</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.487415684201842</v>
+        <v>6.556068483099587</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.575185876500079</v>
+        <v>3.644130913747226</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.919740370818623</v>
+        <v>2.989498760504596</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.513761391704229</v>
+        <v>3.582887749012578</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.178672481520479</v>
+        <v>5.248015073988554</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.479409357348693</v>
+        <v>1.548914049558348</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.594948058614534</v>
+        <v>2.664259985853654</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.9836079602744832</v>
+        <v>1.052751563310217</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.041042269918208</v>
+        <v>4.110880041884634</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.265764362109032</v>
+        <v>1.335741119825144</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.6404663759522933</v>
+        <v>0.710177131375346</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.069543227437968</v>
+        <v>5.139397575145033</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.00709</t>
+          <t>X ≈ -0.007094</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.467424899857349</v>
+        <v>2.1551028898242</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.401892685895163</v>
+        <v>0.3721685718171202</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.621506189496849</v>
+        <v>2.557077041586929</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.375955559673322</v>
+        <v>3.29431947322945</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.662726574536215</v>
+        <v>5.859800977472418</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.199408352370433</v>
+        <v>2.832400204610295</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.221903060069174</v>
+        <v>-1.561497986045552</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.229959048692145</v>
+        <v>-2.564000374506314</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.920101871314273</v>
+        <v>-3.248951776327267</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.230659958691469</v>
+        <v>-2.569369558323075</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.69064956990907</v>
+        <v>-3.024428404342075</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.237492656329714</v>
+        <v>-2.576378804529611</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.893350907777915</v>
+        <v>-2.241716830633578</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.08278013558225439</v>
+        <v>-0.281454017899442</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.8920375819157726</v>
+        <v>0.5177702481722264</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.01898812743110767</v>
+        <v>-0.3453751720959843</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.6186090227435059</v>
+        <v>0.2489489078052998</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.715050207510842</v>
+        <v>2.329349587209698</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.399540849271467</v>
+        <v>4.002768435525319</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>4.58830861323851</v>
+        <v>4.191201443141821</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.109329289690336</v>
+        <v>0.7341779041450636</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.033964090049381</v>
+        <v>0.6587946029033489</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.309221674677559</v>
+        <v>0.9336248207684221</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.439972480220156</v>
+        <v>3.048255338017604</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.00556</t>
+          <t>X ≈ -0.005564</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>205</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.745072846167723</v>
+        <v>4.780708433743023</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.674445025479301</v>
+        <v>4.449140534491534</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9.304166234604565</v>
+        <v>8.811491007459487</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.04434693105686</v>
+        <v>9.54299010346017</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.776326979927966</v>
+        <v>6.573653458601967</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.573230968499395</v>
+        <v>3.366149541969676</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8590998472516631</v>
+        <v>0.9258108458970469</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.004489434366818</v>
+        <v>3.071598238301974</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.075899869626909</v>
+        <v>2.143004298892699</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.272361336931333</v>
+        <v>2.340426602620077</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.035088149413731</v>
+        <v>3.102890435055947</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.269958897369449</v>
+        <v>2.338135776352011</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.055482735163928</v>
+        <v>4.125042885151387</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.150252280999787</v>
+        <v>2.932982580365788</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.8379885789037971</v>
+        <v>0.3255769147154481</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3.376070862411332</v>
+        <v>2.871936707559165</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.757164942258171</v>
+        <v>2.251996065174488</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>2.166663504494537</v>
+        <v>1.949001655397453</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.05112337736500194</v>
+        <v>0.01818369170728573</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.299009405676919</v>
+        <v>-2.229871813645389</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.4063139665787929</v>
+        <v>-0.3364828952032752</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.457032594961305</v>
+        <v>-1.387058433052346</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.670320398740323</v>
+        <v>-1.600610682828616</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.6924832406218755</v>
+        <v>0.762337588329153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004028</t>
+          <t>X ≈ -0.004033</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.765968456748602</v>
+        <v>2.55507737934677</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.276482325694289</v>
+        <v>5.08738755554041</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.370234260519567</v>
+        <v>3.43108373359415</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.615269571446142</v>
+        <v>3.942091670286587</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.302610876127474</v>
+        <v>2.651575905461456</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.393895378433541</v>
+        <v>4.751131411897752</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.105245525726644</v>
+        <v>4.463607529659136</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9256840165147224</v>
+        <v>-0.589747055168786</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.019576242017877</v>
+        <v>1.364811072751117</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2290347014717966</v>
+        <v>0.1149838694599765</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4329245417944492</v>
+        <v>-0.0913309503867481</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.663531089344687</v>
+        <v>-1.326027470372971</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4017114701805014</v>
+        <v>-0.051257150165128</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.622751628557296</v>
+        <v>-0.2718608512668226</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3.487618929573848</v>
+        <v>3.865802638650109</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.697044905693772</v>
+        <v>2.061961173218691</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.343746459483242</v>
+        <v>0.01053793031783101</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.448672497973071</v>
+        <v>-0.09439069404680822</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7104257391712707</v>
+        <v>-0.3588310546473679</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.9097680361851204</v>
+        <v>1.268223124158006</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1103435047889647</v>
+        <v>0.2466327983150478</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.6640742398225612</v>
+        <v>-0.7894685996668187</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.001822494238112</v>
+        <v>1.887583327700831</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.927166400850609</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002497</t>
+          <t>X ≈ -0.002502</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>262</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.226400480967548</v>
+        <v>-1.574342218334536</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.741269236166147</v>
+        <v>3.404135069291833</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.297787620012343</v>
+        <v>1.960157158313145</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.097072056003469</v>
+        <v>2.759643065908804</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.86986183487673</v>
+        <v>3.561161969614055</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.058329463843634</v>
+        <v>3.747174737799817</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.281567034626455</v>
+        <v>2.969267191961933</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.620999229186566</v>
+        <v>2.308907939151936</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.283393971016778</v>
+        <v>1.971142074563559</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3688198803795402</v>
+        <v>0.05734947806384127</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.634546166610107</v>
+        <v>-1.946465992989815</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.91768817578221</v>
+        <v>-2.229382848459203</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.585706477665944</v>
+        <v>-4.122290967898699</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.807425981738817</v>
+        <v>-4.346259282981563</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.186400816346747</v>
+        <v>-2.726000976160734</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-3.646523386873142</v>
+        <v>-4.411351769148624</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.414937547492308</v>
+        <v>-3.179941034146253</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.759789050741446</v>
+        <v>-2.522288437035591</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.925504765250096</v>
+        <v>-2.685896604217319</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.358077050687257</v>
+        <v>-1.894305646782001</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.520083292618146</v>
+        <v>-1.831454591590052</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.74025915030127</v>
+        <v>-2.670303672874539</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.229815434859177</v>
+        <v>-3.160114601355964</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.543413240480341</v>
+        <v>-2.473558892773063</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0009664</t>
+          <t>X ≈ -0.000972</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.197675657969249</v>
+        <v>3.419227558341454</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.570369064175871</v>
+        <v>1.79941210708111</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.986393781090214</v>
+        <v>4.206472368873314</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.275201854003107</v>
+        <v>6.483659434716877</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.210273661460235</v>
+        <v>1.458729769664146</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.112138431440968</v>
+        <v>3.352275939000457</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.350006891298797</v>
+        <v>2.588568424696817</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>6.790302218111933</v>
+        <v>7.009166360347109</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7.264908877177575</v>
+        <v>7.482034317516664</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.210542366875366</v>
+        <v>5.434211625959598</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.770698471837228</v>
+        <v>4.001553801980712</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.495576084325847</v>
+        <v>3.726905864917306</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.516667524563054</v>
+        <v>1.753988142285515</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.725044252734634</v>
+        <v>1.962142683726007</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.067278337651778</v>
+        <v>1.305789239640802</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.947848812368512</v>
+        <v>3.185413147541283</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.337803394456721</v>
+        <v>-2.089818016757228</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.87388321677868</v>
+        <v>-2.623371943832829</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.9403522207505688</v>
+        <v>-0.6940420052611742</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.753554031373838</v>
+        <v>-0.5072793914913802</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-3.447936555288862</v>
+        <v>-3.191644555566256</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.525215823272788</v>
+        <v>-3.268653545305689</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.821760784708317</v>
+        <v>-2.567182182832951</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-3.760838878806219</v>
+        <v>-3.502291324054383</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005646</t>
+          <t>X ≈ 0.0005581</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.509240673474736</v>
+        <v>6.529494691236827</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6.170921241441576</v>
+        <v>6.194437681867214</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.064572768059364</v>
+        <v>1.095870184334288</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.867886230003286</v>
+        <v>2.717102124706607</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.175873054766441</v>
+        <v>2.050897354866862</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.367765766994488</v>
+        <v>3.237172660585294</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.940771526341138</v>
+        <v>3.803237683233831</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.663128695373814</v>
+        <v>2.715053902113752</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4.380542659741749</v>
+        <v>4.426145114102681</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.28118960073401</v>
+        <v>4.327667091463653</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.234590628950357</v>
+        <v>6.274233262935844</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.61298215712479</v>
+        <v>3.664595731069497</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.172144534403337</v>
+        <v>5.223379363811041</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.944797709684792</v>
+        <v>4.00280225536175</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.609381151222465</v>
+        <v>1.675112567840138</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.197805043122116</v>
+        <v>1.264518441743263</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.07030949822213</v>
+        <v>2.136976331524878</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.04662493578033633</v>
+        <v>0.0225463587825061</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.8415587368349051</v>
+        <v>0.9072096060934953</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.3145186305059084</v>
+        <v>-0.2456331348311807</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.531482928194983</v>
+        <v>-1.456725398855419</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.281932182035597</v>
+        <v>-2.203221237410546</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.824998520583613</v>
+        <v>-3.942778329820136</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.546163388268653</v>
+        <v>-1.671776014551803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002096</t>
+          <t>X ≈ 0.002089</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.826018524208578</v>
+        <v>4.518354315631456</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4130969642650015</v>
+        <v>-0.5451855492432429</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.08902196367201</v>
+        <v>0.9617309574804409</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7020596529067902</v>
+        <v>0.5763352117781366</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6431244189746721</v>
+        <v>-0.7335497822446371</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.109107630626752</v>
+        <v>-1.19998408367892</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7371682985447308</v>
+        <v>0.644758090465551</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8538556769431267</v>
+        <v>-0.9354493614932906</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.467418239473822</v>
+        <v>-1.5473319852195</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.916046888590024</v>
+        <v>-1.99111635206129</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.470016987771551</v>
+        <v>-0.7368863546007631</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.4225942390819455</v>
+        <v>-0.6853748892684237</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.55052320761029</v>
+        <v>-1.807149875422674</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.101656540593801</v>
+        <v>-2.356630067296507</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.762951232784367</v>
+        <v>-2.820725721495407</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.151849264570835</v>
+        <v>-3.214418253480751</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.959604186811966</v>
+        <v>-3.018178129525872</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.043061596333573</v>
+        <v>-5.091021030153343</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-7.792768030801511</v>
+        <v>-7.830027724298979</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-6.294013935291822</v>
+        <v>-6.330215523173209</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-5.858171764624082</v>
+        <v>-5.886206375212105</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.757688931945523</v>
+        <v>-3.995842838521675</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.460886343570827</v>
+        <v>-5.697521703242067</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.320074112674426</v>
+        <v>-7.751783079193338</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003627</t>
+          <t>X ≈ 0.003619</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.182514537646171</v>
+        <v>-3.89245730918131</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.468435866566075</v>
+        <v>-2.185988546721923</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.874843058289834</v>
+        <v>-2.596458723591176</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.535668108829839</v>
+        <v>-1.265198857186007</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.183976091603661</v>
+        <v>-4.149742862652793</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.511849554744387</v>
+        <v>-4.473912601490703</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.707431750353386</v>
+        <v>-2.687543149559033</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.651539762628261</v>
+        <v>1.635458171785253</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.394348546198586</v>
+        <v>-1.105063788694359</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.164190149442895</v>
+        <v>-1.871474249978434</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.408760455883474</v>
+        <v>-2.113653827322594</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.13463691881384</v>
+        <v>-0.8473223037806648</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.737622275021891</v>
+        <v>-1.450225987099813</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.569560082049797</v>
+        <v>-5.263619906224569</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.612445704244408</v>
+        <v>-2.324333046030802</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.633089732662718</v>
+        <v>-5.331608260087606</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.183220292828473</v>
+        <v>-2.893200553477264</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.705978684332365</v>
+        <v>-0.4259723514667613</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.00878721057844</v>
+        <v>-0.7244947517088249</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.341401900387865</v>
+        <v>-1.051806785151243</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.368977611070498</v>
+        <v>-1.077891669903408</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-3.517471526816728</v>
+        <v>-3.21380917898086</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.688292215256887</v>
+        <v>-1.399428059249772</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.800502984577157</v>
+        <v>-2.508972444358804</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005158</t>
+          <t>X ≈ 0.005149</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.368835249282483</v>
+        <v>1.800627391529709</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.387865387308928</v>
+        <v>3.867630555430424</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3987740269322515</v>
+        <v>0.03434799456592685</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5221992513287503</v>
+        <v>-0.6796920999462586</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3211228342173555</v>
+        <v>0.8168055386753679</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.448928875124956</v>
+        <v>-2.012029166409235</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.585497351247227</v>
+        <v>-5.187929962689104</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.677443255126917</v>
+        <v>-4.256562825760966</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4743321115584607</v>
+        <v>0.01138990408659168</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.24131232263796</v>
+        <v>-0.7508745637268674</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.161576974731354</v>
+        <v>-1.69014894936528</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.43452151174376</v>
+        <v>-1.959072170158073</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.955756633344777</v>
+        <v>-2.467522794136002</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.979438100270059</v>
+        <v>-1.470840944596809</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.252837372937087</v>
+        <v>0.300195448206857</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.2551421870930142</v>
+        <v>0.2865527059408279</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.8054938463127144</v>
+        <v>1.369919731679545</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.492520202916296</v>
+        <v>3.089537812838074</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.112786899717811</v>
+        <v>2.089979354914462</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.506596433495254</v>
+        <v>0.4542007037710647</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.956051088008032</v>
+        <v>2.952663753953509</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.478898427575004</v>
+        <v>3.487541100685668</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.358464013218814</v>
+        <v>1.326657792152645</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.677732254788666</v>
+        <v>3.689166856621839</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.006689</t>
+          <t>X ≈ 0.00668</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.421667294831529</v>
+        <v>-2.895023831779312</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.75007287790644</v>
+        <v>-5.716433400833743</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-8.226298804157551</v>
+        <v>-9.139428377901872</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.429252141860744</v>
+        <v>-7.864769434627831</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-9.327009599241926</v>
+        <v>-10.18581341781009</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-8.653970746044102</v>
+        <v>-9.501215336714097</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-6.43138190055388</v>
+        <v>-7.289870893993758</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.709997108418868</v>
+        <v>-6.574067670440009</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.151701035426356</v>
+        <v>-5.042183046910282</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.441440769231328</v>
+        <v>-5.322078571370731</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.635356266414249</v>
+        <v>-3.556505517674729</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.200487803479085</v>
+        <v>-7.337818321604317</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.827713662374016</v>
+        <v>-6.979744180687476</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.051995134146537</v>
+        <v>-6.218112024475637</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.67012983441203</v>
+        <v>-3.369905682484593</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-3.592163352777511</v>
+        <v>-3.977509376461562</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.212468180338625</v>
+        <v>-2.609583778191471</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.000504910040348</v>
+        <v>-1.713049568705181</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.4769821835474133</v>
+        <v>-0.9964707311271326</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.735560851801409</v>
+        <v>1.193344540169406</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.01972325163754363</v>
+        <v>-0.8528014407533249</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.934778545511719</v>
+        <v>1.072680261680958</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.717167925191816</v>
+        <v>2.15915649397148</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.118383946329452</v>
+        <v>0.5760402479688125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.00822</t>
+          <t>X ≈ 0.00821</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>129</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.673744645661522</v>
+        <v>-4.025839558056532</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.547509217566827</v>
+        <v>-3.585545409588903</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.14111379858975</v>
+        <v>-1.206699386567337</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-9.228666009517731</v>
+        <v>-7.287508047959037</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.144129062552814</v>
+        <v>0.7999130668596024</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.031943059075317</v>
+        <v>-2.086278893948972</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.043121138654527</v>
+        <v>-2.095871774942466</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-6.645280393251277</v>
+        <v>-4.675561124829549</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.61104496182498</v>
+        <v>-4.628987885346532</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.304037986366581</v>
+        <v>-2.341089307072949</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.794918183210342</v>
+        <v>-2.829012412188128</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.097653631100222</v>
+        <v>-3.917101652457355</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.910250664162938</v>
+        <v>-1.980234603896598</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.815980414339009</v>
+        <v>-0.6794378821194229</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.692252104058802</v>
+        <v>-0.5450507787290775</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.3232425477991043</v>
+        <v>0.822053284160468</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-5.109743324457099</v>
+        <v>-3.965503301017783</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.889145345203538</v>
+        <v>-1.744762609490124</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.223409779170858</v>
+        <v>-3.079258825465025</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-4.336240310077478</v>
+        <v>-3.66513015644351</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-3.329053122176248</v>
+        <v>-2.674625330031603</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.629814379369201</v>
+        <v>-1.49186168696292</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-3.905426809786384</v>
+        <v>-2.762813331069978</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-3.206174350605195</v>
+        <v>-1.585932405998733</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009753</t>
+          <t>X ≈ 0.009743</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.663958304365607</v>
+        <v>-1.142093996225015</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.019214140295126</v>
+        <v>-3.496820919263079</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.403570780104573</v>
+        <v>-3.889952187745443</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.08173176807849813</v>
+        <v>-0.6078937383602607</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.427044172560038</v>
+        <v>-1.913759023875095</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.828462565199814</v>
+        <v>3.280688458980308</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.059955913042167</v>
+        <v>0.5261961341922614</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.802594994210878</v>
+        <v>1.250478455025217</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.225409682414679</v>
+        <v>-2.713021894232156</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.043003339949834</v>
+        <v>-5.483863596885428</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3129885802267793</v>
+        <v>-1.221365562705635</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.156343656343665</v>
+        <v>5.557199674845201</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.052260601121795</v>
+        <v>4.446608177568805</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.871720116618128</v>
+        <v>7.260726072607198</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.171972551050168</v>
+        <v>3.572279744723673</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.726216274140903</v>
+        <v>2.146464646464644</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.673755233053285</v>
+        <v>6.052951549891219</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>6.548363653692732</v>
+        <v>4.938009835969027</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>7.784894979889749</v>
+        <v>6.164002226994363</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>8.992346938775484</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>7.428738366512242</v>
+        <v>5.808301868996359</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.311966984338973</v>
+        <v>3.712253887385231</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>9.668374803882465</v>
+        <v>8.027132640271333</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>9.592433464613883</v>
+        <v>7.951300387048114</v>
       </c>
     </row>
     <row r="27">
@@ -2344,325 +2344,325 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9102932327676783</v>
+        <v>-0.2882063511204933</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.277623088248006</v>
+        <v>-1.77306322085731</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.539445016259876</v>
+        <v>-2.021165687542293</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.366808183855298</v>
+        <v>-3.860297871796597</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.949341157534263</v>
+        <v>1.44276978190603</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.380624313513678</v>
+        <v>3.878108646530727</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.529944147633209</v>
+        <v>3.134045520311638</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.147751299958507</v>
+        <v>1.741606864034715</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.193328628468848</v>
+        <v>1.775126743757532</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.549521310359729</v>
+        <v>2.148118315657577</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5766895662391036</v>
+        <v>0.151677318390071</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.162764202090045</v>
+        <v>7.804729268030769</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.53265500607484</v>
+        <v>11.23976309795373</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>12.43489370065844</v>
+        <v>12.18496849684969</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>8.405175944767201</v>
+        <v>8.117734290178213</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.87664048877064</v>
+        <v>8.712121212121204</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>11.11333331147561</v>
+        <v>10.85093134787101</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>9.884754389762335</v>
+        <v>9.609727007686203</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.853686541458181</v>
+        <v>8.689254752246875</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.793539325842673</v>
+        <v>5.467009653124038</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.250338916844747</v>
+        <v>6.060827121521605</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>7.421574872438093</v>
+        <v>9.394072069203425</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.572754533302209</v>
+        <v>7.395819508958198</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.002431171561888</v>
+        <v>3.91089634664398</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01282</t>
+          <t>X ≈ 0.01281</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-5.859156839514455</v>
+        <v>-7.189044393918451</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-10.51107260787415</v>
+        <v>-10.29050560831373</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-9.280343067641006</v>
+        <v>-9.13296740402248</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-9.976359509563515</v>
+        <v>-9.828808707192941</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-8.961972114251338</v>
+        <v>-7.397914763694743</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.537774380364048</v>
+        <v>-2.898351148942162</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.053855224950041</v>
+        <v>-5.233325561714608</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.013238014454359</v>
+        <v>-4.102525724036518</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.49989706956454</v>
+        <v>0.3028970353504192</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0843192308695393</v>
+        <v>-1.154371465093092</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.118933442313633</v>
+        <v>-4.305893223837586</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.557196534808483</v>
+        <v>4.851265909473902</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.432705316321339</v>
+        <v>3.734325937750462</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.211348505286942</v>
+        <v>4.362175347969547</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.4326573606160338</v>
+        <v>0.8054813257513018</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.1624026890053827</v>
+        <v>-0.04940711462450764</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-2.956765632009251</v>
+        <v>-1.63259961392086</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.0766744212388204</v>
+        <v>1.161110406895688</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.1394487416929593</v>
+        <v>-0.07227357449887251</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.166044776119399</v>
+        <v>0.1145722354691543</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.260904068614032</v>
+        <v>3.919852154459726</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.199874386105748</v>
+        <v>-0.5038198939058987</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.01788776084504207</v>
+        <v>-0.2293451814239233</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.398708213319367</v>
+        <v>-0.3051774346471205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01435</t>
+          <t>X ≈ 0.01434</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.838976478214541</v>
+        <v>-6.959223181807999</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-12.6730127428962</v>
+        <v>-13.93716237332023</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.592374793714797</v>
+        <v>-8.710651507821311</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-10.4710231793717</v>
+        <v>-11.63656849022699</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-10.82555413278063</v>
+        <v>-11.96167520209057</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-12.80539235856069</v>
+        <v>-13.98980873109288</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-11.39836905388969</v>
+        <v>-12.53383718706296</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.34936132080373</v>
+        <v>-8.388259458026845</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.350800582241668</v>
+        <v>-8.357456036795966</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.776809906054545</v>
+        <v>-4.69803553049622</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.502450638939209</v>
+        <v>-4.436796401154822</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-2.504719593776592</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.732122717423017</v>
+        <v>-3.629306162057219</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.127392571935538</v>
+        <v>-6.072607260726002</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-5.786323810972839</v>
+        <v>-4.508528336084346</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-5.191263761351529</v>
+        <v>-3.914141414141412</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.151444412022123</v>
+        <v>-1.8258363288966</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-7.60425391507399</v>
+        <v>-6.375121477162288</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-3.040304665185587</v>
+        <v>-1.714785651793456</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6793478260869534</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-5.570374322041523</v>
+        <v>-4.29270823201378</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-5.646329377684133</v>
+        <v>-4.368554193422881</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.023728124245331</v>
+        <v>0.3503649635037149</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.07424357996441</v>
+        <v>2.496754932502597</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01588</t>
+          <t>X ≈ 0.01587</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-2.510310982895845</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-15.0974985240607</v>
+        <v>-11.91268684884468</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-10.00798936615363</v>
+        <v>-6.672384219554026</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-12.94400490156901</v>
+        <v>-9.658065511724011</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-13.36654845520708</v>
+        <v>-10.05213104254636</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-10.94570686625524</v>
+        <v>-7.580782572066745</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.90986738547997</v>
+        <v>0.6565927533669367</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-7.621411721720179</v>
+        <v>-4.155418225185677</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8.461911693352775</v>
+        <v>-6.328383257723168</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.013524881899954</v>
+        <v>-4.863536695997425</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.739165614784618</v>
+        <v>-4.519546983905414</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.240481740481741</v>
+        <v>-7.059368648425682</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-14.80941740341329</v>
+        <v>-11.45758899034011</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-15.03077421444768</v>
+        <v>-11.67866786678668</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-13.46748323126276</v>
+        <v>-12.33681116436723</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-8.427978737196938</v>
+        <v>-7.196969696969695</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-8.562072431345861</v>
+        <v>-7.330886833947169</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-8.667055847441141</v>
+        <v>-7.435727537768351</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-8.450932684509326</v>
+        <v>-7.219836156844025</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-8.263888888888893</v>
+        <v>-7.032990346875998</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.362644853442362</v>
+        <v>-3.03008196938751</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-6.660822131307228</v>
+        <v>-5.378655203523891</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-8.608269187047327</v>
+        <v>-7.376907763769076</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-13.12865497076024</v>
+        <v>-11.9981945624469</v>
       </c>
     </row>
     <row r="31">
@@ -2672,161 +2672,161 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-21.67412140575085</v>
+        <v>-20.30751378009869</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-18.00929692039512</v>
+        <v>-20.64229057844855</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.448997384481316</v>
+        <v>-10.96919851636838</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.83720930232564</v>
+        <v>-0.5710414246999562</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-8.528060482698407</v>
+        <v>-12.01794300835829</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.340895869691622</v>
+        <v>-8.127273118557206</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.886237998254352</v>
+        <v>2.211889308663551</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.392316647264202</v>
+        <v>-5.47372954349693</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.350800582241625</v>
+        <v>-5.432242361582283</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.124635993011054</v>
+        <v>-6.205158037618773</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.149723274104332</v>
+        <v>1.476309011950612</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.870629370629374</v>
+        <v>-2.506144095201137</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.74613815214223</v>
+        <v>0.07439754164644086</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.524781341107875</v>
+        <v>-0.1466813348001494</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-4.508528336084403</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>4.460910151691955</v>
+        <v>-0.2104377104377164</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.326816457543032</v>
+        <v>3.35934885628852</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>8.221833041447809</v>
+        <v>3.254508152467395</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>8.437956204379567</v>
+        <v>3.470399533391664</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>8.624999999999943</v>
+        <v>3.657245343359641</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>12.0817995910021</v>
+        <v>6.818402879097412</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>8.00584453535955</v>
+        <v>3.038853213984616</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.2806197018415091</v>
+        <v>-4.094079480940849</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>8.204678362573041</v>
+        <v>3.237495673243288</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.01894</t>
+          <t>X ≈ 0.01892</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>15</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.325878594249303</v>
+        <v>6.359152886568133</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.990703079604977</v>
+        <v>6.024376088218318</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.55100261551884</v>
+        <v>4.586357039187327</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-9.496124031007845</v>
+        <v>-9.459930313588941</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>16.80527285063478</v>
+        <v>16.87094588053046</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>23.65910413030822</v>
+        <v>23.72457873329449</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>22.8862379982542</v>
+        <v>22.95263004940414</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>29.27435001940231</v>
+        <v>29.34108527131774</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>29.31586608442504</v>
+        <v>29.38257245323254</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>21.87536400698894</v>
+        <v>21.94299011052938</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.816389940770847</v>
+        <v>8.883716419357874</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.537296037296088</v>
+        <v>8.60496701591002</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.920528514524435</v>
+        <v>-5.851528384279476</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-6.20575651497461</v>
+        <v>-6.136363636363534</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.2218330414476597</v>
+        <v>0.2915451895042835</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>7.291666666666757</v>
+        <v>7.360949047063485</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.2806197018417507</v>
+        <v>0.3503649635038357</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-6.461988304093566</v>
+        <v>-6.392133956386289</v>
       </c>
     </row>
     <row r="33">
@@ -2839,158 +2839,158 @@
         <v>16</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.674121405750839</v>
+        <v>-3.64084711343201</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-16.50929692039512</v>
+        <v>-16.47562391178178</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.69899738448126</v>
+        <v>-11.66364296081277</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2780604826984643</v>
+        <v>-0.2123874528027869</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.09089586969172103</v>
+        <v>-0.02542126670545031</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.8637620017457479</v>
+        <v>-0.797369950595801</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.107683352735734</v>
+        <v>5.174418604651166</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.149199417758368</v>
+        <v>5.21590578656587</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.62536400698894</v>
+        <v>10.69299011052938</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.600276725895725</v>
+        <v>-1.532950247308698</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-14.37937062937067</v>
+        <v>-14.31169965075674</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.253861847857728</v>
+        <v>-9.184861717612769</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.475218658892125</v>
+        <v>-9.405940594059402</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-10.13414989792943</v>
+        <v>-10.06408389163996</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-9.53908984830818</v>
+        <v>-9.469696969697104</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-9.778166958552248</v>
+        <v>-9.708454810495624</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-3.312043795620433</v>
+        <v>-3.242563429571298</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.125000000000043</v>
+        <v>3.194282380396771</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-3.66820040899804</v>
+        <v>-3.598263787569387</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-3.744155464640649</v>
+        <v>-3.674109748978488</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-3.469380298158519</v>
+        <v>-3.399635036496434</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.704678362573183</v>
+        <v>2.774532710280461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.022</t>
+          <t>X ≈ 0.02198</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>23</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.19586053618555</v>
+        <v>-10.16258624386672</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-10.5310360508299</v>
+        <v>-10.49736304221656</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.97073651491604</v>
+        <v>-11.93538209124755</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-12.68452982810923</v>
+        <v>-12.64833611069032</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-8.701973526176722</v>
+        <v>-8.636300496281045</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.514808913169908</v>
+        <v>-8.449334310183637</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-13.63550113218043</v>
+        <v>-13.56910908103048</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-9.566229690742496</v>
+        <v>-9.499494438827064</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.87253971267641</v>
+        <v>-13.80583334386891</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-14.64637512344584</v>
+        <v>-14.5787490199054</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-14.37201585633051</v>
+        <v>-14.30468937774348</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.30328367284888</v>
+        <v>-10.23561269423495</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.615703369533506</v>
+        <v>1.684703499778465</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.394346558499151</v>
+        <v>1.463624623331874</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>5.083241406418431</v>
+        <v>5.153307412707896</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.678301456039783</v>
+        <v>5.747694334650859</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-7.49927049897871</v>
+        <v>-7.429701063196184</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-7.60425391507399</v>
+        <v>-7.534541767017366</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-7.388130752142175</v>
+        <v>-7.31865038609304</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-7.201086956521799</v>
+        <v>-7.13180457612507</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-3.396461278563173</v>
+        <v>-3.32652465713452</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>1.150184919232842</v>
+        <v>1.219930180894927</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-3.27358250699212</v>
+        <v>-3.203728159284843</v>
       </c>
     </row>
   </sheetData>
@@ -3180,165 +3180,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02164</t>
+          <t>X &gt; -0.02163</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3346</v>
+        <v>3350</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1400667806546707</v>
+        <v>0.1391706748870334</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1177814644029738</v>
+        <v>0.1169027786096848</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.09005815457427957</v>
+        <v>0.08917519403742347</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1057773355994982</v>
+        <v>0.104857025679209</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.0050292791323443</v>
+        <v>-0.006465814334397635</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06860098265243408</v>
+        <v>-0.06995808380754198</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.08135046442783533</v>
+        <v>-0.08271298593879095</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01575507677051036</v>
+        <v>-0.01720349873563976</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.04283226512522731</v>
+        <v>0.04131440469365089</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05988781651274877</v>
+        <v>0.05832899281237758</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05386141045438109</v>
+        <v>0.05231588412157606</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.03024819135599444</v>
+        <v>0.02872271688161021</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.06410909242137564</v>
+        <v>-0.06555198836556286</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.08904464220559305</v>
+        <v>-0.09046440358321206</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.07453737930051574</v>
+        <v>-0.07599219768342635</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.08768853644161823</v>
+        <v>-0.08911328893461246</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.05493123109400244</v>
+        <v>-0.05639933157763011</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.05262996571214984</v>
+        <v>-0.05410439333233086</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1171019872050394</v>
+        <v>-0.118494875174882</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1212686567164241</v>
+        <v>-0.1226526225847877</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1988812092368306</v>
+        <v>-0.2001874380315769</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1972617967791592</v>
+        <v>-0.1985727561383044</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2631508389412218</v>
+        <v>-0.2643769045954301</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.2615499697640189</v>
+        <v>-0.2627807225554406</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02011</t>
+          <t>X &gt; -0.0201</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3317</v>
+        <v>3321</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1881540433509983</v>
+        <v>0.186904082740277</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.108702480623144</v>
+        <v>0.1075349275840622</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.09324347831083202</v>
+        <v>0.09204225761930473</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.004564746221014104</v>
+        <v>-0.005675100578770298</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1731444155521729</v>
+        <v>-0.1749623031021912</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2689318517006711</v>
+        <v>-0.2706294128569482</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2751297282004188</v>
+        <v>-0.2768486803740728</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2366010757071138</v>
+        <v>-0.2383773198319048</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2079434393844934</v>
+        <v>-0.2097536858561924</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1540565874271493</v>
+        <v>-0.155960414208252</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1025289781479799</v>
+        <v>-0.1044859401701217</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1239636002327487</v>
+        <v>-0.1259060713987665</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1192464632423835</v>
+        <v>-0.1212362674327423</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2326577932474052</v>
+        <v>-0.234520600063604</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2123218762817984</v>
+        <v>-0.2142340417901138</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2308191716163108</v>
+        <v>-0.2326888591532565</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1364807747072732</v>
+        <v>-0.1384698759052156</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1031744818745466</v>
+        <v>-0.105208642776951</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1099065289136263</v>
+        <v>-0.1119260272862661</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1157407407407476</v>
+        <v>-0.1177476947912339</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1892847463473473</v>
+        <v>-0.1912240763779636</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2171141871473381</v>
+        <v>-0.2190239831041936</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.285986687549638</v>
+        <v>-0.2878048137389797</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2837147637458699</v>
+        <v>-0.2855395571089616</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3291</v>
+        <v>3294</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3089805858001995</v>
+        <v>0.323578572428751</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2315723823516294</v>
+        <v>0.2161734344184651</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1669446445042482</v>
+        <v>0.1519678989157356</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.073995771670198</v>
+        <v>0.05928111268353575</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0628036851153766</v>
+        <v>-0.07844540631923991</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2212222522846048</v>
+        <v>-0.2367739237102313</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3120691359657783</v>
+        <v>-0.3273457887111277</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2408198223474187</v>
+        <v>-0.2560949905149954</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1517685193257208</v>
+        <v>-0.1671404509681267</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.09135308832119904</v>
+        <v>-0.1065866730256388</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07182636269960341</v>
+        <v>-0.08715345263074425</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.000396969061810637</v>
+        <v>-0.01572263926244233</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.01703568189774529</v>
+        <v>-0.032062927900256</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.09927197606873506</v>
+        <v>-0.1141730395799812</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1038468676263946</v>
+        <v>-0.1185798044465045</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.09683461945081007</v>
+        <v>-0.1117320999210776</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.03097614403367999</v>
+        <v>-0.04590432176077996</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.003452695678873852</v>
+        <v>-0.01148511352592863</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.05567465098150848</v>
+        <v>0.04062844675486588</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.01232928679817746</v>
+        <v>-0.02736710413935128</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.08213483522746401</v>
+        <v>-0.09697473691718983</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1095517598121418</v>
+        <v>-0.1243524674250054</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1203523516213707</v>
+        <v>-0.1352192550092397</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1174121874117162</v>
+        <v>-0.1322675325854377</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3269</v>
+        <v>3273</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3052224581617153</v>
+        <v>0.3033276438495847</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3206939638345929</v>
+        <v>0.3187615206916661</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1133126459138722</v>
+        <v>0.1115543676632456</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05490465045571113</v>
+        <v>0.05317830064336704</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01954466761330309</v>
+        <v>-0.02253326082223595</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2106859518334474</v>
+        <v>-0.2134340287838015</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3273955988242179</v>
+        <v>-0.3300447226322376</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2842496761835918</v>
+        <v>-0.2869678349961404</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1644424823634338</v>
+        <v>-0.167305892266242</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1593603305072477</v>
+        <v>-0.1622730473653533</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1415625272363741</v>
+        <v>-0.1444840269800309</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.06780403382048661</v>
+        <v>-0.07083207084801302</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1075203844431414</v>
+        <v>-0.1105620830208451</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1888508638326556</v>
+        <v>-0.1918071794995484</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1280486166603581</v>
+        <v>-0.1311161890196075</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1555073032973624</v>
+        <v>-0.1585113555549427</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.08832395759738176</v>
+        <v>-0.09141898472322652</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.08351047000263634</v>
+        <v>-0.08661888490854608</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.06296010594419954</v>
+        <v>-0.06608386886355078</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.132714634891542</v>
+        <v>-0.1357450837473095</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2299363503182477</v>
+        <v>-0.2328791721846883</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2265003133106944</v>
+        <v>-0.2294532604287909</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2698390137547619</v>
+        <v>-0.2727260566551806</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.266413714514691</v>
+        <v>-0.2693108583111368</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3234</v>
+        <v>3238</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3326332764721087</v>
+        <v>0.3303273729219143</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.382594971496772</v>
+        <v>0.380204309077115</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3113712791132102</v>
+        <v>0.3089713380519115</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2600734695044409</v>
+        <v>0.2576878570679924</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.03511197349581607</v>
+        <v>0.03131841148950798</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2523349840828288</v>
+        <v>-0.2557652470493892</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3619933151877248</v>
+        <v>-0.3653423008261711</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1923166472642706</v>
+        <v>-0.195894855705312</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.07163776291260859</v>
+        <v>-0.0753638107289305</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.08892170729676963</v>
+        <v>-0.09268024617419002</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.07386773297918836</v>
+        <v>-0.07762880775164405</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.02709090047352447</v>
+        <v>-0.03093041998746315</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.02427787251107816</v>
+        <v>-0.02819812881625694</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1040719264630212</v>
+        <v>-0.1079110374091599</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.03547583070771054</v>
+        <v>-0.03944576413765333</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.06962655404524298</v>
+        <v>-0.07351705595698377</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.03109776646189744</v>
+        <v>-0.0350470804803038</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1176731313917472</v>
+        <v>-0.1215250940961212</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1609940889208374</v>
+        <v>-0.1647805125191937</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2026714021000657</v>
+        <v>-0.2063962130640959</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2950925931190582</v>
+        <v>-0.2987420350237926</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.2908180109940872</v>
+        <v>-0.2944801193487692</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3994421219605968</v>
+        <v>-0.4029539620906633</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2715121136173764</v>
+        <v>-0.2751893403681791</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3173</v>
+        <v>3177</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4873304090176589</v>
+        <v>0.4841528865680331</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3881991672418081</v>
+        <v>0.3851138187590166</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4370389336151703</v>
+        <v>0.4337616670796578</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4610740063656635</v>
+        <v>0.4577007989124553</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1762001689306061</v>
+        <v>0.1709041617153559</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.08893723603451775</v>
+        <v>-0.093887620383029</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.3426021271375603</v>
+        <v>-0.3473073331881125</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1643454964332847</v>
+        <v>-0.1693020342464209</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.07351074535329616</v>
+        <v>-0.0785804289729839</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.139069629659943</v>
+        <v>-0.1441299145411321</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.09760880373627145</v>
+        <v>-0.102699463609639</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.01819608962466646</v>
+        <v>0.01293189518247573</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.04262056420252947</v>
+        <v>0.03722109292671405</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.09727332430211533</v>
+        <v>-0.1025204497230305</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.01472815060069621</v>
+        <v>-0.02014164430787702</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.02950166849038283</v>
+        <v>-0.03484610627467077</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.01235104873799742</v>
+        <v>0.006938657144651472</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1682267257746446</v>
+        <v>-0.1734249644384462</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2480098119829321</v>
+        <v>-0.2530913994015904</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.2626298394711952</v>
+        <v>-0.2676792668840022</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.4093842880911467</v>
+        <v>-0.4143015234183594</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.4665964095224595</v>
+        <v>-0.4714516804033764</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.5826443183222736</v>
+        <v>-0.5873317010652599</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4193367650663617</v>
+        <v>-0.4242397165373788</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3114</v>
+        <v>3118</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.326516146050281</v>
+        <v>0.3228587127380393</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2317745081763078</v>
+        <v>0.2281977442691741</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4361700796335768</v>
+        <v>0.4321678069476533</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3464626526765713</v>
+        <v>0.3424916112040108</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1907393896283764</v>
+        <v>0.1840900734962219</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1786991902536172</v>
+        <v>-0.184860042215611</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4226090154793383</v>
+        <v>-0.4285501738812485</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2038182447083585</v>
+        <v>-0.2100740564847641</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1440252546609386</v>
+        <v>-0.1503565817711916</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.16427793674508</v>
+        <v>-0.1706752789980754</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.06326041633384705</v>
+        <v>-0.06975957340259953</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.09199853249756984</v>
+        <v>0.08526520547334115</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1381381521422327</v>
+        <v>0.1312137058451555</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.03182359462900308</v>
+        <v>0.02500569750070269</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.09639765250285137</v>
+        <v>0.08941786723435996</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.03810425803404627</v>
+        <v>0.03126272320130141</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.01922273758147952</v>
+        <v>0.01238589332555762</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1627823431676347</v>
+        <v>-0.1694023136966507</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2160995827316867</v>
+        <v>-0.2226306726068401</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2345253367543307</v>
+        <v>-0.2410155055738059</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.4058487888503777</v>
+        <v>-0.412185607498806</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4947973131643053</v>
+        <v>-0.5010328259014827</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.6182567026528147</v>
+        <v>-0.6243064055248837</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.4183145725585646</v>
+        <v>-0.42463342185561</v>
       </c>
     </row>
     <row r="13">
@@ -3758,1883 +3758,1883 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3038</v>
+        <v>3042</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5238531123805359</v>
+        <v>0.5190223808584165</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3044285698009546</v>
+        <v>0.2998330072782665</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4843141552376053</v>
+        <v>0.4792724815639815</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.475535005399486</v>
+        <v>0.4703984475694369</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3250634950575062</v>
+        <v>0.3164429947633636</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2036067481093724</v>
+        <v>0.1951669685887083</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.125218630223614</v>
+        <v>-0.1333457596836993</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.05767355623611081</v>
+        <v>-0.06593456735668468</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.06813161559655612</v>
+        <v>0.05970689876738078</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.06434765749336435</v>
+        <v>-0.07271669575334982</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.09793697453036287</v>
+        <v>0.08939017822321205</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1657113378424881</v>
+        <v>0.157029884279325</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.241054518163871</v>
+        <v>0.232105200172974</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1376422334963294</v>
+        <v>0.1287907296627466</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.2859354319031908</v>
+        <v>0.2767879536566653</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1785726598994373</v>
+        <v>0.1696472925981141</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1954535675594542</v>
+        <v>0.1864810064774076</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.04443488113238203</v>
+        <v>0.03563967769335363</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.04840593824284412</v>
+        <v>-0.05705309153388782</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.0390368178829732</v>
+        <v>-0.04767428408128183</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2010021189617746</v>
+        <v>-0.2095117350241509</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.4217870435879263</v>
+        <v>-0.4300230209889122</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.555181548569756</v>
+        <v>-0.5632071692600675</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3483170291319695</v>
+        <v>-0.3566309978064055</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.009387</t>
+          <t>X &gt; -0.009389</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2934</v>
+        <v>2939</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8405894498460995</v>
+        <v>0.8156012322803932</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4900264896184083</v>
+        <v>0.4654432952428706</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4562479623884528</v>
+        <v>0.4309516337818238</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6415424099762248</v>
+        <v>0.6155456354930422</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4986919724319137</v>
+        <v>0.4679708974338581</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3664212034790495</v>
+        <v>0.3360092371836743</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1549604652146499</v>
+        <v>0.1244839059671676</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2348019968035331</v>
+        <v>0.2040294337543855</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4314985021937758</v>
+        <v>0.400401385753419</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1182405334475618</v>
+        <v>0.08725018502988746</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.03910230362582467</v>
+        <v>0.008377665970435544</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.08515754442434798</v>
+        <v>0.05419326689833781</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.2028444339758479</v>
+        <v>0.1710704857770153</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.001683515020921789</v>
+        <v>-0.02988091281152094</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.04254055399038492</v>
+        <v>0.01054297403168647</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.08973566747867068</v>
+        <v>-0.1212069798768169</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.06760720787688967</v>
+        <v>-0.09920134360586985</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2543574347427224</v>
+        <v>-0.2857043860474135</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.3242077969814474</v>
+        <v>-0.3553351687017283</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2531484002722948</v>
+        <v>-0.284310891774517</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4016869599002391</v>
+        <v>-0.4329000894047894</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.6276704510165843</v>
+        <v>-0.6585538156223976</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.8096699063356141</v>
+        <v>-0.8401112269725388</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4565349980267683</v>
+        <v>-0.4876312910806391</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.007856</t>
+          <t>X &gt; -0.007859</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2823</v>
+        <v>2828</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8234190018388006</v>
+        <v>0.8312679339198397</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3316521129967924</v>
+        <v>0.3050778426041845</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3526903792318237</v>
+        <v>0.3252127780429674</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.6785740578655108</v>
+        <v>0.6500884130029192</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3684912414394717</v>
+        <v>0.3342405767019514</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4348873052467184</v>
+        <v>0.4006152758103951</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2806041954373981</v>
+        <v>0.2461274132003695</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3392789850006181</v>
+        <v>0.3045170575344258</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4716095657499082</v>
+        <v>0.4366233384476885</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0001437038518190548</v>
+        <v>-0.03449053690200543</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.09287193040912456</v>
+        <v>-0.1271952314692015</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1046792713459297</v>
+        <v>-0.1391644394890932</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.0442641061499387</v>
+        <v>-0.07954294339653956</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1388261421254455</v>
+        <v>-0.1740871761594747</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.07059057589552964</v>
+        <v>-0.10638209396636</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.2314247123136965</v>
+        <v>-0.266594007778771</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.2738902562378911</v>
+        <v>-0.3090814788084799</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.3225289239110367</v>
+        <v>-0.3577138083784774</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.438988632961312</v>
+        <v>-0.4738553462673778</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.301777502652989</v>
+        <v>-0.336791065930953</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.5763745066624963</v>
+        <v>-0.6112450662694044</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.7021200664104725</v>
+        <v>-0.7368305970349383</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.8666890800281166</v>
+        <v>-0.900960593230181</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.6738196891449277</v>
+        <v>-0.7084941638356028</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006325</t>
+          <t>X &gt; -0.006329</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2687</v>
+        <v>2691</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7908232436956908</v>
+        <v>0.7638709108953492</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3280969518824719</v>
+        <v>0.3016622239114355</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2378563821361652</v>
+        <v>0.2115875814225632</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5420486078298339</v>
+        <v>0.5154694404086939</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.04991438795933334</v>
+        <v>0.05293185321419003</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2949636497168271</v>
+        <v>0.2768120297139305</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3566521994377254</v>
+        <v>0.3381544216346626</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4693185728615177</v>
+        <v>0.450554548500449</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6432778781580666</v>
+        <v>0.6242575973567028</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1130537515279926</v>
+        <v>0.09456127503954548</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.03861216299316794</v>
+        <v>0.0203041905611272</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.003271089784618653</v>
+        <v>-0.01508477839264799</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.04932569847284896</v>
+        <v>0.03053428534796154</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1500425372755174</v>
+        <v>-0.1686210827672809</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1193131026772036</v>
+        <v>-0.1381579657140364</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2440991247458868</v>
+        <v>-0.2625832238651853</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3190632751963918</v>
+        <v>-0.3374910525602814</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.4762731598147809</v>
+        <v>-0.4945133941070452</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.683886291905722</v>
+        <v>-0.7017622426276802</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.5492846525455235</v>
+        <v>-0.5673131669131095</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.6616948327897774</v>
+        <v>-0.6797411446591326</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7899903474966479</v>
+        <v>-0.8078824931299025</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.9768207743489086</v>
+        <v>-0.9943601479376554</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.8820354446468457</v>
+        <v>-0.8997519422651479</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.004794</t>
+          <t>X &gt; -0.004798</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4642232563843436</v>
+        <v>0.4326353146830471</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.03088828384974107</v>
+        <v>-0.04034624498194006</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5109725943973018</v>
+        <v>-0.4975758145297959</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2427906976744154</v>
+        <v>-0.2289560366329653</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5056515191130302</v>
+        <v>-0.4847784963853528</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.02419620396725009</v>
+        <v>0.0220597408915566</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.315152695891463</v>
+        <v>0.2896952233346681</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2599269424793249</v>
+        <v>0.234418604651168</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5249509207643825</v>
+        <v>0.4990190318639947</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.06529357119870838</v>
+        <v>-0.0906367909918373</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2088808173517975</v>
+        <v>-0.2338913766639195</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1839452682149272</v>
+        <v>-0.2091355481925845</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.281561566846122</v>
+        <v>-0.3071062065907668</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.42262933733452</v>
+        <v>-0.4243848602983746</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1983811303662009</v>
+        <v>-0.1763983721854885</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.5431059125650748</v>
+        <v>-0.5210613356680796</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5731433656791438</v>
+        <v>-0.5510247851168373</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.6945656723786087</v>
+        <v>-0.6960100092110011</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7361491434290386</v>
+        <v>-0.7611302701975475</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4047666934835021</v>
+        <v>-0.4302156115711426</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.6827879341488625</v>
+        <v>-0.7080468329690603</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7348962053813111</v>
+        <v>-0.7601226107147383</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.9195413936074814</v>
+        <v>-0.9443676460661123</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.012082314300386</v>
+        <v>-1.036810813452526</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003263</t>
+          <t>X &gt; -0.003268</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2273</v>
+        <v>2278</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2525801649298245</v>
+        <v>0.2388390243186791</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5188955242345656</v>
+        <v>-0.5085502092087282</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8678455520205333</v>
+        <v>-0.8562945090029217</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5975353506643799</v>
+        <v>-0.6098067491172685</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7638683429604782</v>
+        <v>-0.771153261786651</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3775931173981064</v>
+        <v>-0.4097431158113807</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.0333424213261182</v>
+        <v>-0.09141705046492632</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3689426443841839</v>
+        <v>0.3096716587523858</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4794706338563515</v>
+        <v>0.419965149289574</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.05023774355810673</v>
+        <v>-0.1094116361955102</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.1882802285227001</v>
+        <v>-0.2469083075970318</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.04789888167022838</v>
+        <v>-0.1071541962112335</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.270513907454621</v>
+        <v>-0.3304673144645847</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4042282995582056</v>
+        <v>-0.4383115476901907</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5373050250109301</v>
+        <v>-0.545484329276718</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.7490854642659599</v>
+        <v>-0.7569123812556313</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.5942361740359132</v>
+        <v>-0.6023000462276542</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.7171752955421624</v>
+        <v>-0.7509427649415272</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.7385143838557227</v>
+        <v>-0.7978634733733188</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5256368028107161</v>
+        <v>-0.5852969359924103</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.7354236075919758</v>
+        <v>-0.7952168783189748</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.7414082118933152</v>
+        <v>-0.7574430823117382</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.188157782767057</v>
+        <v>-1.202947893012357</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.28234319484001</v>
+        <v>-1.297021284451851</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001732</t>
+          <t>X &gt; -0.001737</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4452668527593175</v>
+        <v>0.4744806342269783</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.073924448762163</v>
+        <v>-1.017044030124971</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.280275134851266</v>
+        <v>-1.222321461798963</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.078881517022893</v>
+        <v>-1.047701516744667</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.367566655537971</v>
+        <v>-1.334182324597656</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9555203756205373</v>
+        <v>-0.9499774797231524</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4652202320966623</v>
+        <v>-0.4891845462565101</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.07553696302257862</v>
+        <v>0.04985027707346035</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.244449294057226</v>
+        <v>0.2183737036438487</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1048340128130434</v>
+        <v>-0.1310839635446968</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.000144274599577443</v>
+        <v>-0.02603325126126066</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1957037016501815</v>
+        <v>0.1686513131582856</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1614007884157687</v>
+        <v>0.1623192912892577</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.03915200513166184</v>
+        <v>0.06956658060660459</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.3224551506549034</v>
+        <v>-0.2621036936201619</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.3715972814101249</v>
+        <v>-0.2819802782655643</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.3570289339336838</v>
+        <v>-0.2673090051390261</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.5813399878036094</v>
+        <v>-0.5207381190642195</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5838691924458246</v>
+        <v>-0.5524940883132459</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4171836228287873</v>
+        <v>-0.4151777483798895</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6331954437546585</v>
+        <v>-0.660547096137897</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.4809910334433454</v>
+        <v>-0.5088471127048635</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.922163598357244</v>
+        <v>-0.948593886273251</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.118046649858528</v>
+        <v>-1.144118083370415</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002007</t>
+          <t>X &gt; -0.0002069</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.08632427670045928</v>
+        <v>0.08966513601124149</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.418767672484258</v>
+        <v>-1.385094663870916</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.96710323406343</v>
+        <v>-1.931748810394943</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.037930051074632</v>
+        <v>-2.031889459364152</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.703743695191484</v>
+        <v>-1.699156255031198</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.48598515540597</v>
+        <v>-1.512190068933819</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8323549665698238</v>
+        <v>-0.8913810926570349</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8001378763145439</v>
+        <v>-0.859583625003232</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6710912474177064</v>
+        <v>-0.7308315252021202</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.7980140690737016</v>
+        <v>-0.8583491751849124</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4915749911447449</v>
+        <v>-0.5523528157062358</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2346337872653592</v>
+        <v>-0.2963365222650722</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.01534001135160423</v>
+        <v>-0.04567781599179455</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1807057809525929</v>
+        <v>-0.17775267459632</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5036907713896639</v>
+        <v>-0.4669937965084472</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8044873847022203</v>
+        <v>-0.7350945060911442</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.09871545735058618</v>
+        <v>-0.02914602156806012</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2823686392245151</v>
+        <v>-0.2459688082559808</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.5373801184903897</v>
+        <v>-0.5339968002319964</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.3733174425126222</v>
+        <v>-0.4031420316973353</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.2661240902549693</v>
+        <v>-0.3297867438962854</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.0839926347697002</v>
+        <v>-0.1481993848327434</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.6744364779337175</v>
+        <v>-0.737078982684686</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.7733992090963824</v>
+        <v>-0.8359552313909617</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.00133</t>
+          <t>X &gt; 0.001323</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.200859373665232</v>
+        <v>-1.202637360592952</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.939778203817575</v>
+        <v>-2.906105195204233</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.574665833679127</v>
+        <v>-2.53931141001064</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.021079467727894</v>
+        <v>-2.98488575030899</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.481237740223541</v>
+        <v>-2.451692265637007</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.458700421231164</v>
+        <v>-2.465260838897919</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.788912705027691</v>
+        <v>-1.833466207280253</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.494193322867481</v>
+        <v>-1.576918293744555</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.683463224763436</v>
+        <v>-1.765699564604702</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.815911160796297</v>
+        <v>-1.89904469536085</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.839531259139505</v>
+        <v>-1.922267059097038</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.005714715392131</v>
+        <v>-1.091190267378671</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.054937116674971</v>
+        <v>-1.103037438605433</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.007476723408253</v>
+        <v>-1.016678849092955</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.9271606506176013</v>
+        <v>-0.8968575652464068</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.205756514974709</v>
+        <v>-1.136363636363633</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5333985962204082</v>
+        <v>-0.4638291604378821</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3296128227082704</v>
+        <v>-0.2998526599579847</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.8137261643956677</v>
+        <v>-0.8232085908616256</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.3851010101010104</v>
+        <v>-0.4347498776677838</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.01254003163946038</v>
+        <v>-0.1036401316553253</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.3564851287512028</v>
+        <v>0.2641888387821894</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.04304853821238197</v>
+        <v>-0.09378039315852504</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6185335132703571</v>
+        <v>-0.6682282324805726</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002861</t>
+          <t>X &gt; 0.002854</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.74975165785164</v>
+        <v>-2.675271966496616</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.589128853168233</v>
+        <v>-3.513827102377924</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.516224275237555</v>
+        <v>-3.44051113881445</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.977916748094579</v>
+        <v>-3.901575989491455</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.953628186651358</v>
+        <v>-2.893957561954764</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.805542334338142</v>
+        <v>-2.790954432112628</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.438109095258767</v>
+        <v>-2.471383384684763</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.658758468512161</v>
+        <v>-1.74203815437486</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.738986236250071</v>
+        <v>-1.821909339484549</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.790176533551602</v>
+        <v>-1.875344624542109</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.191492942111942</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.155575194036729</v>
+        <v>-1.195650788077671</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9275727523379018</v>
+        <v>-0.9217925776465421</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7262752945641466</v>
+        <v>-0.6717633788695281</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.4553671422236008</v>
+        <v>-0.4016366342559934</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.7056156302184462</v>
+        <v>-0.6014537264537267</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.09013006701049164</v>
+        <v>0.1936831906228633</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.8817315186051076</v>
+        <v>0.9334370813962707</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.9798698368943874</v>
+        <v>0.9804095434016702</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.13347457627119</v>
+        <v>1.082795893910237</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.489772449356586</v>
+        <v>1.384844320538804</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.413817393713977</v>
+        <v>1.360759228198262</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.349321991917904</v>
+        <v>1.348672916126326</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.103745368510332</v>
+        <v>1.155142363116958</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004393</t>
+          <t>X &gt; 0.004384</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.469302128642362</v>
+        <v>-2.436027836323532</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.808493707543711</v>
+        <v>-3.77482069893037</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.641768468818611</v>
+        <v>-3.606414045150125</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.455963388437468</v>
+        <v>-4.419769671018564</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.712799438521756</v>
+        <v>-2.647126408626079</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.471549136023334</v>
+        <v>-2.4601602225287</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.385391780417734</v>
+        <v>-2.428896055013425</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.30671745290374</v>
+        <v>-2.405902680489405</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.80644574353196</v>
+        <v>-1.962809072871885</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.716966971820341</v>
+        <v>-1.876105366857558</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.148964919639418</v>
+        <v>-2.249751052137675</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.159673659673658</v>
+        <v>-1.264116569185695</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.7690133630092859</v>
+        <v>-0.8179262337418507</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2217510380775707</v>
+        <v>0.2307899811171836</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.033139796919329</v>
+        <v>-0.02372062221513715</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.2588899496717474</v>
+        <v>0.3282828282828234</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.7308568615834332</v>
+        <v>0.8004262973659593</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.192510493419441</v>
+        <v>1.20063609859529</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.3691302934484</v>
+        <v>1.315517378509512</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.61790780141844</v>
+        <v>1.502363188477538</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.049345229947278</v>
+        <v>1.868907929602415</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.379069687489256</v>
+        <v>2.259914517957895</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.943905705898359</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.867964366629892</v>
+        <v>1.875343247261128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.005924</t>
+          <t>X &gt; 0.005915</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.251925989586745</v>
+        <v>-3.28027019035504</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.275883168887283</v>
+        <v>-5.297739296397168</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.303038397750257</v>
+        <v>-4.331912191581999</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.258086234465736</v>
+        <v>-5.165058518717053</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.33143804602777</v>
+        <v>-3.337387452802787</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.476161570174774</v>
+        <v>-2.549459728243868</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.732867201262032</v>
+        <v>-1.879100719826532</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.823309383341744</v>
+        <v>-2.037119856887294</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.078073309514359</v>
+        <v>-2.356209598049517</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.813956381360576</v>
+        <v>-2.10033118910961</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.146393230750093</v>
+        <v>-2.361263500320746</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.8997229987509456</v>
+        <v>-1.125632099490105</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3231206570922822</v>
+        <v>-0.489209543699765</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.670589360548945</v>
+        <v>0.569875609084491</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.01165812151164403</v>
+        <v>-0.08826768849606736</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.3637048053979015</v>
+        <v>0.3365984298187712</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.715637842719218</v>
+        <v>0.6869427940519444</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.9274291485037125</v>
+        <v>0.8242328408360962</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.217493354196868</v>
+        <v>1.161189597063085</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.844512195121951</v>
+        <v>1.711231532939102</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.864461373663829</v>
+        <v>1.652946866183726</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.154806684321585</v>
+        <v>2.015284190415535</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.063281484503349</v>
+        <v>2.00085040039685</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.498939656834395</v>
+        <v>1.513900875529465</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007455</t>
+          <t>X &gt; 0.007445</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.514885736960984</v>
+        <v>-3.403129205349551</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.4424179395034</v>
+        <v>-5.164213452193827</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.060462352634119</v>
+        <v>-2.798745971906271</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.570434009776328</v>
+        <v>-4.304093018290374</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.43251908142458</v>
+        <v>-1.15335417229565</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5195242588463813</v>
+        <v>-0.3324735646451913</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2447524170811732</v>
+        <v>-0.1535506162058979</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5923166472642691</v>
+        <v>-0.590240666347249</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.42131340275445</v>
+        <v>-1.499625116762182</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-1.07288290534364</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.991528732316276</v>
+        <v>-1.980088562094075</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.7791365937433312</v>
+        <v>0.8554978014726018</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.42029545551302</v>
+        <v>1.580688521621632</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.483047793756356</v>
+        <v>2.734634485812805</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.8610346927607821</v>
+        <v>0.9582803256124421</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.616608386041875</v>
+        <v>1.712411656501118</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.643028335552664</v>
+        <v>1.738238928469329</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.538044919457384</v>
+        <v>1.633398224648147</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.754168082389199</v>
+        <v>1.849289605572473</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.879019292604497</v>
+        <v>1.876391006594815</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.461220812866998</v>
+        <v>2.45205570124859</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.224494053044324</v>
+        <v>2.315890251021592</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.856182402806191</v>
+        <v>1.950364963503652</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.619469359357659</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.008986</t>
+          <t>X &gt; 0.008976</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.473318192899384</v>
+        <v>-3.240847113431968</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.414919410354962</v>
+        <v>-5.575623911781783</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.039358830264398</v>
+        <v>-3.21364296081277</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.351545717754739</v>
+        <v>-3.526596980255512</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.507980161413329</v>
+        <v>-1.662387452802783</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.3995467862439384</v>
+        <v>0.1245787332945838</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.7491412240607431</v>
+        <v>0.3526300494042403</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9915217365741142</v>
+        <v>0.4744186046511629</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.06335118952907948</v>
+        <v>-0.6840942134341361</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1124656076155262</v>
+        <v>-0.7423806309535834</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.257984636646228</v>
+        <v>-1.758853861766532</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.316876835132419</v>
+        <v>2.099266144011921</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.81510366938361</v>
+        <v>2.508686669483964</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.607945641310721</v>
+        <v>3.624362436243622</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.529136106127368</v>
+        <v>1.350057522501452</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.124196155748749</v>
+        <v>1.944444444444443</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.409980757745878</v>
+        <v>3.224668721608388</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.69647807187372</v>
+        <v>2.513767411726597</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.318280747990109</v>
+        <v>3.133699196691332</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.505324543610541</v>
+        <v>3.320545006659358</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.976322917574052</v>
+        <v>3.788099848794332</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.494688348746855</v>
+        <v>3.308213483344829</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.363784002044412</v>
+        <v>3.178647791786481</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.882163149591356</v>
+        <v>2.698775134522805</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01052</t>
+          <t>X &gt; 0.01051</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.76553539273371</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.009296920395123</v>
+        <v>-6.095324659911455</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.94899738448126</v>
+        <v>-3.044565654079605</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.162790697674417</v>
+        <v>-4.256272790729327</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.528060482698457</v>
+        <v>-1.599544560034701</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4511715589147371</v>
+        <v>-0.6644486981268543</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4239264404653511</v>
+        <v>0.3092385282072385</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.5421921688566442</v>
+        <v>0.2804036420576494</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2249569935159457</v>
+        <v>-0.1768622932346346</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.862705779140839</v>
+        <v>0.4429901105293794</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.647745080326104</v>
+        <v>-1.893225936531756</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.36430025670532</v>
+        <v>1.234782761303606</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.011960936952363</v>
+        <v>2.02420629246275</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.550097796804074</v>
+        <v>2.715271527152723</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.6253437729566542</v>
+        <v>0.7945019669458944</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.726732936502088</v>
+        <v>1.893939393939398</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.352132913239231</v>
+        <v>2.517598014537683</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.740820383219898</v>
+        <v>1.907706805665988</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.21010810311374</v>
+        <v>2.376123439115574</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.143987341772146</v>
+        <v>2.310443996558341</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.119774274546351</v>
+        <v>3.283049343743826</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.043819218903742</v>
+        <v>3.207203382334725</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.799607043613712</v>
+        <v>1.966526579665263</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.217336590421205</v>
+        <v>1.38564382139149</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01205</t>
+          <t>X &gt; 0.01204</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.477979926651116</v>
+        <v>-4.759057976051771</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.385502708176475</v>
+        <v>-7.330256499641209</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.35896523014042</v>
+        <v>-3.336965644518841</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.394301951693706</v>
+        <v>-4.369408481852965</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.830311286556991</v>
+        <v>-2.468777229160615</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.147347482594895</v>
+        <v>-1.962322225171867</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4794577946259579</v>
+        <v>-0.4978491838225949</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.07521582026819829</v>
+        <v>-0.1370829927929265</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.347543253251402</v>
+        <v>-0.734573446660967</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3720960331327348</v>
+        <v>-0.04418937665010247</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-2.47748400936657</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6130307600895861</v>
+        <v>-0.6423448120470141</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7571298217139741</v>
+        <v>-0.6088099376775347</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3248918615065008</v>
+        <v>0.00964382152501031</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.63741787178563</v>
+        <v>-1.297850125406192</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.06196566530150704</v>
+        <v>-0.05411255411255667</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.1960593594504303</v>
+        <v>0.1366456335852959</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.627840161166624</v>
+        <v>-0.2928703949112119</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.5686751586279328</v>
+        <v>0.5723716353637656</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.082516339869279</v>
+        <v>1.408568094682437</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.500100244596815</v>
+        <v>2.489398550093036</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.770550417712379</v>
+        <v>1.439526614657964</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4113386560899315</v>
+        <v>0.4153000284387147</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.9889920880632914</v>
+        <v>0.6641430998907722</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01358</t>
+          <t>X &gt; 0.01357</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>239</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.09078807241746</v>
+        <v>-4.057513780098631</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-6.509296920395123</v>
+        <v>-6.475623911781781</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.69899738448126</v>
+        <v>-1.663642960812773</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.829457364341081</v>
+        <v>-2.793263646922178</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.111393816031793</v>
+        <v>-1.045720786136116</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.75756253635835</v>
+        <v>-1.692087933372079</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.8029046649209661</v>
+        <v>0.8692967160709131</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9410166860690694</v>
+        <v>1.007751937984501</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.8654449337060726</v>
+        <v>-1.03409421343413</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4527698647295253</v>
+        <v>0.2763234438627151</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.783331119201165</v>
+        <v>-1.949616913975362</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.062425022676067</v>
+        <v>-2.228366317423358</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.931686115640197</v>
+        <v>-1.862685985395238</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.316222842992538</v>
+        <v>-1.246944778159815</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.975154082029839</v>
+        <v>-1.905088075740373</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.1248639068854516</v>
+        <v>-0.05547102827437556</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.5778624826476388</v>
+        <v>0.6474319184301649</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.7823510589706544</v>
+        <v>-0.7126389109140305</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.6890022294841742</v>
+        <v>0.7584825955333088</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.712866108786613</v>
+        <v>1.782148489183342</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.006485783470659</v>
+        <v>2.076422404899311</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.930530727828049</v>
+        <v>2.00057644349021</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.5316657269461729</v>
+        <v>0.6014109886082579</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.8741344295187048</v>
+        <v>0.9439887772259823</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01511</t>
+          <t>X &gt; 0.0151</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.384436857021711</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.040224755446673</v>
+        <v>-4.744854681012548</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2943582092235246</v>
+        <v>-0.02902757619738594</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.008151522416682</v>
+        <v>-0.7419815956401266</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.203898280188128</v>
+        <v>1.486330495915169</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.875598975669142</v>
+        <v>1.160476169192023</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.710980266295529</v>
+        <v>3.978271075045271</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.916961703251197</v>
+        <v>3.187239117471677</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6802875006599152</v>
+        <v>0.6646237352838256</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.460856234968212</v>
+        <v>1.430169597708868</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.373592788071889</v>
+        <v>-1.372693837052289</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.170821406572699</v>
+        <v>-2.164263753320796</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.740908479982117</v>
+        <v>-1.45290295472622</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4078611459387602</v>
+        <v>-0.1275900785954818</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.066792384976061</v>
+        <v>-1.301197293701811</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.082671809723045</v>
+        <v>0.839581380818494</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.466712830600024</v>
+        <v>1.221128161366792</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.8435946994788424</v>
+        <v>0.6008235400198387</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.577852577436559</v>
+        <v>1.332178838469936</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.2830310880829</v>
+        <v>2.034488565963741</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.81236953918858</v>
+        <v>3.553798068100797</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.736414483545971</v>
+        <v>3.477952106691696</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.9023813598726562</v>
+        <v>0.6596433140191138</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.8264400206041884</v>
+        <v>0.5838110607958384</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01664</t>
+          <t>X &gt; 0.01663</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.982269893368091</v>
+        <v>-2.642290578448453</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.659110723626846</v>
+        <v>1.919690372520563</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.620993086109365</v>
+        <v>1.87340301974448</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.634101679463697</v>
+        <v>4.870945880530542</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.469914941119136</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.724075836092133</v>
+        <v>4.952630049404242</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.121196866249242</v>
+        <v>5.341085271317837</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.460010228569182</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.0375261691511</v>
+        <v>3.276323443862708</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2578313822123803</v>
+        <v>-0.4496169139753619</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.02126252126252126</v>
+        <v>-0.7283663174233581</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.232624638628721</v>
+        <v>1.48180494905386</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.038294854621384</v>
+        <v>3.26072607260727</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.703687939908413</v>
+        <v>1.93591610836004</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.974423665205464</v>
+        <v>3.196969696969703</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.516005646732225</v>
+        <v>3.729719226658887</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.735346554961261</v>
+        <v>2.958211856171047</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.62714539356876</v>
+        <v>3.84076990376203</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.48986486486487</v>
+        <v>4.694282380396729</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>6.298015807218256</v>
+        <v>5.485069545764027</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.897736427251338</v>
+        <v>6.075890251021598</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.794133215355075</v>
+        <v>3.017031630170322</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.069543227437968</v>
+        <v>4.274532710280376</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01817</t>
+          <t>X &gt; 0.01816</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>123</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.01558482038493736</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.275255925133337</v>
+        <v>1.308928933746678</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.713604241535009</v>
+        <v>4.748958665203496</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.373794668179237</v>
+        <v>2.40998838559814</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.512589923805592</v>
+        <v>8.57826295370127</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.260730146568477</v>
+        <v>6.326204749554748</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.48786401451445</v>
+        <v>5.554256065664397</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.64833375923979</v>
+        <v>7.715069011155222</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.43781730393723</v>
+        <v>4.504523672744732</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.289998153330401</v>
+        <v>5.357624256870842</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.9397076202046719</v>
+        <v>-0.8723811416176446</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4057933935982661</v>
+        <v>-0.3381224149843334</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.721747908239792</v>
+        <v>1.79074803848475</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.939415487449338</v>
+        <v>4.008693552282061</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.280484248412037</v>
+        <v>3.350550254701503</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>3.875544298033418</v>
+        <v>3.944937176644494</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.741450603884495</v>
+        <v>3.811020039667021</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.823459057707908</v>
+        <v>2.893171205764531</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.85259035072103</v>
+        <v>3.922070716770165</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>4.85264227642277</v>
+        <v>4.921924656819499</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>5.122449997506102</v>
+        <v>5.192386618934755</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>4.508261978264336</v>
+        <v>4.578007239926421</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.432320638995868</v>
+        <v>4.502174986703146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.0197</t>
+          <t>X &gt; 0.01969</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.8963436279730175</v>
+        <v>-0.8630693356541883</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6203327092345035</v>
+        <v>0.6540057178478449</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.736187800703924</v>
+        <v>4.771542224372411</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.022394487510766</v>
+        <v>4.05858820492967</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.360828406190421</v>
+        <v>7.426501436086099</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.844289315493505</v>
+        <v>3.909763918479776</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.071423183439478</v>
+        <v>3.137815234589425</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.644720389772772</v>
+        <v>4.711455641688204</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.9825327510917035</v>
+        <v>1.049239119899205</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.986475118100053</v>
+        <v>3.054101221640494</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.647889147889153</v>
+        <v>-1.58021816927522</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.783175189179268</v>
+        <v>2.852175319424227</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.413670229996761</v>
+        <v>4.482948294829484</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>3.75473899095946</v>
+        <v>3.824804997248926</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.275724966506765</v>
+        <v>5.345117845117841</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.215705346431918</v>
+        <v>4.285274782214444</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.184796004410714</v>
+        <v>3.254508152467338</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.326845093268453</v>
+        <v>4.396325459317588</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.513888888888886</v>
+        <v>4.583171269285614</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>4.896614405816855</v>
+        <v>4.966551027245508</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.095434516656375</v>
+        <v>5.165179778318461</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.945419103313846</v>
+        <v>6.015273451021123</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.02123</t>
+          <t>X &gt; 0.02122</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4132518405333983</v>
+        <v>-0.3799775482145691</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.599398731778791</v>
+        <v>3.633071740392133</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.59448087638831</v>
+        <v>7.629835300056797</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.793731041456013</v>
+        <v>5.829924758874917</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.528669347699633</v>
+        <v>4.594143950685904</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.755803215645606</v>
+        <v>3.822195266795553</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.564205091866164</v>
+        <v>4.630940343781596</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2578950699322817</v>
+        <v>0.3246014387397835</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.657972702641111</v>
+        <v>1.725598806181551</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.415494117200069</v>
+        <v>-2.348167638613042</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.5662815445424201</v>
+        <v>0.6339525231563528</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.876572934750918</v>
+        <v>4.945573064995877</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.829129167194829</v>
+        <v>6.898407232027552</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.170197928157528</v>
+        <v>6.240263934446993</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.852214499518048</v>
+        <v>7.921607378129124</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>6.631164283629985</v>
+        <v>6.700733719412511</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.43922434579558</v>
+        <v>5.508936493852204</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.655347508727395</v>
+        <v>5.72482787477653</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.755434782608688</v>
+        <v>4.824717163005417</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>6.386147417088999</v>
+        <v>6.456084038517652</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>8.484105404924655</v>
+        <v>8.554151120586816</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>6.584967527928519</v>
+        <v>6.654712789590604</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>6.509026188660052</v>
+        <v>6.578880536367329</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02277</t>
+          <t>X &gt; 0.02275</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.847617724683985</v>
+        <v>2.880892017002814</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>8.309543659315018</v>
+        <v>8.34321666792836</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>14.11622000682308</v>
+        <v>14.15157443049157</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>11.9531513313111</v>
+        <v>11.98934504873</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>14.48643227092472</v>
+        <v>14.5521053008204</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.87649543465615</v>
+        <v>8.94197003764242</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9.274350019402391</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.968039997468509</v>
+        <v>5.034746366276011</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.092755311336767</v>
+        <v>7.160381414877207</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.570013129176736</v>
+        <v>1.637339607763764</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.189469950339515</v>
+        <v>4.257140928953447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>5.963529456490058</v>
+        <v>6.032529586735016</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>8.64072337009339</v>
+        <v>8.710001434926113</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>8.57685218067747</v>
+        <v>8.646245059288546</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.34130921116622</v>
+        <v>11.41087864694875</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.787050432752096</v>
+        <v>9.85676258080872</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>10.00317359568391</v>
+        <v>10.07265396173305</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>8.740942028985515</v>
+        <v>8.810224409382243</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>9.64701698230639</v>
+        <v>9.716953603735043</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>11.02033728898262</v>
+        <v>11.09038300464479</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>8.396561730827081</v>
+        <v>8.466306992489166</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>9.769895753877442</v>
+        <v>9.83975010158472</v>
       </c>
     </row>
   </sheetData>
@@ -5824,165 +5824,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02164</t>
+          <t>X &lt; -0.02163</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.297309811547898</v>
+        <v>-7.264035519229068</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.173635065640674</v>
+        <v>-6.138280641972187</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.336703741152675</v>
+        <v>-8.300510023733771</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.904872076901356</v>
+        <v>-2.839199047005678</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8572524910079196</v>
+        <v>0.9236445421578665</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.319852879148321</v>
+        <v>-2.253117627232889</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.176887538763374</v>
+        <v>-5.110181169955872</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-5.950722949532803</v>
+        <v>-5.883096845992362</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.676363682417467</v>
+        <v>-5.609037203830439</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.506182223573518</v>
+        <v>-4.438511244959585</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1664280072146909</v>
+        <v>0.2354281374596496</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.394346558499187</v>
+        <v>1.46362462333191</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.735415319461886</v>
+        <v>0.8054813257513516</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.330475369083267</v>
+        <v>1.399868247694343</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2528936873845069</v>
+        <v>-0.1833242516019808</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.756796784089708</v>
+        <v>2.826277150138843</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>2.943840579710141</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.84583709314591</v>
+        <v>9.915582354807995</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>9.769895753877442</v>
+        <v>9.83975010158472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02011</t>
+          <t>X &lt; -0.0201</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>98</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.735345895546715</v>
+        <v>-6.702071603227886</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.428589221215951</v>
+        <v>-4.393234797547464</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.08115804461319</v>
+        <v>-2.044964327194286</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.6760211499546</v>
+        <v>3.741694179850278</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.924410252757305</v>
+        <v>6.989884855743576</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.171952283968587</v>
+        <v>7.238344335118533</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.872989475184717</v>
+        <v>5.939724727100149</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.894097376942042</v>
+        <v>4.960803745749544</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.099853802907305</v>
+        <v>3.167479906447745</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.333396743492031</v>
+        <v>1.400723222079058</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.074711003282438</v>
+        <v>2.142381981896371</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.970627948060596</v>
+        <v>2.039628078305554</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.830903790087469</v>
+        <v>5.900181854920191</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>5.171972551050168</v>
+        <v>5.242038557339633</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.767032600671548</v>
+        <v>5.836425479282624</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>2.571714416726707</v>
+        <v>2.641283852509233</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.446322837366118</v>
+        <v>1.516034985422742</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>1.662446000297933</v>
+        <v>1.731926366347068</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.849489795918366</v>
+        <v>1.918772176315095</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.367513876716338</v>
+        <v>4.43745049814499</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>5.31196698433903</v>
+        <v>5.382012700001191</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>7.627558477351762</v>
+        <v>7.697303739013847</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>7.551617138083294</v>
+        <v>7.621471485790572</v>
       </c>
     </row>
     <row r="8">
@@ -5992,79 +5992,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.512831083170155</v>
+        <v>-8.840847113431963</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-6.428651759104795</v>
+        <v>-5.975623911781781</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.013642960812774</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.743435858964745</v>
+        <v>-3.326596980255509</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.07644757947264935</v>
+        <v>0.3376125471972102</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.142975098050258</v>
+        <v>4.524578733294589</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.595915417609135</v>
+        <v>6.952630049404242</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.704457546284118</v>
+        <v>5.074418604651164</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.326618772597079</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7463317489244261</v>
+        <v>1.142990110529375</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2142394031365384</v>
+        <v>0.617049752691301</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.677757726144812</v>
+        <v>-1.261699650756697</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.189345718825507</v>
+        <v>-0.784861717612813</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.008652308849811</v>
+        <v>1.394059405940595</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.156172682715734</v>
+        <v>1.535916108360041</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.9447811194338911</v>
+        <v>1.330303030303028</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.8022158005214806</v>
+        <v>-0.4036141066744463</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-1.713650829519985</v>
+        <v>-1.308454810495626</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-3.110430892394618</v>
+        <v>-2.692563429571301</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.310483870967737</v>
+        <v>-0.9057176196032728</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.5656705587439816</v>
+        <v>0.9517362124306956</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.296167116004597</v>
+        <v>1.675890251021599</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.570942282486726</v>
+        <v>1.950364963503652</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.495000943218258</v>
+        <v>1.874532710280377</v>
       </c>
     </row>
     <row r="9">
@@ -6077,76 +6077,76 @@
         <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-7.098778939997374</v>
+        <v>-7.065504647678544</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.4339544546417</v>
+        <v>-7.400281446028359</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.394202863933316</v>
+        <v>-3.358848440264829</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.73813316342784</v>
+        <v>-2.701939446008936</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.048608427903943</v>
+        <v>-0.9829353980082658</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.248145226198737</v>
+        <v>3.313619829185008</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.899936628391281</v>
+        <v>5.966328679541228</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.93645047602341</v>
+        <v>5.003185727938842</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.238240513648783</v>
+        <v>2.304946882456285</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.149336609728664</v>
+        <v>2.216962713269105</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.738764369994691</v>
+        <v>1.806090848581718</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.08980745282115521</v>
+        <v>0.1574784314350879</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.020110754881955</v>
+        <v>1.089110885126914</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.853548464395551</v>
+        <v>2.922826529228274</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.509685718508933</v>
+        <v>1.579751724798399</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.104745768130314</v>
+        <v>2.17413864674139</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6007890602827572</v>
+        <v>0.6703584960652833</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.4958056441874774</v>
+        <v>0.5655177922441013</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.02699730026998282</v>
+        <v>0.09647766631911736</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.583904109589042</v>
+        <v>1.653186489985771</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.780429727988349</v>
+        <v>3.850366349417001</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.704474672345739</v>
+        <v>3.7745203880079</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.664181345677186</v>
+        <v>4.733926607339271</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.588240006408718</v>
+        <v>4.658094354115995</v>
       </c>
     </row>
     <row r="10">
@@ -6159,76 +6159,76 @@
         <v>181</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.160309251054663</v>
+        <v>-6.127034958735834</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.047970953544294</v>
+        <v>-7.014297944930952</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.277726666249215</v>
+        <v>-6.242372242580728</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.886547603751758</v>
+        <v>-5.850353886332854</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.831927886013375</v>
+        <v>-1.766254856117698</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.327612417601145</v>
+        <v>3.393087020587416</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.31717722477363</v>
+        <v>5.383569275923577</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.276191640028557</v>
+        <v>2.342926891943989</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1077629536699689</v>
+        <v>0.1744693224774707</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4388999185911402</v>
+        <v>0.506526022131581</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.16077299786118</v>
+        <v>0.2280994764482074</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6708070934590253</v>
+        <v>-0.6031361148450927</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6903259362555687</v>
+        <v>-0.6213258060106099</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7457758162459953</v>
+        <v>0.8150538810787182</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.4656416106366024</v>
+        <v>-0.3955756043471368</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.1294184389847786</v>
+        <v>0.1988113175958546</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.5571614430094485</v>
+        <v>-0.4875920072269224</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.9953137044311759</v>
+        <v>1.0650258524878</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.763923055208295</v>
+        <v>1.833403421257429</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.503453038674031</v>
+        <v>2.57273541907076</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.170197381057299</v>
+        <v>4.240134002485952</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.09424232541469</v>
+        <v>4.164288041076851</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>6.026476055432731</v>
+        <v>6.096221317094816</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.740589964783048</v>
+        <v>3.810444312490326</v>
       </c>
     </row>
     <row r="11">
@@ -6241,76 +6241,76 @@
         <v>242</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.566683389221872</v>
+        <v>-6.533409096903043</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.248966341882728</v>
+        <v>-5.215293333269386</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.275443665472991</v>
+        <v>-6.240089241804505</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.989236978666149</v>
+        <v>-6.953043261247245</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.222275358731522</v>
+        <v>-3.156602328835845</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2706743782422052</v>
+        <v>0.3361489812284759</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.630039651146852</v>
+        <v>3.696431702296799</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.285369303148961</v>
+        <v>1.352104555064393</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.08721594668398325</v>
+        <v>0.1539223154914851</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9662730978980321</v>
+        <v>1.033899201438473</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4141860840216225</v>
+        <v>0.4815125626086498</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.104577240940877</v>
+        <v>-1.036906262326944</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.402622178436289</v>
+        <v>-1.33362204819133</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4421367130087006</v>
+        <v>0.5114147778414235</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.6300176665244663</v>
+        <v>-0.5599516602350008</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.4481807573989514</v>
+        <v>-0.3787878787878753</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.9954975920437406</v>
+        <v>-0.9259281562612145</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.378857834836175</v>
+        <v>1.448569982892799</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.421427278759737</v>
+        <v>2.490907644808871</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.608471074380169</v>
+        <v>2.677753454776898</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.544609508357418</v>
+        <v>4.614546129786071</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.295100733706555</v>
+        <v>5.365146449368716</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>6.809545321676275</v>
+        <v>6.87929058333836</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.66748827992847</v>
+        <v>4.737342627635748</v>
       </c>
     </row>
     <row r="12">
@@ -6323,76 +6323,76 @@
         <v>301</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.508008448940167</v>
+        <v>-3.474734156621338</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.514280309099441</v>
+        <v>-2.480607300486099</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.950658514049366</v>
+        <v>-4.915304090380879</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.335548172757477</v>
+        <v>-4.299354455338573</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.707462476053948</v>
+        <v>-2.64178944615827</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.134187186786725</v>
+        <v>1.199661789772996</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.683580190945321</v>
+        <v>3.749972242095268</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.411670063699184</v>
+        <v>1.478405315614616</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7887343014793018</v>
+        <v>0.8554406702868036</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.011576631573654</v>
+        <v>1.079202735114094</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.04296775579605594</v>
+        <v>0.0243587227909714</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.650965313756004</v>
+        <v>-1.583294335142071</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.003457861549926</v>
+        <v>-0.9341797967172027</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.662389100587227</v>
+        <v>-1.592323094297761</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.067329050965846</v>
+        <v>-0.9979361723547697</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.8691968314935181</v>
+        <v>-0.7996273957109921</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.019175234138778</v>
+        <v>1.088887382195402</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.567524310691859</v>
+        <v>1.637004676740993</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.754568106312291</v>
+        <v>1.82385048670902</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.536949092663178</v>
+        <v>3.606885714091831</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.45767177788435</v>
+        <v>4.527717493546511</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>5.729124685230268</v>
+        <v>5.798869946892353</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.659827864234231</v>
+        <v>3.729682211941508</v>
       </c>
     </row>
     <row r="13">
@@ -6405,1880 +6405,1880 @@
         <v>377</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.337251379225599</v>
+        <v>-4.30397708690677</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.550410978750563</v>
+        <v>-2.516737970137221</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.255363432226616</v>
+        <v>-4.220009008558129</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.438652766639933</v>
+        <v>-4.402459049221029</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.212410615324458</v>
+        <v>-3.146737585428781</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.229490034147908</v>
+        <v>-2.164015431161637</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4459196958670262</v>
+        <v>0.5123117470169731</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.09788693904145163</v>
+        <v>-0.03115168712601957</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.117378831578506</v>
+        <v>-1.050672462771004</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.0344503166184893</v>
+        <v>0.03317578692195156</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.351602985842675</v>
+        <v>-1.284276507255647</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.8959488787075</v>
+        <v>-1.828277900093568</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.489936118414803</v>
+        <v>-2.420935988169845</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.650284971889469</v>
+        <v>-1.581006907056747</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.839720189706611</v>
+        <v>-2.769654183417146</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.979408150695313</v>
+        <v>-1.910015272084237</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.113501844844237</v>
+        <v>-2.043932409061711</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.8922253139899112</v>
+        <v>-0.8225131659332874</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1455981722782624</v>
+        <v>-0.07611780622912789</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2238063660477394</v>
+        <v>-0.1545239856510108</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.089757150683745</v>
+        <v>1.159693772112398</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.870566020770582</v>
+        <v>2.940611736432743</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.941097155422462</v>
+        <v>4.010842417084547</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.273643879814479</v>
+        <v>2.343498227521756</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.009387</t>
+          <t>X &lt; -0.009389</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.233372965002353</v>
+        <v>-5.099180446765303</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.073745984844187</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.058144993628865</v>
+        <v>-2.913642960812773</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.395638930522651</v>
+        <v>-4.251596980255506</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.513507468145455</v>
+        <v>-3.337387452802787</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.702642231438034</v>
+        <v>-2.525421266705408</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.396506284489988</v>
+        <v>-1.214036617262423</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.882961137908758</v>
+        <v>-1.700581395348834</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.088846320287374</v>
+        <v>-2.909094213434138</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.159979028354094</v>
+        <v>-0.973676556137292</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.6777195533385552</v>
+        <v>-0.4912835806420333</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9568134568134568</v>
+        <v>-0.7700329840900295</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.665504259500182</v>
+        <v>-1.476528384279483</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.431559615233077</v>
+        <v>-0.2392739273927376</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.6746904384699661</v>
+        <v>-0.4807505583066245</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1282698190516172</v>
+        <v>0.3219696969696955</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.005823875097306086</v>
+        <v>0.1880525599922223</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.136593956208664</v>
+        <v>1.333211856171047</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.560617327040696</v>
+        <v>1.757436570428709</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.1239604989605</v>
+        <v>1.319282380396722</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.036061545264005</v>
+        <v>2.235069545764034</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.41540794492284</v>
+        <v>3.617556917688262</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.521783943005808</v>
+        <v>4.725364963503651</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.36684052473526</v>
+        <v>2.56619937694704</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.007856</t>
+          <t>X &lt; -0.007859</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.011959243588635</v>
+        <v>-4.063858957763607</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.644432055530253</v>
+        <v>-1.522155214658262</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.901700087183954</v>
+        <v>-1.775741099560662</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.629006913890635</v>
+        <v>-3.503923545399346</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.13616859080657</v>
+        <v>-1.978461902887382</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.455760734556549</v>
+        <v>-2.299109929987978</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.708356596340302</v>
+        <v>-1.548215974284425</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.986911241858863</v>
+        <v>-1.8264274190375</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.621070852511906</v>
+        <v>-2.461759188053421</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3543657227407877</v>
+        <v>-0.1889895849020959</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.08891246329346103</v>
+        <v>0.2542747949924902</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1476563976564051</v>
+        <v>0.3139348670097988</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1322402262361493</v>
+        <v>0.03679648881697517</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3220786384051806</v>
+        <v>0.4925365633010088</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.0009852372057039815</v>
+        <v>0.1728027411857553</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.7649642057460113</v>
+        <v>0.9363944008614098</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.9687083494349267</v>
+        <v>1.140886739349241</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.201562771177478</v>
+        <v>1.374455510993378</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.755523771947132</v>
+        <v>1.928756367383009</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.097972972972968</v>
+        <v>1.269578488687763</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.412880672083134</v>
+        <v>2.588284435780949</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.012601292116194</v>
+        <v>3.189257425302472</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.794133215355075</v>
+        <v>3.9713463509825</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.87359728149201</v>
+        <v>3.049490409095945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006325</t>
+          <t>X &lt; -0.006329</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>728</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.987308218937613</v>
+        <v>-2.886388951566396</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.262044173142371</v>
+        <v>-1.163552581191929</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.053392988876865</v>
+        <v>-0.9554810952434991</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.31663685152057</v>
+        <v>-2.217131959679385</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4841044387424205</v>
+        <v>-0.4953092635023779</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.39584092463673</v>
+        <v>-1.330366321650459</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.619256507240209</v>
+        <v>-1.552864456090262</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.035173790121405</v>
+        <v>-1.968438538205973</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.680470911911968</v>
+        <v>-2.613764543104466</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.7070535754286453</v>
+        <v>-0.6394274718882045</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4326943083133088</v>
+        <v>-0.3653678297262815</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2997002997002909</v>
+        <v>-0.2320293210863582</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4626530566489748</v>
+        <v>-0.3936529264040161</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2775285938551235</v>
+        <v>0.3468066586878464</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.16804790426837</v>
+        <v>0.2381139105578356</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.6257453165271158</v>
+        <v>0.6951381951381919</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.903739534466105</v>
+        <v>0.9733089702486311</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.485569305184022</v>
+        <v>1.555281453240646</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.251143017566385</v>
+        <v>2.320623383615519</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.751373626373635</v>
+        <v>1.820656006770363</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.169711678914133</v>
+        <v>2.239648300342786</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.643207172722072</v>
+        <v>2.713252888384233</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.330070251292113</v>
+        <v>3.399815512954198</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.979403637298368</v>
+        <v>3.049257985005646</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.004794</t>
+          <t>X &lt; -0.004798</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>933</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.272840722719849</v>
+        <v>-1.188821527078019</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.05053213943393331</v>
+        <v>0.07554879610734844</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.235494594128369</v>
+        <v>1.196165141532646</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4147494092774551</v>
+        <v>0.3766013139875568</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.118998340830942</v>
+        <v>1.06162535402752</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2981151210285802</v>
+        <v>-0.2925152837994247</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.070981253082607</v>
+        <v>-1.00458920193266</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9217284119701503</v>
+        <v>-0.8549931600547183</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.628875448551788</v>
+        <v>-1.562169079744287</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.04976968285063776</v>
+        <v>0.01785642068980309</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.331541455922455</v>
+        <v>0.3988679345094823</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2663512957630658</v>
+        <v>0.3340222743769985</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5322344088267243</v>
+        <v>0.6012345390716831</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9102203132706137</v>
+        <v>0.9149150209138526</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.3160108737747507</v>
+        <v>0.2567717233332942</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.232614331756267</v>
+        <v>1.172014260249554</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.312882909847431</v>
+        <v>1.252000866587586</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.636624038232313</v>
+        <v>1.640581592073964</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.745566065044095</v>
+        <v>1.815046431093229</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.8607984994640958</v>
+        <v>0.9300808798608244</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.603771723906661</v>
+        <v>1.673708345335314</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.742178940504139</v>
+        <v>1.8122246561663</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.231316379226342</v>
+        <v>2.301061640888427</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.47691844831801</v>
+        <v>2.546772796025287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003263</t>
+          <t>X &lt; -0.003268</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5327601492062897</v>
+        <v>-0.5049586116898084</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.012537140740243</v>
+        <v>0.989532882643303</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.631422195938327</v>
+        <v>1.604665670399086</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.005041470157749</v>
+        <v>1.028725881873626</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.339072384434402</v>
+        <v>1.354206433660096</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5646985359027283</v>
+        <v>0.6301731388889991</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.120755008738719</v>
+        <v>-0.004500309300922822</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9237851787327997</v>
+        <v>-0.8076461372560999</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.144506875947926</v>
+        <v>-1.028626146942443</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.08267795105302156</v>
+        <v>0.03572851822841727</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.191681316062315</v>
+        <v>0.3097881603903403</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.08741258741258662</v>
+        <v>0.03103875694234404</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3615227675268429</v>
+        <v>0.4826798396925227</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6297682177482926</v>
+        <v>0.6990462825810155</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.899125058287737</v>
+        <v>0.9157936236706306</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.31905375939774</v>
+        <v>1.335202417879579</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.009828716737424</v>
+        <v>1.026307153168084</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.255107997664915</v>
+        <v>1.324820145721539</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.296099812085352</v>
+        <v>1.418917727308632</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.8701838879159283</v>
+        <v>0.992266604761312</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.290205895730594</v>
+        <v>1.413787045033672</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.301816514343678</v>
+        <v>1.337941083624571</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.189551400615649</v>
+        <v>2.225912728621971</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.376307084114259</v>
+        <v>2.413007732190977</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001732</t>
+          <t>X &lt; -0.001737</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.6620732129797062</v>
+        <v>-0.7038336668643836</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.522617973221898</v>
+        <v>1.438388827071719</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.754693176200071</v>
+        <v>1.668510013691481</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.395761466981369</v>
+        <v>1.350369710035061</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.811187210701114</v>
+        <v>1.764562901807146</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.217656294964108</v>
+        <v>1.212158577155485</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5157624837049752</v>
+        <v>0.5520618675860618</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2595984073778155</v>
+        <v>-0.2233086680761076</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5019716255347433</v>
+        <v>-0.4659123952523103</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.001694738003848784</v>
+        <v>0.03958101962028593</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1497799196501646</v>
+        <v>-0.1124957018541579</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4288738231250662</v>
+        <v>-0.3912451053021542</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3760209387668638</v>
+        <v>-0.3780435357946317</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.2001653539880763</v>
+        <v>-0.2440087758775817</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.3210421362099751</v>
+        <v>0.2342115629055002</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.3897357744677592</v>
+        <v>0.2604166666666643</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3695515002780709</v>
+        <v>0.2400248414421213</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.6919185115332169</v>
+        <v>0.6044897129752087</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6943664607898228</v>
+        <v>0.6497853248770937</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.4540598290598297</v>
+        <v>0.4521171382314861</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.765560274762727</v>
+        <v>0.8074739173487302</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.5471550766699806</v>
+        <v>0.5890762809574497</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.178055599277457</v>
+        <v>1.219930180894963</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.45823961613435</v>
+        <v>1.500477115127133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002007</t>
+          <t>X &lt; -0.0002069</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1636</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1135614544422126</v>
+        <v>-0.1171533102727906</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.532725004087219</v>
+        <v>1.492176817258311</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.076901457688152</v>
+        <v>2.033165549825533</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.094369570454774</v>
+        <v>2.085081851861275</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.729099785430726</v>
+        <v>1.723857221573354</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.489695233294306</v>
+        <v>1.519950231467554</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.7777675534035993</v>
+        <v>0.8441596045535462</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7429667165382909</v>
+        <v>0.809701968453723</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6016674250709855</v>
+        <v>0.6683737938784873</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7419087967512823</v>
+        <v>0.8095349002917231</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4068835422334658</v>
+        <v>0.4742100208204931</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.1277896387585642</v>
+        <v>0.1954606173724969</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1075203844431414</v>
+        <v>-0.07456311919720804</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.07328652719694873</v>
+        <v>0.0699887173360878</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.4275106637311339</v>
+        <v>0.3868606543685758</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.7541294552961091</v>
+        <v>0.676555315494987</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.01548183096552691</v>
+        <v>-0.09141898472322652</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1851582248218335</v>
+        <v>0.1451144390467789</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.4624060821301725</v>
+        <v>0.4585965215886532</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.2827017114914412</v>
+        <v>0.3155407799080265</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.167374163129189</v>
+        <v>0.2373107845578417</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.03083028126648202</v>
+        <v>0.03921543439567898</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.6106930514748186</v>
+        <v>0.6804383131369036</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.7181257953359292</v>
+        <v>0.7879801430432067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.00133</t>
+          <t>X &lt; 0.001323</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9087828167002812</v>
+        <v>0.9092814212724036</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.250363048692968</v>
+        <v>2.219748838860887</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.922136636137296</v>
+        <v>1.890883788158426</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.217817863439564</v>
+        <v>2.185291851448035</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.80097510265481</v>
+        <v>1.776541486435114</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.781847812618793</v>
+        <v>1.78743293216116</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.266846559368275</v>
+        <v>1.303145513321773</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.039864889610406</v>
+        <v>1.106600141525838</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.184526906154453</v>
+        <v>1.251233274961955</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.287432083316943</v>
+        <v>1.355058186857384</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.303926471628778</v>
+        <v>1.371252950215805</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.663821737828961</v>
+        <v>0.7314927164428937</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.7048584823795849</v>
+        <v>0.7429361163222055</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.669334774251908</v>
+        <v>0.6765761671577195</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6096517549631315</v>
+        <v>0.5857356029448724</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.8226672576351035</v>
+        <v>0.7675387188022569</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.306133934275195</v>
+        <v>0.2519070491563085</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1494442100103157</v>
+        <v>0.1263412659111935</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5206862974509221</v>
+        <v>0.5280977274534919</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.190667011375389</v>
+        <v>0.2291661013269604</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.09400185677458239</v>
+        <v>-0.02406523534592964</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.3767821450955751</v>
+        <v>-0.3067364294334141</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.07116508863955318</v>
+        <v>-0.0322617169513606</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3702241463289226</v>
+        <v>0.4089691115213299</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002861</t>
+          <t>X &lt; 0.002854</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.441536957238533</v>
+        <v>1.401356351694652</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.887454303458902</v>
+        <v>1.846598310440434</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.808349009107346</v>
+        <v>1.767326358884866</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.010928678717569</v>
+        <v>1.96948842899716</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.467485174317126</v>
+        <v>1.437033998020532</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.387389208259322</v>
+        <v>1.382637504443302</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.193587664178573</v>
+        <v>1.215436285484422</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7814027291277199</v>
+        <v>0.8294988185549101</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.822918794150354</v>
+        <v>0.8709860004696139</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.8508651205746887</v>
+        <v>0.9002093618662812</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.062379245583777</v>
+        <v>1.085142444313398</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5159056629644851</v>
+        <v>0.5390133617210324</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.3983896010945287</v>
+        <v>0.3962434517276563</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2928455694754106</v>
+        <v>0.2642911349958581</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.1514368936814634</v>
+        <v>0.1231653281549541</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2823387231205245</v>
+        <v>0.2271376268255523</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1376766197236066</v>
+        <v>-0.1923741423568686</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.5552996070560496</v>
+        <v>-0.58306435980397</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.6071532194703693</v>
+        <v>-0.6086348581427288</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6880861991960714</v>
+        <v>-0.6634666146903641</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.8739842410658341</v>
+        <v>-0.822347791143919</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.8341912108425262</v>
+        <v>-0.8088282476379263</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.8011862883238337</v>
+        <v>-0.8024500499011822</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6718869325968413</v>
+        <v>-0.6995512932942418</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004393</t>
+          <t>X &lt; 0.004384</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9941832625538751</v>
+        <v>0.9789402945811219</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.541706766618397</v>
+        <v>1.525398583105748</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.436248517158091</v>
+        <v>1.419417595652035</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.729788228114842</v>
+        <v>1.712125901447308</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.019109328622292</v>
+        <v>0.9905200001046666</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9191533509810057</v>
+        <v>0.9142550954412485</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.8845973091648816</v>
+        <v>0.9034497215353881</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.85214602705895</v>
+        <v>0.8950008104732206</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6475587286689546</v>
+        <v>0.7142650974764564</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6120334081374139</v>
+        <v>0.6796595116778548</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.7873925395946273</v>
+        <v>0.8306674721334701</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3851964613146421</v>
+        <v>0.428866386979152</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.228896772831888</v>
+        <v>0.2491005465381306</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1733706096108136</v>
+        <v>-0.1770644660856533</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.06841448297462449</v>
+        <v>-0.07229070329362486</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.1884938762570769</v>
+        <v>-0.2165168301811775</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.3804203845622354</v>
+        <v>-0.4082118078238679</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.5676406427627825</v>
+        <v>-0.5708778084422335</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.6393464271993849</v>
+        <v>-0.6182824106723643</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.7401315789473699</v>
+        <v>-0.6949490211651295</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.9132661984716393</v>
+        <v>-0.8433295770429865</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.047220047116916</v>
+        <v>-1.001412380557355</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8716436726440335</v>
+        <v>-0.8502929312331986</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.841019455459012</v>
+        <v>-0.8438883423512067</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.005924</t>
+          <t>X &lt; 0.005915</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2596</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.021164144268369</v>
+        <v>1.033482388483741</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.665549705371753</v>
+        <v>1.677883179057623</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.321236600942598</v>
+        <v>1.334823296855944</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.588552356815221</v>
+        <v>1.564235394121162</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9767379817928941</v>
+        <v>0.9819717183407235</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7032500036288596</v>
+        <v>0.7303368906842209</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4678118946074576</v>
+        <v>0.5179142275916462</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4963589765361149</v>
+        <v>0.569155446756433</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5762627574896584</v>
+        <v>0.6713246950977663</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4934062334764562</v>
+        <v>0.5901845763249156</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5982639807094969</v>
+        <v>0.6720843414691657</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2039627039627092</v>
+        <v>0.2780390118105629</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.02389458702505465</v>
+        <v>0.0772443546393049</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2899765374470746</v>
+        <v>-0.2591304480178991</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.08032444618009293</v>
+        <v>-0.04870519114015082</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1929360021541981</v>
+        <v>-0.184806542938027</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.3041954701214493</v>
+        <v>-0.2959217989821354</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.3707025491640223</v>
+        <v>-0.3394667381601053</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.4623900826539042</v>
+        <v>-0.4471438760686013</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6601096575606036</v>
+        <v>-0.6226217397418878</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.6646413478205773</v>
+        <v>-0.6032714917295507</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.7562801759569595</v>
+        <v>-0.7176382543713231</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.7282366708962158</v>
+        <v>-0.7128091505179199</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.5503293415871511</v>
+        <v>-0.5575165963451951</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007455</t>
+          <t>X &lt; 0.007445</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2793</v>
+        <v>2795</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.774277170761664</v>
+        <v>0.7526071732987347</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.206082218088319</v>
+        <v>1.148931248360569</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6407462052623316</v>
+        <v>0.5849330448832077</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9444412225250787</v>
+        <v>0.8890725354140088</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2431440789551331</v>
+        <v>0.1817165728473711</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0382915857609305</v>
+        <v>-0.003147567489435232</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.02181617138219138</v>
+        <v>-0.04202235701286838</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.05600837055469299</v>
+        <v>0.0567295889592927</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2400761105595066</v>
+        <v>0.2613927648034746</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.1433611559554393</v>
+        <v>0.1663222546606704</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3671920798083761</v>
+        <v>0.369029774096937</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2477729118242635</v>
+        <v>-0.2664802429793198</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3883605991956287</v>
+        <v>-0.4263886530391403</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6243978166365878</v>
+        <v>-0.6831435908485517</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.2626754245270746</v>
+        <v>-0.2853544126963428</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4319469911651836</v>
+        <v>-0.4550593402789005</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4377423134466056</v>
+        <v>-0.4607569638173032</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4143356504750528</v>
+        <v>-0.4372865361119125</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.4630091156061269</v>
+        <v>-0.4861302630237674</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4904808723632428</v>
+        <v>-0.4927036760923684</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.619201839613126</v>
+        <v>-0.6207959764105055</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5666062696495047</v>
+        <v>-0.5893458004805439</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4853072845578623</v>
+        <v>-0.5083112440097608</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.4326291920276901</v>
+        <v>-0.4768089712938632</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.008986</t>
+          <t>X &lt; 0.008976</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2922</v>
+        <v>2924</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5775792745213124</v>
+        <v>0.5399822543450483</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.9073413919560167</v>
+        <v>0.9376708859060798</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4733988034016576</v>
+        <v>0.5047243861260071</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4936614643957213</v>
+        <v>0.5253254423372056</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1817487816067143</v>
+        <v>0.2088174484906062</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1419857879478101</v>
+        <v>-0.09564598580652728</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1995930644160069</v>
+        <v>-0.1332010132660599</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2397280914059579</v>
+        <v>-0.1535200665583787</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.06197224436697013</v>
+        <v>0.04378581383240032</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.0524289085423959</v>
+        <v>0.05478288489884164</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1395018090276139</v>
+        <v>0.2265930383082093</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4606589729289112</v>
+        <v>-0.427071157232497</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.5426446640868861</v>
+        <v>-0.4936551736455357</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6757643614842053</v>
+        <v>-0.6806508871746075</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.3252109692361458</v>
+        <v>-0.2959284194272129</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.4264618619599219</v>
+        <v>-0.3973913762454018</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.6427977452565585</v>
+        <v>-0.613508340724259</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5227024776779245</v>
+        <v>-0.493437745649203</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.6279816159142513</v>
+        <v>-0.5987430130468852</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.6600307587149672</v>
+        <v>-0.6308542316251362</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.738713229510779</v>
+        <v>-0.7092135654989207</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.6576301568430267</v>
+        <v>-0.6281425582743694</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.63624653148036</v>
+        <v>-0.60689999376131</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5550752308560618</v>
+        <v>-0.5257408875308442</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01052</t>
+          <t>X &lt; 0.01051</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3020</v>
+        <v>3023</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4733440320372253</v>
+        <v>0.4860848168541239</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7816151638985858</v>
+        <v>0.794112930323486</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3481040647941072</v>
+        <v>0.3612830016748916</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4764185280257394</v>
+        <v>0.4895978847872797</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1298169068862478</v>
+        <v>0.1395223265847605</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.01261637068047605</v>
+        <v>0.01575132881501418</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1262867215874977</v>
+        <v>-0.1116203624573728</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.141163054647258</v>
+        <v>-0.1073875917891769</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.09964698962462393</v>
+        <v>-0.04703519595968686</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.181326830189704</v>
+        <v>-0.1275670935589872</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1451073822480282</v>
+        <v>0.1794632047189992</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2467848773917396</v>
+        <v>-0.2311688231932294</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3294144707545072</v>
+        <v>-0.3322405504515871</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.399311068133045</v>
+        <v>-0.421436802433945</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.1473555763711616</v>
+        <v>-0.1696247887375861</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.2920621072248224</v>
+        <v>-0.3143027103766087</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.373546938558718</v>
+        <v>-0.3956933145952348</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.2936990140710805</v>
+        <v>-0.3159160188151944</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3554322253724962</v>
+        <v>-0.3776360847892661</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3472222222222214</v>
+        <v>-0.3694771174559293</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.4739397407875643</v>
+        <v>-0.4959835496314327</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.4640429563678907</v>
+        <v>-0.486093220052787</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.3019688449972264</v>
+        <v>-0.3242382110995266</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.2257852135858371</v>
+        <v>-0.2481268993789101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01205</t>
+          <t>X &lt; 0.01204</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3109</v>
+        <v>3111</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4352485974471563</v>
+        <v>0.4658962550563643</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7251880444161358</v>
+        <v>0.7238645792668166</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2950026155187473</v>
+        <v>0.2947036973260211</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3672989310067649</v>
+        <v>0.3673249647220942</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2122533181340671</v>
+        <v>0.1776125471972136</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1432539862161022</v>
+        <v>0.126627388864371</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.02122277664163619</v>
+        <v>-0.01887171172287339</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.07563397035104202</v>
+        <v>-0.0546012544135337</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.03411790532840797</v>
+        <v>0.005236129404700307</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1035024675547689</v>
+        <v>-0.06277727171990222</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1574106539889613</v>
+        <v>0.179241357946033</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.006973961635928561</v>
+        <v>-0.003385008013978563</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.00895866496274067</v>
+        <v>-0.005111637510275102</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.03308977142819458</v>
+        <v>-0.06598545147689805</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.09676735672099568</v>
+        <v>0.064121236565164</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.05882035841391087</v>
+        <v>-0.05962964042477381</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04545568623103691</v>
+        <v>-0.07827735234474886</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.002886059675844876</v>
+        <v>-0.03569253908079872</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.1208106549653323</v>
+        <v>-0.1215749828447272</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.1716591712174775</v>
+        <v>-0.204594024097652</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.3102312573270041</v>
+        <v>-0.3106915332340421</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.2384499037276768</v>
+        <v>-0.2067952613458885</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.1052323881905934</v>
+        <v>-0.1059332370104897</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1619990256546231</v>
+        <v>-0.1304817545219379</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01358</t>
+          <t>X &lt; 0.01357</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3176</v>
+        <v>3180</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2971106142617117</v>
+        <v>0.2941934861932722</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4792861262110719</v>
+        <v>0.4761099213953486</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.08917533141361389</v>
+        <v>0.08635703918723436</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1439385668013244</v>
+        <v>0.1409866396257016</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.0154586156108607</v>
+        <v>0.01040804438295595</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.06373926967568622</v>
+        <v>0.05864191752981185</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1275464628985858</v>
+        <v>-0.1324763335744805</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1375375811407906</v>
+        <v>-0.1424828037995383</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.002007100574438425</v>
+        <v>0.01083377654708784</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.09955762310510607</v>
+        <v>-0.08644928815524366</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.0675658579863736</v>
+        <v>0.08045827399456584</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.08894806573602665</v>
+        <v>0.1018854322893716</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.08093576745443443</v>
+        <v>0.07555821344328706</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.03513915655043576</v>
+        <v>0.02979608305658843</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.08563032185079322</v>
+        <v>0.08016195345254573</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.05416522519247025</v>
+        <v>-0.05940838751377697</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.1067367941063608</v>
+        <v>-0.1119291364830346</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.00443974296457128</v>
+        <v>-0.009773077915582462</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1153289260825474</v>
+        <v>-0.1205069146576321</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1926100628930811</v>
+        <v>-0.1976774185982393</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.2138908776988089</v>
+        <v>-0.2189832346318212</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2081265156160228</v>
+        <v>-0.2132360846163621</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1033903705537753</v>
+        <v>-0.1086102015387951</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.1290747860415138</v>
+        <v>-0.1342723211661649</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01511</t>
+          <t>X &lt; 0.0151</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3222</v>
+        <v>3225</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2099723057165335</v>
+        <v>0.193461479114994</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2922756975512257</v>
+        <v>0.2757624098448375</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.02024969786805997</v>
+        <v>-0.03613910873264814</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.007283138279170487</v>
+        <v>-0.02302114794971999</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1391715938095786</v>
+        <v>-0.1564978444154903</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1198399882467882</v>
+        <v>-0.1372349619552509</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2885612605474392</v>
+        <v>-0.3056235760200039</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2406329895565165</v>
+        <v>-0.2576801607809358</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1064385186024595</v>
+        <v>-0.1059528117669473</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1518300597601367</v>
+        <v>-0.1508950037386896</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.01680209945203615</v>
+        <v>0.01748225191898456</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.06481613624471549</v>
+        <v>0.0656180253866907</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.04091080911717881</v>
+        <v>0.02403815877779891</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.03833747077332106</v>
+        <v>-0.05509051677965005</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.002030851064688477</v>
+        <v>0.01631190304154728</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1273251424256898</v>
+        <v>-0.1130622650882458</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1501113838939503</v>
+        <v>-0.1357923244962222</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.1127394492585694</v>
+        <v>-0.09842695534241841</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1570236530731748</v>
+        <v>-0.1427182283329032</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.1995505269683804</v>
+        <v>-0.1852468856299083</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2902934322537689</v>
+        <v>-0.2757730812495964</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.285718740074806</v>
+        <v>-0.2711813324925103</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1165258147578783</v>
+        <v>-0.1022078821256116</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.1118951942239192</v>
+        <v>-0.09756031297543899</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01664</t>
+          <t>X &lt; 0.01663</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3267</v>
+        <v>3269</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1556658282917596</v>
+        <v>0.1562367261792161</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.08009195160244786</v>
+        <v>0.1112797649122257</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1570265815615528</v>
+        <v>-0.1248891614206755</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1846951698374824</v>
+        <v>-0.1521366579691019</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.319904670160426</v>
+        <v>-0.2884215160631314</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2678365089610821</v>
+        <v>-0.2364799828599544</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3232626107591017</v>
+        <v>-0.2914356840102386</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.34083933992342</v>
+        <v>-0.3088386251814086</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2210016791337708</v>
+        <v>-0.1890881233001522</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2459404733524195</v>
+        <v>-0.2135740076552111</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.07588648199328674</v>
+        <v>-0.04376682256768305</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.06288694532060646</v>
+        <v>-0.0306115678551464</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1629527569486768</v>
+        <v>-0.1299836688323239</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2442146918490948</v>
+        <v>-0.2110641073256403</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1829899467694744</v>
+        <v>-0.1495018294068942</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2413799246439225</v>
+        <v>-0.2081772870604155</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2657308851570264</v>
+        <v>-0.2324297354900722</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.2303514987294548</v>
+        <v>-0.1970044288162356</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2710902503881627</v>
+        <v>-0.2378291595651945</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3104937328034154</v>
+        <v>-0.277303320794843</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3463349655728791</v>
+        <v>-0.3128114648309079</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.3734763578800866</v>
+        <v>-0.3398847413354815</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2334561855513329</v>
+        <v>-0.2000937520926769</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2911894060219424</v>
+        <v>-0.2577401560395955</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01817</t>
+          <t>X &lt; 0.01816</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3292</v>
+        <v>3296</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.008963034710070872</v>
+        <v>-0.01023548342292457</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.05636994393163519</v>
+        <v>-0.05760100641710153</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2120520177441563</v>
+        <v>-0.2131605972312229</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1543365913942267</v>
+        <v>-0.1555475230781909</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3818810807051065</v>
+        <v>-0.3839560802537676</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2985997971841172</v>
+        <v>-0.3007682793789144</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.268793733386687</v>
+        <v>-0.2710343031463225</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3487858129232748</v>
+        <v>-0.3509437141894125</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.229542644533737</v>
+        <v>-0.2318441379282348</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2601471847835981</v>
+        <v>-0.2624479559358832</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.02879412377772184</v>
+        <v>-0.03136366525974665</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.04825682791783947</v>
+        <v>-0.05081694217145127</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1257964527624083</v>
+        <v>-0.1283149985320762</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2081078169781279</v>
+        <v>-0.2105382952088277</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1826200584868261</v>
+        <v>-0.185112635966739</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.2057565149747091</v>
+        <v>-0.208195759043214</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.2006160977767664</v>
+        <v>-0.2030691475463797</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1662809670422405</v>
+        <v>-0.1687818849959228</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2050525914954662</v>
+        <v>-0.2074982977930517</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2427184466019412</v>
+        <v>-0.2451115589972162</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2520395592255653</v>
+        <v>-0.2544474795971894</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.3098810262677674</v>
+        <v>-0.312223757468395</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2295533926011899</v>
+        <v>-0.2319826252133623</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2266703616067289</v>
+        <v>-0.2291080664186467</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.0197</t>
+          <t>X &lt; 0.01969</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3307</v>
+        <v>3311</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.01957228794289279</v>
+        <v>0.01842103293876107</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.0291226939006819</v>
+        <v>-0.03022937232783107</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1905839229427997</v>
+        <v>-0.1915541252785644</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1964546592013221</v>
+        <v>-0.1974465749718135</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3043683600285902</v>
+        <v>-0.3062312966466294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.190519929842047</v>
+        <v>-0.1925134865912668</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1643035179911934</v>
+        <v>-0.1663603352111451</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2150671738968271</v>
+        <v>-0.2170752336415944</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.09613471830424913</v>
+        <v>-0.09828543411963153</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1601674594368419</v>
+        <v>-0.1622730473653533</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.01116905723679906</v>
+        <v>0.00886684053726583</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.009454992130500273</v>
+        <v>-0.01174479069048573</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1519932523182845</v>
+        <v>-0.1541573226700095</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2047935759858817</v>
+        <v>-0.2069041592506053</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1824008026338859</v>
+        <v>-0.1845658193508015</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.2329058362416774</v>
+        <v>-0.2349877199229411</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1982288049795997</v>
+        <v>-0.2003591337992106</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1645237348879007</v>
+        <v>-0.16670021296774</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2021404139779222</v>
+        <v>-0.2042642739621314</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2085850196315349</v>
+        <v>-0.210694995168879</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.2203152126233334</v>
+        <v>-0.2224339746543933</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2782292029300777</v>
+        <v>-0.2802824021628325</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2272400321366703</v>
+        <v>-0.2293451814238878</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2549527230029582</v>
+        <v>-0.2570287515136442</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.02123</t>
+          <t>X &lt; 0.02122</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3323</v>
+        <v>3327</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.001909676138026839</v>
+        <v>0.0009439313441532704</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.107951628915302</v>
+        <v>-0.1087979935972427</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2456481021846031</v>
+        <v>-0.2463789225809947</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.225010260940941</v>
+        <v>-0.2257902876950126</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3042424096882854</v>
+        <v>-0.3057825514280097</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1900428316791078</v>
+        <v>-0.1917142412943491</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1676542173145705</v>
+        <v>-0.1693795199737522</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1895613313014053</v>
+        <v>-0.1912708957975369</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.07099231381742754</v>
+        <v>-0.07284346537907993</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1084537934306056</v>
+        <v>-0.1102873513083864</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.003440300483170233</v>
+        <v>0.001480890415848535</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.07839611662700463</v>
+        <v>-0.08026808441946542</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1956734855302358</v>
+        <v>-0.1974441022742894</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2492960666328941</v>
+        <v>-0.2510110165946173</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2301883132955709</v>
+        <v>-0.2319495990740066</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2776068101813607</v>
+        <v>-0.2792921720957651</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.243754113027542</v>
+        <v>-0.2454857323493087</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2107292895825879</v>
+        <v>-0.212505215536126</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2170918725435058</v>
+        <v>-0.2188539457777878</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1925533513676001</v>
+        <v>-0.1943396550280667</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2369015515114796</v>
+        <v>-0.2386541779596882</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.294907344339812</v>
+        <v>-0.2965939784767571</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2428460021295535</v>
+        <v>-0.2445869595732759</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2407023175352379</v>
+        <v>-0.2424495560256048</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02277</t>
+          <t>X &lt; 0.02275</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3346</v>
+        <v>3350</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.06771000770983449</v>
+        <v>-0.06835971349126169</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1791306496112739</v>
+        <v>-0.1796571264911506</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3257422612261394</v>
+        <v>-0.3261318365173125</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3101466097362078</v>
+        <v>-0.3105732413831106</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3616414633819716</v>
+        <v>-0.3626545943878199</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2469600789663531</v>
+        <v>-0.2481053522161005</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2597625964528092</v>
+        <v>-0.2609131641389766</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2537086758187002</v>
+        <v>-0.2548743246417615</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1654390826879322</v>
+        <v>-0.166709369451965</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.20796932634439</v>
+        <v>-0.2092096516584903</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.09499241508893874</v>
+        <v>-0.09636089256590452</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1484295930394808</v>
+        <v>-0.1497424824045268</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1832630989748409</v>
+        <v>-0.1845641871159316</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2380315313593471</v>
+        <v>-0.2392739273927376</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1937624165583429</v>
+        <v>-0.1950752581180808</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2367642669126937</v>
+        <v>-0.2380114425975037</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2935235364921596</v>
+        <v>-0.2947073446845678</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2614605146381663</v>
+        <v>-0.2626860381475922</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2663111784912147</v>
+        <v>-0.2675261717471571</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2406716417910459</v>
+        <v>-0.2419132069616552</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2586005284365882</v>
+        <v>-0.2598355143811162</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2868675315461715</v>
+        <v>-0.288071562820889</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2332733367004138</v>
+        <v>-0.2345350663381893</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2615499697640189</v>
+        <v>-0.2627807225554406</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_5.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ret_5.xlsx
@@ -618,1723 +618,1723 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02087</t>
+          <t>X ≈ -0.02073</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.32712751409975</v>
+        <v>-7.064250621802337</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.189683235716295</v>
+        <v>-3.76256686833284</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2391530182193975</v>
+        <v>-8.560139842412148</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.76269120853269</v>
+        <v>1.498924105285411</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>19.28928726145367</v>
+        <v>8.32739602184607</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>22.91036894284997</v>
+        <v>12.0377840832012</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.14917119404611</v>
+        <v>11.25011049926562</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>25.31101235852924</v>
+        <v>14.504763534997</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>28.79293953283306</v>
+        <v>18.19232086136703</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>24.59816074162357</v>
+        <v>13.84838994233969</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>18.0088282452509</v>
+        <v>10.56616863563526</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>17.7363849885752</v>
+        <v>10.29362100597763</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.311258038602482</v>
+        <v>-1.494045731983682</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>16.40645382094685</v>
+        <v>8.940320702995585</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>15.75508243260324</v>
+        <v>8.262726470644132</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>16.35276494196559</v>
+        <v>8.825145921419562</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>9.342093003316322</v>
+        <v>1.596259958327686</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>5.798213275825674</v>
+        <v>5.029198616215083</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.8707412144203772</v>
+        <v>-1.887403976909482</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.6843514226676319</v>
+        <v>-1.673592277065381</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.226646888088247</v>
+        <v>-2.241062133267945</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.143445338817919</v>
+        <v>1.252486415439812</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.418522621808819</v>
+        <v>1.496415421411392</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.343498227522531</v>
+        <v>1.334755415649248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01933</t>
+          <t>X ≈ -0.0192</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-16.48738365925391</v>
+        <v>-24.20668941875642</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.14636290621302</v>
+        <v>-24.45843500982819</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.21888598054533</v>
+        <v>-17.43177592772042</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.930333118580201</v>
+        <v>-18.02651072223409</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-11.9500237106215</v>
+        <v>-22.44969475854359</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.400999088755931</v>
+        <v>-14.01255942945605</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.883798536746099</v>
+        <v>-2.371561286901738</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.923178503505817</v>
+        <v>-6.822178028741646</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.408568342200823</v>
+        <v>-14.99244497484131</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.179556838486853</v>
+        <v>-15.78951573075807</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.219049419974638</v>
+        <v>-11.3724275825095</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-13.56828479202913</v>
+        <v>-24.1065015502969</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-11.00038369039635</v>
+        <v>-21.0720013924149</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-14.91692297906503</v>
+        <v>-25.48029684114292</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-11.88405099771138</v>
+        <v>-22.01274451783492</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-14.98941348547821</v>
+        <v>-25.61605603859012</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-11.43146748152734</v>
+        <v>-21.56926607016204</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-11.53947921140099</v>
+        <v>-21.70836549591392</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-18.723571860304</v>
+        <v>-29.82150739414543</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-11.14417975432195</v>
+        <v>-21.29279523033344</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-11.68964349059275</v>
+        <v>-21.866165995228</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-11.7689488959657</v>
+        <v>-17.78368407152519</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-18.90324297876744</v>
+        <v>-30.04171740543327</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-18.98472654897888</v>
+        <v>-26.04619696530585</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01781</t>
+          <t>X ≈ -0.01768</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.479830440981722</v>
+        <v>8.898236303671048</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-15.77291258330426</v>
+        <v>-7.899847239570391</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.450705412696152</v>
+        <v>7.411655733447446</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.010447960658873</v>
+        <v>2.682823530978716</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-8.792752654494862</v>
+        <v>-5.876641293824001</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.874463261530515</v>
+        <v>-1.579326209156875</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.09330234099367374</v>
+        <v>1.773898704840725</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.555658342188586</v>
+        <v>5.617936571025915</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1413552429332228</v>
+        <v>1.599735239230725</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.572532527635488</v>
+        <v>9.105767318162137</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.848226063807921</v>
+        <v>9.37975113745199</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.573475912144261</v>
+        <v>9.107245919537817</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.20259110589469</v>
+        <v>12.15153289418503</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.98566219645464</v>
+        <v>7.753376679947259</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.835305276876355</v>
+        <v>2.920078160206174</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.17914902815636</v>
+        <v>7.63750608594782</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>7.047881005673815</v>
+        <v>7.536283671231566</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.69864982624973</v>
+        <v>11.56500321673386</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>16.67250506671098</v>
+        <v>15.94309606590984</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>16.86411514618766</v>
+        <v>16.16215023596909</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>21.08470224548898</v>
+        <v>15.6000398421175</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>16.25635684216484</v>
+        <v>15.52960251508151</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>21.29619797295052</v>
+        <v>19.94325754065837</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>21.2269136626624</v>
+        <v>23.953803034697</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01627</t>
+          <t>X ≈ -0.01615</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.194533005756441</v>
+        <v>-6.128450830183418</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.365574159082385</v>
+        <v>-6.374003896989095</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-18.15233563572219</v>
+        <v>-15.46813295991834</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-18.86687723372596</v>
+        <v>-18.67764173271529</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.004582259262961</v>
+        <v>-5.875988077579329</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.702808392472733</v>
+        <v>2.128428820234184</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.935485511423977</v>
+        <v>3.955313632371855</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-8.712519461958834</v>
+        <v>-6.821539621781305</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.673261892775493</v>
+        <v>-6.695567788536962</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.600601340421917</v>
+        <v>-2.249708195223405</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.329546880166042</v>
+        <v>-1.979160688074387</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.762304799032137</v>
+        <v>-2.255060207380488</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.730404474862361</v>
+        <v>-5.989772693907319</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.953398839175506</v>
+        <v>-3.615703355842413</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.611940068098967</v>
+        <v>-6.921323906277784</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-8.02169827264656</v>
+        <v>-6.363574189382739</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.306625440111304</v>
+        <v>-3.84309134423998</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>3.142704125073514</v>
+        <v>6.530013644722828</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.06476562133593</v>
+        <v>12.00131879992568</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.400493679903306</v>
+        <v>9.590896209341622</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>5.860376538472828</v>
+        <v>11.65603277505558</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.786460144796955</v>
+        <v>8.954510710617519</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>11.7752155947766</v>
+        <v>14.46236820533556</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>3.778364438204214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01474</t>
+          <t>X ≈ -0.01463</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.681207985335639</v>
+        <v>-6.616896524496518</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1245073867916133</v>
+        <v>4.000135131734993</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.190354486884814</v>
+        <v>-5.007315697351608</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.15937962227407</v>
+        <v>-5.597899309970103</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.238582055191202</v>
+        <v>-4.321605373828149</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.686670491623694</v>
+        <v>-8.82997454533443</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.304638894041538</v>
+        <v>-3.407529557567059</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.58090131103139</v>
+        <v>-2.156350593850945</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.09216399519507235</v>
+        <v>-0.4737871794072035</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.586919694838684</v>
+        <v>0.2888175773947097</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.22810026865583</v>
+        <v>2.116272657000749</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.315366080559798</v>
+        <v>-1.271639006405366</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.43535989074077</v>
+        <v>-3.940258848099852</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3886634485380469</v>
+        <v>-1.073963342795061</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.044842300190062</v>
+        <v>-1.754343469129459</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.087576189410953</v>
+        <v>-1.195094238612327</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.221746890881953</v>
+        <v>-1.299055301140349</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.581522251437974</v>
+        <v>0.127177561014193</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.434624202650816</v>
+        <v>1.901403805166026</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.985345786703888</v>
+        <v>0.5557770057686895</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>5.719823450706663</v>
+        <v>3.111079492464441</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>8.922546921151032</v>
+        <v>6.160030768178082</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>9.199801394012724</v>
+        <v>6.405536536331958</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>7.487647464378362</v>
+        <v>4.682969701363071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01321</t>
+          <t>X ≈ -0.01311</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.008139903549605</v>
+        <v>6.414534480646672</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.677729416374611</v>
+        <v>4.516404369095127</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5179931228692425</v>
+        <v>-5.005905154407628</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.546213464589336</v>
+        <v>1.028002228505976</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5259377523994289</v>
+        <v>-7.530260974604218</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.713773587650969</v>
+        <v>2.564903081532556</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.946170247849615</v>
+        <v>6.746424576000628</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.985395683366178</v>
+        <v>1.471385354634158</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.714606764668098</v>
+        <v>1.5997286530949</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.258725108793072</v>
+        <v>2.466544063150181</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.84348891556823</v>
+        <v>-5.560576379245688</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.809699655443055</v>
+        <v>-5.83730053723432</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.930049535543155</v>
+        <v>-8.610828089766528</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.841953111478794</v>
+        <v>-10.52286556908759</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.810083288183861</v>
+        <v>-9.544282969783566</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-3.528529670784735</v>
+        <v>-8.987592496662458</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2809339261104711</v>
+        <v>-5.768126631294308</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.3860118290644934</v>
+        <v>-5.902965878429356</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.862863367978626</v>
+        <v>-7.354793780087554</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.676791262904324</v>
+        <v>-3.813681505143506</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.5261223003198623</v>
+        <v>-1.051725784506651</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.091836652869141</v>
+        <v>-1.127144392273863</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.366687426139727</v>
+        <v>0.7822477420206013</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4034333914145449</v>
+        <v>-1.046196965303949</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01168</t>
+          <t>X ≈ -0.01158</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.528850213869489</v>
+        <v>-2.813820822923788</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.639097914594579</v>
+        <v>1.135700924149496</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.453258774405967</v>
+        <v>2.689443839583838</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.777147812791121</v>
+        <v>-4.895913544024204</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.113509748801661</v>
+        <v>-2.372407009389065</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-15.39594118519906</v>
+        <v>-14.82185749529655</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-12.24449527899927</v>
+        <v>-17.02007419344676</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.979446766058871</v>
+        <v>-7.519567228356742</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8.558423789644209</v>
+        <v>-8.795716811747596</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.091596466240766</v>
+        <v>-5.385388027931434</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.439937789793618</v>
+        <v>-6.517978116876023</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.787210490945284</v>
+        <v>-2.586145825414718</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.907101106592023</v>
+        <v>-0.8907398941087052</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.129126774037935</v>
+        <v>-1.138898184122404</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-7.410316381405664</v>
+        <v>-4.627956759721599</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-5.507761751865758</v>
+        <v>-2.665079055824528</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-6.956000083094914</v>
+        <v>-4.17496015205905</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-8.376477811175583</v>
+        <v>-4.309364022156046</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-6.850091220289812</v>
+        <v>-2.69054773160024</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-7.979752292156448</v>
+        <v>-6.697040027826681</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-8.524474029444661</v>
+        <v>-8.673339415149094</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.343293701481009</v>
+        <v>-1.713592753475069</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.069883730755983</v>
+        <v>-2.87854513041821</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.146519921298577</v>
+        <v>-3.041502129623197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01015</t>
+          <t>X ≈ -0.01006</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-7.94355280680368</v>
+        <v>-9.235939448430265</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.425687733769884</v>
+        <v>-9.484515704035019</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.858058613911126</v>
+        <v>-0.229457337469718</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.671228594250664</v>
+        <v>-4.638243286903787</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.007251237746893</v>
+        <v>-4.914639043733892</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-3.823623588698702</v>
+        <v>-4.761386196999631</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.490252432964226</v>
+        <v>-8.42365019002338</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-7.769082133040236</v>
+        <v>-9.685951093014808</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-9.661662977465333</v>
+        <v>-10.517911864685</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.637208565869216</v>
+        <v>-5.572664614945907</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.400999629785389</v>
+        <v>1.398537303860458</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.091367927800938</v>
+        <v>2.081395551500499</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.973668555607389</v>
+        <v>0.9715077018536675</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.656324295020653</v>
+        <v>3.598886827336429</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>7.87381703247015</v>
+        <v>8.672126122345283</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>8.46887745574206</v>
+        <v>9.23442250907226</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>8.338135636523717</v>
+        <v>8.174553341950379</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>9.204864952782046</v>
+        <v>9.963410113532717</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>8.454121906488204</v>
+        <v>9.220802918642832</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.70451008495202</v>
+        <v>7.517749417372841</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.164647231234959</v>
+        <v>6.953247126155333</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.0908702355919</v>
+        <v>6.88033386593478</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>7.337967836729817</v>
+        <v>8.087463872109218</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.381328826785449</v>
+        <v>4.082008162901175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.008624</t>
+          <t>X ≈ -0.008532</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4164531941149932</v>
+        <v>1.498266598991584</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.551150503010433</v>
+        <v>4.894861069023804</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.124910949362707</v>
+        <v>2.739607448229144</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.26451720052426</v>
+        <v>-0.5796939677917763</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.875082131936701</v>
+        <v>3.702060377884088</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.309989656837629</v>
+        <v>-1.612021225245087</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.974685809848033</v>
+        <v>-2.404370350053888</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.356141737866821</v>
+        <v>-1.795776417609169</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5224425982049397</v>
+        <v>0.1569075892695082</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.188896686141419</v>
+        <v>3.014553370170376</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.462433107045015</v>
+        <v>3.286159992735925</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.980459876481049</v>
+        <v>4.839186021123389</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.556068483099587</v>
+        <v>6.472352654157085</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.644130913747226</v>
+        <v>3.483770569128183</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.989498760504596</v>
+        <v>0.9757669093285557</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.582887749012578</v>
+        <v>1.535446168485485</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.248015073988554</v>
+        <v>4.178036633326791</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.548914049558348</v>
+        <v>-0.5311700263482138</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.664259985853654</v>
+        <v>0.5985639684879516</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.052751563310217</v>
+        <v>-1.019012047215327</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.110880041884634</v>
+        <v>2.079583726426002</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.335741119825144</v>
+        <v>-0.745234178172737</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.710177131375346</v>
+        <v>-1.418941945631424</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.139397575145033</v>
+        <v>3.005790802280153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007094</t>
+          <t>X ≈ -0.007008</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.1551028898242</v>
+        <v>3.081843677033561</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3721685718171202</v>
+        <v>2.142675886298207</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.557077041586929</v>
+        <v>4.36795286973485</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.29431947322945</v>
+        <v>6.560418916047723</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.859800977472418</v>
+        <v>8.370117116260815</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.832400204610295</v>
+        <v>6.445048351278793</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.561497986045552</v>
+        <v>1.486269362484194</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.564000374506314</v>
+        <v>1.18388439619887</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.248951776327267</v>
+        <v>-0.7743810685990624</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.569369558323075</v>
+        <v>-0.1780072054862814</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.024428404342075</v>
+        <v>-0.6035925409567326</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.576378804529611</v>
+        <v>-0.1830363653380047</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.241716830633578</v>
+        <v>0.09967382914595646</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.281454017899442</v>
+        <v>1.942212629313431</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.5177702481722264</v>
+        <v>2.657234405780073</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.3453751720959843</v>
+        <v>1.822898515600365</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.2489489078052998</v>
+        <v>2.417352906524798</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.329349587209698</v>
+        <v>4.378787728651311</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.002768435525319</v>
+        <v>5.990414085520868</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>4.191201443141821</v>
+        <v>6.207233363934535</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.7341779041450636</v>
+        <v>2.848377430799729</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.6587946029033489</v>
+        <v>2.774351455999103</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.9336248207684221</v>
+        <v>3.019043356220131</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.048255338017604</v>
+        <v>4.956134037026892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.005564</t>
+          <t>X ≈ -0.005484</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.780708433743023</v>
+        <v>2.325171288338147</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.449140534491534</v>
+        <v>4.023459800137395</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.811491007459487</v>
+        <v>8.613224865973429</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9.54299010346017</v>
+        <v>7.058003713272264</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.573653458601967</v>
+        <v>4.838026812766898</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.366149541969676</v>
+        <v>1.103089026151537</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9258108458970469</v>
+        <v>-1.633436175823633</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.071598238301974</v>
+        <v>0.4987151480045426</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.143004298892699</v>
+        <v>-0.8346302228996336</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.340426602620077</v>
+        <v>-0.1675442951628128</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.102890435055947</v>
+        <v>1.078099419716928</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.338135776352011</v>
+        <v>0.315199835393436</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.125042885151387</v>
+        <v>2.621854101786646</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.932982580365788</v>
+        <v>1.886604593230885</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.3255769147154481</v>
+        <v>-0.7459517431827223</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.871936707559165</v>
+        <v>1.278822785916979</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.251996065174488</v>
+        <v>0.6867450629538681</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.949001655397453</v>
+        <v>0.06508155781609304</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.01818369170728573</v>
+        <v>-2.656342284833478</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.229871813645389</v>
+        <v>-4.889733387267881</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.3364828952032752</v>
+        <v>-3.010307212586106</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.387058433052346</v>
+        <v>-4.066122838651843</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.600610682828616</v>
+        <v>-4.314014628686479</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.762337588329153</v>
+        <v>-2.026589122166591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004033</t>
+          <t>X ≈ -0.00396</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.55507737934677</v>
+        <v>2.915695579156896</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.08738755554041</v>
+        <v>4.961884989039412</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.43108373359415</v>
+        <v>2.798781099699404</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.942091670286587</v>
+        <v>5.887761647438992</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.651575905461456</v>
+        <v>4.69659503289617</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.751131411897752</v>
+        <v>7.154727513379989</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.463607529659136</v>
+        <v>6.830228515611466</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.589747055168786</v>
+        <v>2.391806270926644</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.364811072751117</v>
+        <v>4.361790028310885</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1149838694599765</v>
+        <v>2.18767923082585</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.0913309503867481</v>
+        <v>1.537519331568191</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.326027470372971</v>
+        <v>0.8026184302619015</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.051257150165128</v>
+        <v>1.996472599101367</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2718608512668226</v>
+        <v>1.749595994928754</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3.865802638650109</v>
+        <v>5.683480519526576</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.061961173218691</v>
+        <v>4.398883968208246</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.01053793031783101</v>
+        <v>2.45102640118764</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.09439069404680822</v>
+        <v>1.857552825285616</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3588310546473679</v>
+        <v>2.072644841737002</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.268223124158006</v>
+        <v>4.137192329978838</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2466327983150478</v>
+        <v>3.109674571453404</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7894685996668187</v>
+        <v>2.110901104511839</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.887583327700831</v>
+        <v>5.132009531995386</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>4.972321553214464</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002502</t>
+          <t>X ≈ -0.002436</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.574342218334536</v>
+        <v>-0.8766863650837422</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.404135069291833</v>
+        <v>3.368989199841174</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.960157158313145</v>
+        <v>1.750738387790911</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.759643065908804</v>
+        <v>1.916652337459169</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.561161969614055</v>
+        <v>2.769085346711549</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.747174737799817</v>
+        <v>2.553204799496335</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.969267191961933</v>
+        <v>2.520403652412128</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.308907939151936</v>
+        <v>1.470035499561483</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.971142074563559</v>
+        <v>0.4710189155728202</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.05734947806384127</v>
+        <v>-0.6992851256978767</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.946465992989815</v>
+        <v>-2.688240317319902</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.229382848459203</v>
+        <v>-2.96388576055422</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.122290967898699</v>
+        <v>-4.829103451721181</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.346259282981563</v>
+        <v>-5.079013960840577</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.726000976160734</v>
+        <v>-3.498167503987801</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-4.411351769148624</v>
+        <v>-5.205094483281037</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.179941034146253</v>
+        <v>-4.555379813595891</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.522288437035591</v>
+        <v>-3.179471465207435</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.685896604217319</v>
+        <v>-3.344566729529092</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.894305646782001</v>
+        <v>-3.131337526024744</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.831454591590052</v>
+        <v>-3.699477311701848</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.670303672874539</v>
+        <v>-3.776049476734812</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.160114601355964</v>
+        <v>-4.291527278643159</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.473558892773063</v>
+        <v>-3.318924238031229</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.000972</t>
+          <t>X ≈ -0.0009111</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.419227558341454</v>
+        <v>3.669234621574624</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.79941210708111</v>
+        <v>1.238585283922085</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.206472368873314</v>
+        <v>3.92426406432385</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.483659434716877</v>
+        <v>6.400168222255026</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.458729769664146</v>
+        <v>1.74288407376892</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.352275939000457</v>
+        <v>4.533430902386826</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.588568424696817</v>
+        <v>3.101526509572892</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>7.009166360347109</v>
+        <v>7.627310888119041</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7.482034317516664</v>
+        <v>8.63759732429812</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.434211625959598</v>
+        <v>6.526581700748665</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.001553801980712</v>
+        <v>5.043666699837267</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.726905864917306</v>
+        <v>4.768380154247964</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.753988142285515</v>
+        <v>2.771323132613759</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.962142683726007</v>
+        <v>2.964419307188791</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.305789239640802</v>
+        <v>2.281965343464513</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>3.185413147541283</v>
+        <v>4.611718553947227</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.089818016757228</v>
+        <v>-0.7856192601235819</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.623371943832829</v>
+        <v>-1.800788710316723</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.6940420052611742</v>
+        <v>0.1810438331682533</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.5072793914913802</v>
+        <v>0.3960622894414172</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-3.191644555566256</v>
+        <v>-1.501710433892534</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.268653545305689</v>
+        <v>-2.200155697133418</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.567182182832951</v>
+        <v>-1.694647640609489</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-3.502291324054383</v>
+        <v>-3.184840033150557</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005581</t>
+          <t>X ≈ 0.0006129</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.529494691236827</v>
+        <v>5.694240563464724</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6.194437681867214</v>
+        <v>6.390093548945273</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.095870184334288</v>
+        <v>1.068049382903148</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.717102124706607</v>
+        <v>2.985305848805282</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.050897354866862</v>
+        <v>2.56704893793971</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.237172660585294</v>
+        <v>2.893966312085041</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.803237683233831</v>
+        <v>3.048283785000059</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.715053902113752</v>
+        <v>1.492788927636333</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4.426145114102681</v>
+        <v>3.820324172052239</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.327667091463653</v>
+        <v>3.343745688343006</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.274233262935844</v>
+        <v>5.190483229137911</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.664595731069497</v>
+        <v>3.031734417751764</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.223379363811041</v>
+        <v>4.439965082257437</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.00280225536175</v>
+        <v>2.934979740847695</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.675112567840138</v>
+        <v>1.309740336679944</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.264518441743263</v>
+        <v>0.9258643150235457</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.136976331524878</v>
+        <v>2.085111386345908</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.0225463587825061</v>
+        <v>-0.2570196675359711</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.9072096060934953</v>
+        <v>0.5901948320942054</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.2456331348311807</v>
+        <v>-0.4594803548030413</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.456725398855419</v>
+        <v>-1.029323183282706</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.203221237410546</v>
+        <v>-2.054556028726118</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.942778329820136</v>
+        <v>-3.074283006176302</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.671776014551803</v>
+        <v>-0.51877080496633</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002089</t>
+          <t>X ≈ 0.002137</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.518354315631456</v>
+        <v>4.330690516934744</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5451855492432429</v>
+        <v>0.4021562746089202</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.9617309574804409</v>
+        <v>2.675212740711565</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5763352117781366</v>
+        <v>1.589398723735677</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7335497822446371</v>
+        <v>-0.02633581435738108</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.19998408367892</v>
+        <v>-0.876840814384849</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.644758090465551</v>
+        <v>1.353468068166293</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9354493614932906</v>
+        <v>0.04493714007379168</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.5473319852195</v>
+        <v>-0.3138131034681066</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.99111635206129</v>
+        <v>-1.105762707353939</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7368863546007631</v>
+        <v>0.174923460961395</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6853748892684237</v>
+        <v>-0.09694157266623193</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.807149875422674</v>
+        <v>-1.208571642595537</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.356630067296507</v>
+        <v>-1.456393601832389</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.820725721495407</v>
+        <v>-2.476050738658564</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.214418253480751</v>
+        <v>-2.732563752153254</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-3.018178129525872</v>
+        <v>-2.835216948886078</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.091021030153343</v>
+        <v>-4.321710588740842</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-7.830027724298979</v>
+        <v>-6.819114895763917</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-6.330215523173209</v>
+        <v>-5.254779322519717</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-5.886206375212105</v>
+        <v>-5.487558182925149</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.995842838521675</v>
+        <v>-3.189839348948198</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.697521703242067</v>
+        <v>-5.319086219602056</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.751783079193338</v>
+        <v>-7.854106569823728</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003619</t>
+          <t>X ≈ 0.003661</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.89245730918131</v>
+        <v>-4.310503537094853</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.185988546721923</v>
+        <v>-2.506240366588152</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.596458723591176</v>
+        <v>-3.248367768301861</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.265198857186007</v>
+        <v>-2.30185830779012</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.149742862652793</v>
+        <v>-5.655652212073718</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.473912601490703</v>
+        <v>-5.498718606075634</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.687543149559033</v>
+        <v>-3.729265779548797</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.635458171785253</v>
+        <v>1.891918150833583</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.105063788694359</v>
+        <v>-1.059233933239469</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.871474249978434</v>
+        <v>-1.338123926789898</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.113653827322594</v>
+        <v>-1.581313914887652</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8473223037806648</v>
+        <v>-0.3116644142419602</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.450225987099813</v>
+        <v>-0.9096524554770227</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.263619906224569</v>
+        <v>-4.766776036034059</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.324333046030802</v>
+        <v>-1.535181590480704</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.331608260087606</v>
+        <v>-4.586876976653102</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.893200553477264</v>
+        <v>-2.110486354621528</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.4259723514667613</v>
+        <v>-0.1769530394720462</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.7244947517088249</v>
+        <v>-0.480872128161792</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.051806785151243</v>
+        <v>-0.785387641017671</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.077891669903408</v>
+        <v>-0.3185057547175489</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-3.21380917898086</v>
+        <v>-2.466207136776454</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.399428059249772</v>
+        <v>-0.1500337913944563</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.508972444358804</v>
+        <v>-1.348442215735737</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005149</t>
+          <t>X ≈ 0.005185</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.800627391529709</v>
+        <v>1.373210765897845</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.867630555430424</v>
+        <v>3.733415601642086</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.03434799456592685</v>
+        <v>1.329259358256003</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6796920999462586</v>
+        <v>1.892812253364561</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.8168055386753679</v>
+        <v>2.205720275675056</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.012029166409235</v>
+        <v>-1.686685152186051</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.187929962689104</v>
+        <v>-3.634226053185031</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.256562825760966</v>
+        <v>-3.938647038715054</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.01138990408659168</v>
+        <v>0.2401192784640998</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7508745637268674</v>
+        <v>-0.5502230809718966</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.69014894936528</v>
+        <v>-0.8581049294288476</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.959072170158073</v>
+        <v>-1.712099028991553</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.467522794136002</v>
+        <v>-2.245975116513065</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.470840944596809</v>
+        <v>-1.333138712736805</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.300195448206857</v>
+        <v>0.312192285495108</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.2865527059408279</v>
+        <v>-0.2901475073076725</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.369919731679545</v>
+        <v>0.1867362726172743</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.089537812838074</v>
+        <v>2.384900564151529</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.089979354914462</v>
+        <v>3.185223460134011</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.4542007037710647</v>
+        <v>1.999716080379848</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.952663753953509</v>
+        <v>3.772031469171189</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.487541100685668</v>
+        <v>4.281664268853334</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.326657792152645</v>
+        <v>1.601322145944572</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.689166856621839</v>
+        <v>3.193569116567396</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.00668</t>
+          <t>X ≈ 0.00671</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.895023831779312</v>
+        <v>-1.029701017437013</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.716433400833743</v>
+        <v>-3.797185331808144</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-9.139428377901872</v>
+        <v>-8.043711763578003</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.864769434627831</v>
+        <v>-8.138537738563606</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-10.18581341781009</v>
+        <v>-9.39923048968393</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-9.501215336714097</v>
+        <v>-7.231045602726539</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.289870893993758</v>
+        <v>-6.512452557822634</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-6.574067670440009</v>
+        <v>-5.312805068298481</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5.042183046910282</v>
+        <v>-3.684861787783468</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.322078571370731</v>
+        <v>-3.975023258686747</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.556505517674729</v>
+        <v>-2.703229214834877</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-7.337818321604317</v>
+        <v>-6.50116877430996</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-6.979744180687476</v>
+        <v>-6.613643437153037</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.218112024475637</v>
+        <v>-5.861368009422783</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.369905682484593</v>
+        <v>-3.512340375354249</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-3.977509376461562</v>
+        <v>-3.961395329815645</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.609583778191471</v>
+        <v>-2.049111518850545</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.713049568705181</v>
+        <v>-1.680304122873231</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.9964707311271326</v>
+        <v>-2.48416657113998</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.193344540169406</v>
+        <v>-0.2409691431552545</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.8528014407533249</v>
+        <v>-1.517842963102389</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.072680261680958</v>
+        <v>0.4374513677342122</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.15915649397148</v>
+        <v>1.696314279408533</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.5760402479688125</v>
+        <v>0.5189468587231261</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.00821</t>
+          <t>X ≈ 0.008234</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.025839558056532</v>
+        <v>-2.78386012723135</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.585545409588903</v>
+        <v>-4.543692495144725</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.206699386567337</v>
+        <v>-2.009965096963406</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.287508047959037</v>
+        <v>-7.920175768978488</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.7999130668596024</v>
+        <v>0.1540486794612406</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.086278893948972</v>
+        <v>-3.490839130081369</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.095871774942466</v>
+        <v>-2.009879030358356</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.675561124829549</v>
+        <v>-5.353988928197168</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.628987885346532</v>
+        <v>-5.982507403253734</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.341089307072949</v>
+        <v>-3.746959401914069</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.829012412188128</v>
+        <v>-4.234003902732866</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.917101652457355</v>
+        <v>-4.543250235550012</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.980234603896598</v>
+        <v>-3.390658207641472</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6794378821194229</v>
+        <v>-1.36339508027821</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.5450507787290775</v>
+        <v>-1.26515315164648</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.822053284160468</v>
+        <v>0.06171863274090583</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-3.965503301017783</v>
+        <v>-4.66429594186949</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.744762609490124</v>
+        <v>-2.02306763447735</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-3.079258825465025</v>
+        <v>-2.879159057502967</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-3.66513015644351</v>
+        <v>-3.433803381674792</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.674625330031603</v>
+        <v>-2.462786344593994</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.49186168696292</v>
+        <v>-1.768718097318512</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.762813331069978</v>
+        <v>-3.063545150501625</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.585932405998733</v>
+        <v>-2.456453375560322</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009743</t>
+          <t>X ≈ 0.009758</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.142093996225015</v>
+        <v>-2.523781165872471</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-3.496820919263079</v>
+        <v>-2.773989543729762</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.889952187745443</v>
+        <v>-4.020940869745225</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6078937383602607</v>
+        <v>0.4785188944528898</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.913759023875095</v>
+        <v>-1.829138365323196</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.280688458980308</v>
+        <v>3.422238128973177</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5261961341922614</v>
+        <v>1.611106556902129</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.250478455025217</v>
+        <v>2.325246752839313</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.713021894232156</v>
+        <v>-1.622206586429144</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.483863596885428</v>
+        <v>-4.46229152768624</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.221365562705635</v>
+        <v>-0.1026757851737372</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.557199674845201</v>
+        <v>5.758999629470594</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.446608177568805</v>
+        <v>5.66873859777764</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.260726072607198</v>
+        <v>7.478714493169043</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.572279744723673</v>
+        <v>4.749195394685664</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.146464646464644</v>
+        <v>3.248643743402233</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>6.052951549891219</v>
+        <v>7.895725945017098</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>4.938009835969027</v>
+        <v>6.731914004803997</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.164002226994363</v>
+        <v>7.977304067001299</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>9.222818347111797</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.808301868996359</v>
+        <v>7.624446010679577</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.712253887385231</v>
+        <v>5.487427818621192</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>8.027132640271333</v>
+        <v>9.854773644105698</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>7.951300387048114</v>
+        <v>9.692634649816263</v>
       </c>
     </row>
     <row r="27">
@@ -2344,79 +2344,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2882063511204933</v>
+        <v>0.4622847895519726</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.77306322085731</v>
+        <v>-1.969852985097788</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.021165687542293</v>
+        <v>-2.268319609786651</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.860297871796597</v>
+        <v>-5.120661666455575</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.44276978190603</v>
+        <v>0.2062455330800859</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.878108646530727</v>
+        <v>2.623118996938807</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.134045520311638</v>
+        <v>0.6190932140813743</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.741606864034715</v>
+        <v>-0.8421217721557284</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.775126743757532</v>
+        <v>-0.6931331713530753</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.148118315657577</v>
+        <v>-0.4039089720556746</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.151677318390071</v>
+        <v>-1.678426562035</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.804729268030769</v>
+        <v>6.646659564184915</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.23976309795373</v>
+        <v>10.77965590309662</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>12.18496849684969</v>
+        <v>12.37451525754906</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>8.117734290178213</v>
+        <v>8.244085013595033</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>8.712121212121204</v>
+        <v>8.805389032414652</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>10.85093134787101</v>
+        <v>11.00035919540233</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>9.609727007686203</v>
+        <v>9.718049802884408</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>8.689254752246875</v>
+        <v>8.783086742673817</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.467009653124038</v>
+        <v>5.549397325663875</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.060827121521605</v>
+        <v>6.131378111639464</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>9.394072069203425</v>
+        <v>9.504491451753147</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.395819508958198</v>
+        <v>7.449275362318879</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.91089634664398</v>
+        <v>3.838860505960419</v>
       </c>
     </row>
     <row r="28">
@@ -2426,571 +2426,571 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.189044393918451</v>
+        <v>-6.269264892319647</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-10.29050560831373</v>
+        <v>-10.58985980061755</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-9.13296740402248</v>
+        <v>-9.178992433178351</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-9.828808707192941</v>
+        <v>-9.76703201092382</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-7.397914763694743</v>
+        <v>-7.333402471065106</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.898351148942162</v>
+        <v>-3.071242445033775</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.233325561714608</v>
+        <v>-5.266725818404339</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.102525724036518</v>
+        <v>-4.210508490239775</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3028970353504192</v>
+        <v>0.03573470266569956</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.154371465093092</v>
+        <v>-1.357995878148294</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.305893223837586</v>
+        <v>-5.195349904639812</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.851265909473902</v>
+        <v>2.747246223080673</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.734325937750462</v>
+        <v>1.632354105629901</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.362175347969547</v>
+        <v>1.384120044196756</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.8054813257513018</v>
+        <v>-2.037760365085603</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.04940711462450764</v>
+        <v>-2.84631935996449</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.63259961392086</v>
+        <v>-4.320062785388131</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.161110406895688</v>
+        <v>-1.713220863152472</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.07227357449887251</v>
+        <v>-2.868621649705325</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.1145722354691543</v>
+        <v>-2.654035204646306</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.919852154459726</v>
+        <v>0.8881093350687763</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.5038198939058987</v>
+        <v>-3.296642227982403</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2293451814239233</v>
+        <v>-3.053007742703983</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.3051774346471205</v>
+        <v>-3.215146736993447</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01434</t>
+          <t>X ≈ 0.01433</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>45</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.959223181807999</v>
+        <v>-6.875960061443934</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-13.93716237332023</v>
+        <v>-13.78853356381447</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-8.710651507821311</v>
+        <v>-8.376560999039384</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-11.63656849022699</v>
+        <v>-11.19118542006983</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-11.96167520209057</v>
+        <v>-11.46674356016913</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-13.98980873109288</v>
+        <v>-13.53203217639334</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-12.53383718706296</v>
+        <v>-12.10489196640373</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-8.388259458026845</v>
+        <v>-7.965367965367975</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8.357456036795966</v>
+        <v>-7.837439055683895</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.69803553049622</v>
+        <v>-4.189046106458754</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.436796401154822</v>
+        <v>-3.91681109185442</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.504719593776592</v>
+        <v>-1.971170824103496</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.629306162057219</v>
+        <v>-3.086062941554303</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.072607260726002</v>
+        <v>-5.556519225209534</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-4.508528336084346</v>
+        <v>-4.016451384872397</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-3.914141414141412</v>
+        <v>-3.455147366052771</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.8258363288966</v>
+        <v>-1.336805555555564</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-6.375121477162288</v>
+        <v>-5.914134105161601</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.714785651793456</v>
+        <v>-1.255227433571392</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>1.181581233709764</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.29270823201378</v>
+        <v>-3.8303077121153</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-4.368554193422881</v>
+        <v>-3.905470234070584</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.3503649635037149</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.496754932502597</v>
+        <v>2.842691923584937</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01587</t>
+          <t>X ≈ 0.01586</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.510310982895845</v>
+        <v>-2.431515616999491</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-11.91268684884468</v>
+        <v>-11.56631134159221</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.672384219554026</v>
+        <v>-6.154338776817163</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-9.658065511724011</v>
+        <v>-8.968963197847572</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-10.05213104254636</v>
+        <v>-9.244521337946907</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.580782572066745</v>
+        <v>-6.865365509726665</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6565927533669367</v>
+        <v>1.22844136692953</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.155418225185677</v>
+        <v>-3.520923520923525</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.328383257723168</v>
+        <v>-5.615216833461609</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.863536695997425</v>
+        <v>-4.189046106458754</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.519546983905414</v>
+        <v>-3.91681109185442</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.059368648425682</v>
+        <v>-6.415615268547946</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-11.45758899034011</v>
+        <v>-11.97495183044319</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-11.67866786678668</v>
+        <v>-12.22318589187627</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-12.33681116436723</v>
+        <v>-12.90534027376129</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-7.196969696969695</v>
+        <v>-7.89959181049722</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-7.330886833947169</v>
+        <v>-8.003472222222229</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-7.435727537768351</v>
+        <v>-8.13635632738383</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-7.219836156844025</v>
+        <v>-7.921894100238056</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-7.032990346875998</v>
+        <v>-7.707307655179072</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-3.03008196938751</v>
+        <v>-3.830307712115356</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-5.378655203523891</v>
+        <v>-6.127692456292863</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-7.376907763769076</v>
+        <v>-8.106280193236714</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-11.9981945624469</v>
+        <v>-12.71286363197062</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.0174</t>
+          <t>X ≈ 0.01738</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-20.30751378009869</v>
+        <v>-18.92724211272593</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-20.64229057844855</v>
+        <v>-19.17314894842991</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-10.96919851636838</v>
+        <v>-8.889381511859895</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5710414246999562</v>
+        <v>-1.789476018360482</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-12.01794300835829</v>
+        <v>-9.757341850767453</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-8.127273118557206</v>
+        <v>-9.600408244769369</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.211889308663551</v>
+        <v>1.142971281459445</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.47372954349693</v>
+        <v>-6.854256854256803</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-5.432242361582283</v>
+        <v>-6.726327944572752</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.205158037618773</v>
+        <v>-7.52237943979209</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.476309011950612</v>
+        <v>0.4421632671198878</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.506144095201137</v>
+        <v>-3.680572533505263</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.07439754164644086</v>
+        <v>-0.9493108048021384</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1466813348001494</v>
+        <v>-1.197544866235248</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-4.508528336084403</v>
+        <v>-5.725853094274143</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2104377104377164</v>
+        <v>-1.318395229300641</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.35934885628852</v>
+        <v>2.423878205128204</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>3.254508152467395</v>
+        <v>2.290994099966603</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.470399533391664</v>
+        <v>2.505456327112377</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.657245343359641</v>
+        <v>2.720042772171361</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>6.818402879097412</v>
+        <v>5.99875211694453</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.038853213984616</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.094079480940849</v>
+        <v>-5.371237458193974</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.237495673243288</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.01892</t>
+          <t>X ≈ 0.0189</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.359152886568133</v>
+        <v>3.600230414746498</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.024376088218318</v>
+        <v>3.354323579042727</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.586357039187327</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-9.459930313588941</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>16.87094588053046</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>23.72457873329449</v>
+        <v>22.81717417281295</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>22.95263004940414</v>
+        <v>29.16494930343747</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>29.34108527131774</v>
+        <v>28.86002886002865</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>29.38257245323254</v>
+        <v>28.98795776971296</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>21.94299011052938</v>
+        <v>21.04904913163658</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.883716419357874</v>
+        <v>7.035569860526635</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.60496701591002</v>
+        <v>6.758987906055339</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.851528384279476</v>
+        <v>-1.498761354252586</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>5.395861727171358</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-2.429149797570851</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-6.136363636363534</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.2915451895042835</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>7.360949047063485</v>
+        <v>5.467295519424113</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>4.899851018043265</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>4.824688496088193</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.3503649635038357</v>
+        <v>-2.074534161490682</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-6.392133956386289</v>
+        <v>-9.379530298637384</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02046</t>
+          <t>X ≈ 0.02043</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.64084711343201</v>
+        <v>-3.542626728110676</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-16.47562391178178</v>
+        <v>-14.89964467492562</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-11.66364296081277</v>
+        <v>-10.59878322126161</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2123874528027869</v>
+        <v>5.199923106497508</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02542126670545031</v>
+        <v>5.356856712495627</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.797369950595801</v>
+        <v>-0.9937808552927265</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.174418604651166</v>
+        <v>9.812409812409882</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.21590578656587</v>
+        <v>9.940338722093905</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.69299011052938</v>
+        <v>14.69984278243005</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.532950247308698</v>
+        <v>3.860966685923358</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-14.31169965075674</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.184861717612769</v>
+        <v>-8.64161849710986</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.405940594059402</v>
+        <v>-8.889852558542934</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-10.06408389163996</v>
+        <v>-4.016451384872433</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-9.469696969697104</v>
+        <v>-3.455147366052813</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-3.559027777777779</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-9.708454810495624</v>
+        <v>-3.69191188293938</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-3.242563429571298</v>
+        <v>2.078105899761951</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.194282380396771</v>
+        <v>7.848247900376535</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-3.598263787569387</v>
+        <v>1.725247843440201</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-3.674109748978488</v>
+        <v>1.650085321484831</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-3.399635036496434</v>
+        <v>1.893719806763293</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.774532710280461</v>
+        <v>7.287136368029458</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02198</t>
+          <t>X ≈ 0.02195</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.16258624386672</v>
+        <v>-12.63353581901963</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-10.49736304221656</v>
+        <v>-8.333988109269015</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.93538209124755</v>
+        <v>-9.588682211160595</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-12.64833611069032</v>
+        <v>-10.18108440996882</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-8.636300496281045</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.449334310183637</v>
+        <v>-5.754254398615487</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-13.56910908103048</v>
+        <v>-11.09479095630275</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-9.499494438827064</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.80583334386891</v>
+        <v>-11.2717824900273</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-14.5787490199054</v>
+        <v>-12.06783398524664</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-14.30468937774348</v>
+        <v>-16.34105351609684</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.23561269423495</v>
+        <v>-12.0721809251136</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.684703499778465</v>
+        <v>0.4492905937992333</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.463624623331874</v>
+        <v>0.2010565323661595</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>5.153307412707896</v>
+        <v>4.064356695935643</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.747694334650859</v>
+        <v>4.625660714755341</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-7.429701063196184</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-7.534541767017366</v>
+        <v>-4.702012893040397</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-7.31865038609304</v>
+        <v>-4.487550665894624</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-7.13180457612507</v>
+        <v>-4.272964220835668</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-3.32652465713452</v>
+        <v>-0.29495417676182</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>1.219930180894927</v>
+        <v>4.418972332015812</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-3.203728159284843</v>
+        <v>-4.834075753182745</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1805 +3180,1805 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02163</t>
+          <t>X &gt; -0.02149</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3350</v>
+        <v>3374</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1391706748870334</v>
+        <v>0.1812472783657029</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1169027786096848</v>
+        <v>0.1867314538533691</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.08917519403742347</v>
+        <v>0.1261390500524229</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.104857025679209</v>
+        <v>0.1098032527514903</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.006465814334397635</v>
+        <v>0.02750931339404872</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06995808380754198</v>
+        <v>-0.06439590804948381</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.08271298593879095</v>
+        <v>-0.1058094276574479</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.01720349873563976</v>
+        <v>-0.04009756222146876</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.04131440469365089</v>
+        <v>0.04558117316108934</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05832899281237758</v>
+        <v>0.03370084356091496</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05231588412157606</v>
+        <v>0.05720721343048751</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.02872271688161021</v>
+        <v>0.03381703439882955</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.06555198836556286</v>
+        <v>-0.05963917657805951</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.09046440358321206</v>
+        <v>-0.08370598643890759</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.07599219768342635</v>
+        <v>-0.06860759073836675</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.08911328893461246</v>
+        <v>-0.08107548222334771</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.05639933157763011</v>
+        <v>-0.04921805678793589</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.05410439333233086</v>
+        <v>-0.01669820772570318</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.118494875174882</v>
+        <v>-0.05105788965635583</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1226526225847877</v>
+        <v>-0.02623404160101472</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2001874380315769</v>
+        <v>-0.07286356379172787</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1985727561383044</v>
+        <v>-0.04159451000534631</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2643769045954301</v>
+        <v>-0.1062801932367066</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.2627807225554406</v>
+        <v>-0.1323459477184912</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.0201</t>
+          <t>X &gt; -0.01996</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3321</v>
+        <v>3346</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.186904082740277</v>
+        <v>0.2418790599570713</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1075349275840622</v>
+        <v>0.2197799753779321</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.09204225761930473</v>
+        <v>0.1988275763491956</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.005675100578770298</v>
+        <v>0.09817881047086985</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1749623031021912</v>
+        <v>-0.04194580550513649</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2706294128569482</v>
+        <v>-0.1656693807796117</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2768486803740728</v>
+        <v>-0.2008380462927875</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2383773198319048</v>
+        <v>-0.1618118810266438</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2097536858561924</v>
+        <v>-0.1062743890833175</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.155960414208252</v>
+        <v>-0.08190324931589998</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1044859401701217</v>
+        <v>-0.0307338863369111</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1259060713987665</v>
+        <v>-0.05203906578174866</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1212362674327423</v>
+        <v>-0.04763577444077782</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.234520600063604</v>
+        <v>-0.1592208541329256</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2142340417901138</v>
+        <v>-0.1383258674026564</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2326888591532565</v>
+        <v>-0.1556045316262171</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1384698759052156</v>
+        <v>-0.06298774729098966</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.105208642776951</v>
+        <v>-0.05892328575031058</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1119260272862661</v>
+        <v>-0.03569097679230993</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1177476947912339</v>
+        <v>-0.01244861703645483</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1912240763779636</v>
+        <v>-0.05471964270823548</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2190239831041936</v>
+        <v>-0.05242363908855907</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2878048137389797</v>
+        <v>-0.1196918720203684</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2855395571089616</v>
+        <v>-0.1446229465751259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01857</t>
+          <t>X &gt; -0.01844</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3294</v>
+        <v>3322</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.323578572428751</v>
+        <v>0.4185092958056913</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2161734344184651</v>
+        <v>0.3980693069989272</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1519678989157356</v>
+        <v>0.326200991188955</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.05928111268353575</v>
+        <v>0.2291217812068496</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.07844540631923991</v>
+        <v>0.1199404000556541</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2367739237102313</v>
+        <v>-0.06563164412450817</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3273457887111277</v>
+        <v>-0.1851555183654554</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2560949905149954</v>
+        <v>-0.1136936427529704</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1671404509681267</v>
+        <v>0.001271695822815389</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1065866730256388</v>
+        <v>0.03157739474028176</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.08715345263074425</v>
+        <v>0.05120490014957824</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01572263926244233</v>
+        <v>0.1217439262797626</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.032062927900256</v>
+        <v>0.1042560903489189</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1141730395799812</v>
+        <v>0.02371286762753044</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1185798044465045</v>
+        <v>0.01970725951196783</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.1117320999210776</v>
+        <v>0.02833611743071174</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.04590432176077996</v>
+        <v>0.09238572644437681</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.01148511352592863</v>
+        <v>0.09748448458199022</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.04062844675486588</v>
+        <v>0.1794985457894072</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.02736710413935128</v>
+        <v>0.1412925987128304</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.09697473691718983</v>
+        <v>0.1028585368403654</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1243524674250054</v>
+        <v>0.0756769781234965</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1352192550092397</v>
+        <v>0.09648170197177564</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1322675325854377</v>
+        <v>0.04250462008638323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01704</t>
+          <t>X &gt; -0.01692</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3273</v>
+        <v>3298</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3033276438495847</v>
+        <v>0.35680115505712</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3187615206916661</v>
+        <v>0.4584543879927594</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1115543676632456</v>
+        <v>0.2746391616515922</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05317830064336704</v>
+        <v>0.2112658557991693</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02253326082223595</v>
+        <v>0.1635783505265778</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2134340287838015</v>
+        <v>-0.05461628040080768</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3300447226322376</v>
+        <v>-0.1994118256295394</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2869678349961404</v>
+        <v>-0.1554035048301898</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.167305892266242</v>
+        <v>-0.01036054342575454</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1622730473653533</v>
+        <v>-0.03445673447807707</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1444840269800309</v>
+        <v>-0.01668021497935968</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.07083207084801302</v>
+        <v>0.05635519133792144</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1105620830208451</v>
+        <v>0.01658639862907307</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1918071794995484</v>
+        <v>-0.03253695999395489</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1311161890196075</v>
+        <v>-0.001399138795086685</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1585113555549427</v>
+        <v>-0.02703685990233851</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.09141898472322652</v>
+        <v>0.03821545637921986</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.08661888490854608</v>
+        <v>0.01403377215881818</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.06608386886355078</v>
+        <v>0.06478467663146148</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1357450837473095</v>
+        <v>0.0247066122682682</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2328791721846883</v>
+        <v>-0.009916584847523779</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2294532604287909</v>
+        <v>-0.03678336538377636</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2727260566551806</v>
+        <v>-0.04794601789738095</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2693108583111368</v>
+        <v>-0.1315011900866452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01551</t>
+          <t>X &gt; -0.01539</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3238</v>
+        <v>3260</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3303273729219143</v>
+        <v>0.4323961168482739</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.380204309077115</v>
+        <v>0.538096539780895</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3089713380519115</v>
+        <v>0.4581438673631411</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2576878570679924</v>
+        <v>0.4314433062174388</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.03131841148950798</v>
+        <v>0.2339782045965251</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2557652470493892</v>
+        <v>-0.08006281838367357</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3653423008261711</v>
+        <v>-0.2478411407841605</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.195894855705312</v>
+        <v>-0.07770007770008647</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.0753638107289305</v>
+        <v>0.06756518519824084</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.09268024617419002</v>
+        <v>-0.008634784935644291</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.07762880775164405</v>
+        <v>0.00619532427757008</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.03093041998746315</v>
+        <v>0.08329807021869584</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.02819812881625694</v>
+        <v>0.08659917332735034</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1079110374091599</v>
+        <v>0.009230010264403177</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.03944576413765333</v>
+        <v>0.0792625609485782</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.07351705595698377</v>
+        <v>0.04682461817135675</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.0350470804803038</v>
+        <v>0.08345768288950239</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1215250940961212</v>
+        <v>-0.06191936746002824</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1647805125191937</v>
+        <v>-0.07435283768914047</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2063962130640959</v>
+        <v>-0.08680111923136025</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2987420350237926</v>
+        <v>-0.145900043643941</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.2944801193487692</v>
+        <v>-0.141589860748212</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.4029539620906633</v>
+        <v>-0.2170846499473313</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2751893403681791</v>
+        <v>-0.1770763109072178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01398</t>
+          <t>X &gt; -0.01387</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3177</v>
+        <v>3196</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4841528865680331</v>
+        <v>0.5735584225573049</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3851138187590166</v>
+        <v>0.4687691086529</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4337616670796578</v>
+        <v>0.5675898661559273</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4577007989124553</v>
+        <v>0.552181080759361</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1709041617153559</v>
+        <v>0.3252039082946396</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.093887620383029</v>
+        <v>0.09515443772548338</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.3473073331881125</v>
+        <v>-0.1845682813742329</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1693020342464209</v>
+        <v>-0.03607503607504015</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.0785804289729839</v>
+        <v>0.07840578323789771</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1441299145411321</v>
+        <v>-0.01459127779832414</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.102699463609639</v>
+        <v>-0.03605904033265972</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.01293189518247573</v>
+        <v>0.1104307275728615</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.03722109292671405</v>
+        <v>0.1672371312032368</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1025204497230305</v>
+        <v>0.03092099105157331</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.02014164430787702</v>
+        <v>0.1159805790727972</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.03484610627467077</v>
+        <v>0.07169408213699313</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.006938657144651472</v>
+        <v>0.1111425486523032</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1734249644384462</v>
+        <v>-0.06570603936939534</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2530913994015904</v>
+        <v>-0.1139174262819935</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.2676792668840022</v>
+        <v>-0.09966876629017918</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.4143015234183594</v>
+        <v>-0.2111211607625094</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.4714516804033764</v>
+        <v>-0.2677800110145654</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.5873317010652599</v>
+        <v>-0.3497028464185092</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4242397165373788</v>
+        <v>-0.2743988843694538</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01245</t>
+          <t>X &gt; -0.01234</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3118</v>
+        <v>3136</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3228587127380393</v>
+        <v>0.46180505409896</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2281977442691741</v>
+        <v>0.3913271074964868</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4321678069476533</v>
+        <v>0.6742256127228359</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3424916112040108</v>
+        <v>0.5430773598203302</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1840900734962219</v>
+        <v>0.4754997925337747</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.184860042215611</v>
+        <v>0.04790159377508729</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4285501738812485</v>
+        <v>-0.3171765630842103</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2100740564847641</v>
+        <v>-0.06491675273401398</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1503565817711916</v>
+        <v>0.0492988405748207</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1706752789980754</v>
+        <v>-0.06206197947463465</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.06975957340259953</v>
+        <v>0.0696396332434901</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.08526520547334115</v>
+        <v>0.2242266063638212</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1312137058451555</v>
+        <v>0.3351848076248487</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.02500569750070269</v>
+        <v>0.2328429277889228</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.08941786723435996</v>
+        <v>0.3008070500330575</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.03126272320130141</v>
+        <v>0.2450222692313631</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.01238589332555762</v>
+        <v>0.2236285661257753</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1694023136966507</v>
+        <v>0.04597622795955658</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2226306726068401</v>
+        <v>0.02461974885459739</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2410155055738059</v>
+        <v>-0.02860984909273157</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.412185607498806</v>
+        <v>-0.1950381641347505</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.5010328259014827</v>
+        <v>-0.2513380904547589</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.6243064055248837</v>
+        <v>-0.3713600643095631</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.42463342185561</v>
+        <v>-0.25963233945361</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01092</t>
+          <t>X &gt; -0.01082</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3042</v>
+        <v>3065</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5190223808584165</v>
+        <v>0.5376841527184197</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2998330072782665</v>
+        <v>0.3740838641090889</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4792724815639815</v>
+        <v>0.6275435591805376</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4703984475694369</v>
+        <v>0.6690702975602818</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3164429947633636</v>
+        <v>0.5414708799518948</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1951669685887083</v>
+        <v>0.3923560457568485</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1333457596836993</v>
+        <v>0.06974210959302951</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.06593456735668468</v>
+        <v>0.1077684621988411</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.05970689876738078</v>
+        <v>0.2541915359467239</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.07271669575334982</v>
+        <v>0.06125160924980833</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.08939017822321205</v>
+        <v>0.2222402401793744</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.157029884279325</v>
+        <v>0.2893282189759816</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.232105200172974</v>
+        <v>0.3635830633583197</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1287907296627466</v>
+        <v>0.2646189861725148</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.2767879536566653</v>
+        <v>0.4149806978283479</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1696472925981141</v>
+        <v>0.3124340780662607</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1864810064774076</v>
+        <v>0.3255208333333286</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.03563967769335363</v>
+        <v>0.1468666546343371</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.05705309153388782</v>
+        <v>0.0875159612892773</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.04767428408128183</v>
+        <v>0.125862758636508</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2095117350241509</v>
+        <v>0.001359678874067072</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.4300230209889122</v>
+        <v>-0.2174653070699506</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.5632071692600675</v>
+        <v>-0.3132817153067222</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3566309978064055</v>
+        <v>-0.1951909837922585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.009389</t>
+          <t>X &gt; -0.009294</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2939</v>
+        <v>2961</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8156012322803932</v>
+        <v>0.8809657651869927</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4654432952428706</v>
+        <v>0.7203501103390693</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4309516337818238</v>
+        <v>0.6576442323489431</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6155456354930422</v>
+        <v>0.8554805011348421</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4679708974338581</v>
+        <v>0.7331072973998189</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3360092371836743</v>
+        <v>0.5733723217604449</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1244839059671676</v>
+        <v>0.3680578134633805</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2040294337543855</v>
+        <v>0.4517559102711886</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.400401385753419</v>
+        <v>0.632543023169184</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.08725018502988746</v>
+        <v>0.2591331652499278</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.008377665970435544</v>
+        <v>0.1809248417927378</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.05419326689833781</v>
+        <v>0.2263849556924384</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1710704857770153</v>
+        <v>0.3422307626479153</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.02988091281152094</v>
+        <v>0.1475085993163674</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.01054297403168647</v>
+        <v>0.1249627565417057</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1212069798768169</v>
+        <v>-0.0009353230903101917</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.09920134360586985</v>
+        <v>0.04983715184187076</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2857043860474135</v>
+        <v>-0.1979224435505458</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.3553351687017283</v>
+        <v>-0.2332749348825445</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.284310891774517</v>
+        <v>-0.1337644661215407</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4329000894047894</v>
+        <v>-0.2428133351472965</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.6585538156223976</v>
+        <v>-0.4667632179083512</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.8401112269725388</v>
+        <v>-0.6083433637671263</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4876312910806391</v>
+        <v>-0.3454202006973972</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.007859</t>
+          <t>X &gt; -0.00777</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2828</v>
+        <v>2852</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8312679339198397</v>
+        <v>0.8573732718894078</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3050778426041845</v>
+        <v>0.5608053366726509</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3252127780429674</v>
+        <v>0.5780741094418786</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.6500884130029192</v>
+        <v>0.9103311382712462</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3342405767019514</v>
+        <v>0.6196374917291365</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4006152758103951</v>
+        <v>0.6568954271684433</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2461274132003695</v>
+        <v>0.474016673850258</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3045170575344258</v>
+        <v>0.5376538849342154</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4366233384476885</v>
+        <v>0.650721235755114</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.03449053690200543</v>
+        <v>0.1538243285261203</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1271952314692015</v>
+        <v>0.0622464997686123</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1391644394890932</v>
+        <v>0.05008926279904813</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.07954294339653956</v>
+        <v>0.107944897930345</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1740871761594747</v>
+        <v>0.0200006909329602</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.10638209396636</v>
+        <v>0.09244604803757994</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.266594007778771</v>
+        <v>-0.05965397055937416</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.3090814788084799</v>
+        <v>-0.1079376530255374</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.3577138083784774</v>
+        <v>-0.1851861228896254</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.4738553462673778</v>
+        <v>-0.2650668144293107</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.336791065930953</v>
+        <v>-0.09993137133219676</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.6112450662694044</v>
+        <v>-0.3315725496323836</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.7368305970349383</v>
+        <v>-0.456120393690675</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.900960593230181</v>
+        <v>-0.5773632636888664</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7084941638356028</v>
+        <v>-0.4734994430973174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006329</t>
+          <t>X &gt; -0.006246</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2691</v>
+        <v>2709</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7638709108953492</v>
+        <v>0.7399501386536755</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3016622239114355</v>
+        <v>0.4773031260427274</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2115875814225632</v>
+        <v>0.3780177555393749</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5154694404086939</v>
+        <v>0.6120799192893216</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.05293185321419003</v>
+        <v>0.2105128751517853</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2768120297139305</v>
+        <v>0.3513561624405881</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3381544216346626</v>
+        <v>0.4205828848230695</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.450554548500449</v>
+        <v>0.503541310880756</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6242575973567028</v>
+        <v>0.7259481200381117</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.09456127503954548</v>
+        <v>0.1713407217943939</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0203041905611272</v>
+        <v>0.0973941493897641</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.01508477839264799</v>
+        <v>0.06239526679446072</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.03053428534796154</v>
+        <v>0.1083815028901753</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1686210827672809</v>
+        <v>-0.08146712272093737</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1381579657140364</v>
+        <v>-0.04294145109759739</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2625832238651853</v>
+        <v>-0.1590282804600065</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3374910525602814</v>
+        <v>-0.2412401816396681</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.4945133941070452</v>
+        <v>-0.4261046392315819</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.7017622426276802</v>
+        <v>-0.5952749239504911</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.5673131669131095</v>
+        <v>-0.4328677157925682</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.6797411446591326</v>
+        <v>-0.4994325892048437</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8078824931299025</v>
+        <v>-0.6266473314926699</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.9943601479376554</v>
+        <v>-0.7672068025028054</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.8997519422651479</v>
+        <v>-0.7601135396856336</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.004798</t>
+          <t>X &gt; -0.004722</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2486</v>
+        <v>2505</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4326353146830471</v>
+        <v>0.610854284547635</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04034624498194006</v>
+        <v>0.18851431905059</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4975758145297959</v>
+        <v>-0.2926338414780147</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2289560366329653</v>
+        <v>0.08714241271345458</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4847784963853528</v>
+        <v>-0.1663385592887252</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0220597408915566</v>
+        <v>0.2901371986892798</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2896952233346681</v>
+        <v>0.5878562933547684</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.234418604651168</v>
+        <v>0.5039343397137799</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4990190318639947</v>
+        <v>0.8530371347923236</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.0906367909918373</v>
+        <v>0.1989385435346236</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2338913766639195</v>
+        <v>0.01752833096792017</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2091355481925845</v>
+        <v>0.04180758935167717</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3071062065907668</v>
+        <v>-0.09630848121157243</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4243848602983746</v>
+        <v>-0.2417412265349768</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1763983721854885</v>
+        <v>0.01430968646143782</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.5210613356680796</v>
+        <v>-0.2761227385601828</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5510247851168373</v>
+        <v>-0.31681263269639</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.6960100092110011</v>
+        <v>-0.4661054313264756</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7611302701975475</v>
+        <v>-0.4274275221061359</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4302156115711426</v>
+        <v>-0.06991338566044192</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.7080468329690603</v>
+        <v>-0.29495417676182</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7601226107147383</v>
+        <v>-0.346546332107259</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.9443676460661123</v>
+        <v>-0.4783649675561179</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.036810813452526</v>
+        <v>-0.6569754084177291</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003268</t>
+          <t>X &gt; -0.003198</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2278</v>
+        <v>2289</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2388390243186791</v>
+        <v>0.393359431058947</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5085502092087282</v>
+        <v>-0.2619217074752243</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8562945090029217</v>
+        <v>-0.5843532068315866</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6098067491172685</v>
+        <v>-0.460229258191184</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.771153261786651</v>
+        <v>-0.6252261328631761</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4097431158113807</v>
+        <v>-0.3576354129198123</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.09141705046492632</v>
+        <v>-0.00120111162881642</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3096716587523858</v>
+        <v>0.3257865296910794</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.419965149289574</v>
+        <v>0.5219359443161338</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1094116361955102</v>
+        <v>0.01127231878367496</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2469083075970318</v>
+        <v>-0.1259046337020919</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1071541962112335</v>
+        <v>-0.02998583207104133</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3304673144645847</v>
+        <v>-0.2937924101533014</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4383115476901907</v>
+        <v>-0.429652471548593</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.545484329276718</v>
+        <v>-0.5206579412983103</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.7569123812556313</v>
+        <v>-0.717276713510806</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.6023000462276542</v>
+        <v>-0.577997967479682</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.7509427649415272</v>
+        <v>-0.6853759352269577</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.7978634733733188</v>
+        <v>-0.6633452287859569</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5852969359924103</v>
+        <v>-0.4669141871362328</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.7952168783189748</v>
+        <v>-0.6162297598175144</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.7574430823117382</v>
+        <v>-0.5784417651827241</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.202947893012357</v>
+        <v>-1.007784317448255</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.297021284451851</v>
+        <v>-1.188180364168076</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001737</t>
+          <t>X &gt; -0.001673</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4744806342269783</v>
+        <v>0.5589357718894021</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.017044030124971</v>
+        <v>-0.735284907243873</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.222321461798963</v>
+        <v>-0.8887799628712543</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.047701516744667</v>
+        <v>-0.7701041921426324</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.334182324597656</v>
+        <v>-1.067743777607738</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9499774797231524</v>
+        <v>-0.737122729501472</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4891845462565101</v>
+        <v>-0.3299436586445168</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.04985027707346035</v>
+        <v>0.1766103676931579</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2183737036438487</v>
+        <v>0.5285740162115573</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1310839635446968</v>
+        <v>0.1039079559901595</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.02603325126126066</v>
+        <v>0.208148018384378</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1686513131582856</v>
+        <v>0.3525077882349166</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1623192912892577</v>
+        <v>0.2974777700807465</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.06956658060660459</v>
+        <v>0.1764865077961346</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.2621036936201619</v>
+        <v>-0.1324789168291716</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.2819802782655643</v>
+        <v>-0.1321982487111342</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.2673090051390261</v>
+        <v>-0.05946522309712066</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.5207381190642195</v>
+        <v>-0.3602197772443176</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5524940883132459</v>
+        <v>-0.3137933886890636</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4151777483798895</v>
+        <v>-0.1195523296218752</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.660547096137897</v>
+        <v>-0.2142656345348186</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.5088471127048635</v>
+        <v>-0.1615684635285177</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.948593886273251</v>
+        <v>-0.5796815313961901</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.144118083370415</v>
+        <v>-0.9103944961681449</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002069</t>
+          <t>X &gt; -0.0001492</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1783</v>
+        <v>1799</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.08966513601124149</v>
+        <v>0.1682033983325013</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.385094663870916</v>
+        <v>-0.9832530357616704</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.931748810394943</v>
+        <v>-1.493420290912439</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.031889459364152</v>
+        <v>-1.670872155263176</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.699156255031198</v>
+        <v>-1.420829877891848</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.512190068933819</v>
+        <v>-1.39923786057804</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8913810926570349</v>
+        <v>-0.7610232906718366</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.859583625003232</v>
+        <v>-0.7593864736721869</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7308315252021202</v>
+        <v>-0.4901248540650229</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8583491751849124</v>
+        <v>-0.7029426645298003</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5523528157062358</v>
+        <v>-0.3993156959059903</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2963365222650722</v>
+        <v>-0.2022377118867951</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.04567781599179455</v>
+        <v>-0.01329991303903455</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.17775267459632</v>
+        <v>-0.1737485186978844</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.4669937965084472</v>
+        <v>-0.4357943158432747</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.7350945060911442</v>
+        <v>-0.7281544451540256</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.02914602156806012</v>
+        <v>0.03175813008129325</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2459688082559808</v>
+        <v>-0.1792478045515082</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.5339968002319964</v>
+        <v>-0.3759574865988853</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.4031420316973353</v>
+        <v>-0.1843265952740722</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3297867438962854</v>
+        <v>-0.0525299343375778</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1481993848327434</v>
+        <v>0.09452976592935158</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.737078982684686</v>
+        <v>-0.4396135265700494</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.8359552313909617</v>
+        <v>-0.6246664854077082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001323</t>
+          <t>X &gt; 0.001375</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.202637360592952</v>
+        <v>-1.009293394777266</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.906105195204233</v>
+        <v>-2.554377459745083</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.53931141001064</v>
+        <v>-2.039222325252105</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.98488575030899</v>
+        <v>-2.663017974066712</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.451692265637007</v>
+        <v>-2.270573442155353</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.465260838897919</v>
+        <v>-2.314040637760471</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.833466207280253</v>
+        <v>-1.572716504368614</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.576918293744555</v>
+        <v>-1.239283592224773</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.765699564604702</v>
+        <v>-1.408602192064393</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.89904469536085</v>
+        <v>-1.565217458533724</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.922267059097038</v>
+        <v>-1.590398946286207</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.091190267378671</v>
+        <v>-0.891337639712674</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.103037438605433</v>
+        <v>-0.9622087050239827</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.016678849092955</v>
+        <v>-0.8361612833751479</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.8968575652464068</v>
+        <v>-0.8077356173923889</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.136363636363633</v>
+        <v>-1.0805953947266</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.4638291604378821</v>
+        <v>-0.4057736494059725</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.2998526599579847</v>
+        <v>-0.1626760522230626</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.8232085908616256</v>
+        <v>-0.5818267601707063</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4347498776677838</v>
+        <v>-0.1256963943225244</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.1036401316553253</v>
+        <v>0.1556067255859972</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.2641888387821894</v>
+        <v>0.5524603870427214</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.09378039315852504</v>
+        <v>0.1217860388753707</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6682282324805726</v>
+        <v>-0.6472309055152365</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002854</t>
+          <t>X &gt; 0.002899</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.675271966496616</v>
+        <v>-2.335299500800026</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.513827102377924</v>
+        <v>-3.288533563814468</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.44051113881445</v>
+        <v>-3.20989433237272</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.901575989491455</v>
+        <v>-3.718963197847607</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.893957561954764</v>
+        <v>-2.827854671280271</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.790954432112628</v>
+        <v>-2.670921065282187</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.471383384684763</v>
+        <v>-2.299336410848241</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.74203815437486</v>
+        <v>-1.558176787534599</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.821909339484549</v>
+        <v>-1.680456384939724</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.875344624542109</v>
+        <v>-1.679307653481573</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-2.028757624853583</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.195650788077671</v>
+        <v>-1.088599289358051</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9217925776465421</v>
+        <v>-0.9010327230512516</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6717633788695281</v>
+        <v>-0.6821473659131243</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.4016366342559934</v>
+        <v>-0.3934654483911046</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.6014537264537267</v>
+        <v>-0.6703843968807561</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.1936831906228633</v>
+        <v>0.1974972035794096</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.9334370813962707</v>
+        <v>0.8700808402624105</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.9804095434016702</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.082795893910237</v>
+        <v>1.147939517982323</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.384844320538804</v>
+        <v>1.556897675090028</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.360759228198262</v>
+        <v>1.481735153134743</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.348672916126326</v>
+        <v>1.472844385887875</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.155142363116958</v>
+        <v>1.142355223248238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004384</t>
+          <t>X &gt; 0.004423</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.436027836323532</v>
+        <v>-1.95216947164937</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.77482069893037</v>
+        <v>-3.440274857346807</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.606414045150125</v>
+        <v>-3.202431645805554</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.419769671018564</v>
+        <v>-3.993838819738151</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.647126408626079</v>
+        <v>-2.279347208593705</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.4601602225287</v>
+        <v>-2.122413602595621</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.428896055013425</v>
+        <v>-2.021973226768637</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.405902680489405</v>
+        <v>-2.227391182615072</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.962809072871885</v>
+        <v>-1.800954810244392</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.876105366857558</v>
+        <v>-1.745487009513212</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.249751052137675</v>
+        <v>-2.115548213821853</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.264116569185695</v>
+        <v>-1.239301229958457</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.8179262337418507</v>
+        <v>-0.8993607548520828</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2307899811171836</v>
+        <v>0.110147441457066</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.02372062221513715</v>
+        <v>-0.1720069404279911</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.3282828282828234</v>
+        <v>0.08929707839166667</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.8004262973659593</v>
+        <v>0.6451764264264241</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.20063609859529</v>
+        <v>1.073173844070197</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.315517378509512</v>
+        <v>1.247837316233586</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.502363188477538</v>
+        <v>1.522946695557209</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.868907929602415</v>
+        <v>1.920669395645668</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.259914517957895</v>
+        <v>2.247516923941639</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>1.787633821280323</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.875343247261128</v>
+        <v>1.62549482699086</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.005915</t>
+          <t>X &gt; 0.005947</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.28027019035504</v>
+        <v>-2.642266584052976</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.297739296397168</v>
+        <v>-4.928989746287456</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.331912191581999</v>
+        <v>-4.142867521648427</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.165058518717053</v>
+        <v>-5.215461797287382</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.337387452802787</v>
+        <v>-3.210107572440741</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.549459728243868</v>
+        <v>-2.212837831988871</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.879100719826532</v>
+        <v>-1.687391632937079</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.037119856887294</v>
+        <v>-1.872264057138011</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.356209598049517</v>
+        <v>-2.224527224284635</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.10033118910961</v>
+        <v>-1.993533285945936</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.361263500320746</v>
+        <v>-2.376498215801469</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.125632099490105</v>
+        <v>-1.141184210984356</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.489209543699765</v>
+        <v>-0.6199055899928183</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.569875609084491</v>
+        <v>0.4096643496696259</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.08826768849606736</v>
+        <v>-0.2724900322154298</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.3365984298187712</v>
+        <v>0.1680410397443239</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.6869427940519444</v>
+        <v>0.7403138855300213</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.8242328408360962</v>
+        <v>0.8009587116261372</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.161189597063085</v>
+        <v>0.8457826674387121</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.711231532939102</v>
+        <v>1.424005476134063</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.652946866183726</v>
+        <v>1.536466829416462</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.015284190415535</v>
+        <v>1.825381977364096</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.00085040039685</v>
+        <v>1.826298016040532</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.513900875529465</v>
+        <v>1.300081351848149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007445</t>
+          <t>X &gt; 0.007472</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.403129205349551</v>
+        <v>-3.148925940709027</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.164213452193827</v>
+        <v>-5.284596555940453</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.798745971906271</v>
+        <v>-2.917243413737545</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.304093018290374</v>
+        <v>-4.297047187348916</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.15335417229565</v>
+        <v>-1.265518713275021</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3324735646451913</v>
+        <v>-0.6361441623950483</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1535506162058979</v>
+        <v>-0.1713836549427299</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.590240666347249</v>
+        <v>-0.7912647282726013</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.499625116762182</v>
+        <v>-1.765698023312915</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.07288290534364</v>
+        <v>-1.370959881432476</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.980088562094075</v>
+        <v>-2.27384110765221</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.8554978014726018</v>
+        <v>0.5428938735055056</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.580688521621632</v>
+        <v>1.263294339657207</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.734634485812805</v>
+        <v>2.379988711298338</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.9582803256124421</v>
+        <v>0.7454533770323266</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.712411656501118</v>
+        <v>1.465487554582147</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.738238928469329</v>
+        <v>1.616736221515623</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.633398224648147</v>
+        <v>1.580558039212065</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.849289605572473</v>
+        <v>1.892034661059128</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.876391006594815</v>
+        <v>1.947131472944264</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.45205570124859</v>
+        <v>2.496114403780446</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.315890251021592</v>
+        <v>2.261462248651313</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.950364963503652</v>
+        <v>1.867138201234319</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>1.545509573771007</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.008976</t>
+          <t>X &gt; 0.008996</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.240847113431968</v>
+        <v>-3.244415992524118</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.575623911781783</v>
+        <v>-5.478394398804525</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.21364296081277</v>
+        <v>-3.154559673658341</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.526596980255512</v>
+        <v>-3.349347558351248</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.662387452802783</v>
+        <v>-1.636834127874039</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1245787332945838</v>
+        <v>0.1105567345852734</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.3526300494042403</v>
+        <v>0.3095105076408302</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4744186046511629</v>
+        <v>0.4022043783475127</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6840942134341361</v>
+        <v>-0.6627096543142983</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7423806309535834</v>
+        <v>-0.7494710732582206</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.758853861766532</v>
+        <v>-1.761122469099931</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.099266144011921</v>
+        <v>1.873273620340946</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.508686669483964</v>
+        <v>2.480625991868123</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.624362436243622</v>
+        <v>3.359143425392809</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.350057522501452</v>
+        <v>1.271366553547914</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.944444444444443</v>
+        <v>1.832670572367576</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.224668721608388</v>
+        <v>3.259662139503682</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.513767411726597</v>
+        <v>2.523156303959794</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.133699196691332</v>
+        <v>3.14003301802709</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.320545006659358</v>
+        <v>3.354619463086074</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.788099848794332</v>
+        <v>3.79321117900917</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.308213483344829</v>
+        <v>3.315634170132356</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.178647791786481</v>
+        <v>3.156854168489197</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.698775134522805</v>
+        <v>2.592300687278204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01051</t>
+          <t>X &gt; 0.01052</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.76553539273371</v>
+        <v>-3.419169937987142</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.095324659911455</v>
+        <v>-6.134212576160152</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.044565654079605</v>
+        <v>-2.944462233607275</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.256272790729327</v>
+        <v>-4.277605173156246</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.599544560034701</v>
+        <v>-1.590200350292619</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6644486981268543</v>
+        <v>-0.6925260035537946</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3092385282072385</v>
+        <v>-0.006126534305032294</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.2804036420576494</v>
+        <v>-0.0641333974667404</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1768622932346346</v>
+        <v>-0.4300316482764543</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4429901105293794</v>
+        <v>0.1508878869405805</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.893225936531756</v>
+        <v>-2.163295789952024</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.234782761303606</v>
+        <v>0.9309850631270109</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.02420629246275</v>
+        <v>1.707508684935071</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.715271527152723</v>
+        <v>2.360147441457073</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.7945019669458944</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.893939393939398</v>
+        <v>1.489297078391672</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.517598014537683</v>
+        <v>2.135416666666671</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.907706805665988</v>
+        <v>1.50253256150507</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.376123439115574</v>
+        <v>1.966994788650837</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.310443996558341</v>
+        <v>1.931581233709828</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.283049343743826</v>
+        <v>2.864136732329094</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.207203382334725</v>
+        <v>2.788974210373809</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.966526579665263</v>
+        <v>1.532608695652186</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.38564382139149</v>
+        <v>0.8704697013627154</v>
       </c>
     </row>
     <row r="28">
@@ -4988,79 +4988,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.759057976051771</v>
+        <v>-4.498040740849454</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.330256499641209</v>
+        <v>-7.291718277190263</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.336965644518841</v>
+        <v>-3.132399640228343</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.369408481852965</v>
+        <v>-4.043273176616182</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.468777229160615</v>
+        <v>-2.089531953658195</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.962322225171867</v>
+        <v>-1.614127010080495</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4978491838225949</v>
+        <v>-0.179909659255884</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1370829927929265</v>
+        <v>0.1521125724947296</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.734573446660967</v>
+        <v>-0.3569011929803949</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.04418937665010247</v>
+        <v>0.3050965985465623</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.47748400936657</v>
+        <v>-2.298067747871457</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6423448120470141</v>
+        <v>-0.6577167949945206</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6088099376775347</v>
+        <v>-0.8141424587711725</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.00964382152501031</v>
+        <v>-0.4233988844215233</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.297850125406192</v>
+        <v>-1.744530902089338</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.05411255411255667</v>
+        <v>-0.5442492474869169</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.1366456335852959</v>
+        <v>-0.3286408413205564</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.2928703949112119</v>
+        <v>-0.781013764373526</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.5723716353637656</v>
+        <v>0.07242609855499182</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.408568094682437</v>
+        <v>0.9259901793967202</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.489398550093036</v>
+        <v>1.955989767472857</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.439526614657964</v>
+        <v>0.9223607918434453</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4153000284387147</v>
+        <v>-0.1119599944436658</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.6641430998907722</v>
+        <v>0.04538982915823908</v>
       </c>
     </row>
     <row r="29">
@@ -5070,571 +5070,571 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.057513780098631</v>
+        <v>-3.959293394777262</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-6.475623911781781</v>
+        <v>-6.288533563814468</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.663642960812773</v>
+        <v>-1.293227665706048</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.793263646922178</v>
+        <v>-2.302296531180936</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.045720786136116</v>
+        <v>-0.4945213379469351</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.692087933372079</v>
+        <v>-1.170921065282194</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.8692967160709131</v>
+        <v>1.36733025581843</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.007751937984501</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.03409421343413</v>
+        <v>-0.476327944572752</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2763234438627151</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.949616913975362</v>
+        <v>-1.41681109185442</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.228366317423358</v>
+        <v>-1.693393046325717</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.862685985395238</v>
+        <v>-1.558285163776496</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.246944778159815</v>
+        <v>-0.9731858918762626</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.905088075740373</v>
+        <v>-1.655340273761318</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.05547102827437556</v>
+        <v>0.1559637450583367</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.6474319184301649</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.7126389109140305</v>
+        <v>-0.4974674384949367</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.7584825955333088</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.782148489183342</v>
+        <v>2.014914567043149</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.076422404899311</v>
+        <v>2.280803398995758</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.00057644349021</v>
+        <v>2.205640877040473</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.6014109886082579</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.9439887772259823</v>
+        <v>1.03713636802938</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.0151</t>
+          <t>X &gt; 0.01509</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.384436857021711</v>
+        <v>-3.286216471700342</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.744854681012548</v>
+        <v>-4.557764333045235</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.02902757619738594</v>
+        <v>0.3413877189093384</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7419815956401266</v>
+        <v>-0.2510144798988847</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.486330495915169</v>
+        <v>2.03752994410435</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.160476169192023</v>
+        <v>1.681643037281908</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.978271075045271</v>
+        <v>4.476304614792788</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.187239117471677</v>
+        <v>3.658563658563651</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6646237352838256</v>
+        <v>1.222390004145204</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.430169597708868</v>
+        <v>1.964800047387399</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.372693837052289</v>
+        <v>-0.839888014931347</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.164263753320796</v>
+        <v>-1.629290482223155</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.45290295472622</v>
+        <v>-1.205721061212394</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1275900785954818</v>
+        <v>0.08450641581604401</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.301197293701811</v>
+        <v>-1.110468478889523</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.839581380818494</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.221128161366792</v>
+        <v>1.398237179487175</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.6008235400198387</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.332178838469936</v>
+        <v>1.479815301471348</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.034488565963741</v>
+        <v>2.20722225935085</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.553798068100797</v>
+        <v>3.69105980925216</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.477952106691696</v>
+        <v>3.615897287296875</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.6596433140191138</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.5838110607958384</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01663</t>
+          <t>X &gt; 0.01662</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>150</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.642290578448453</v>
+        <v>-2.45520023048114</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.919690372520563</v>
+        <v>2.290105667627287</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.87340301974448</v>
+        <v>2.364370135485721</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.870945880530542</v>
+        <v>5.422145328719722</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.952630049404242</v>
+        <v>5.450663589151759</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.341085271317837</v>
+        <v>5.812409812409811</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.276323443862708</v>
+        <v>3.810953893541239</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4496169139753619</v>
+        <v>0.08318890814557989</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.7283663174233581</v>
+        <v>-0.193393046325717</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.48180494905386</v>
+        <v>2.025048169556847</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.26072607260727</v>
+        <v>3.776814108123737</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.93591610836004</v>
+        <v>2.42799305957201</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.196969696969703</v>
+        <v>3.655963745058344</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.729719226658887</v>
+        <v>4.218749999999993</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>2.958211856171047</v>
+        <v>3.419199228171735</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.84076990376203</v>
+        <v>4.300328121984165</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>4.694282380396729</v>
+        <v>5.181581233709821</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.485069545764027</v>
+        <v>5.947470065662415</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.075890251021598</v>
+        <v>6.538974210373802</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.017031630170322</v>
+        <v>3.449275362318851</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.274532710280376</v>
+        <v>4.620469701362715</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01816</t>
+          <t>X &gt; 0.01814</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.3168202764977011</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.308928933746678</v>
+        <v>1.050176113604884</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.748958665203496</v>
+        <v>4.634191689132663</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.40998838559814</v>
+        <v>3.235337877421216</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.57826295370127</v>
+        <v>8.604941027644458</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.326204749554748</v>
+        <v>7.148971407836093</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.554256065664397</v>
+        <v>6.353889395603375</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.715069011155222</v>
+        <v>8.468323790904421</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.504523672744732</v>
+        <v>5.370446248975632</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.357624256870842</v>
+        <v>6.18729797956275</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.8723811416176446</v>
+        <v>0.00792009094128332</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3381224149843334</v>
+        <v>0.5377897493732107</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.79074803848475</v>
+        <v>2.648704083535335</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.008693552282061</v>
+        <v>4.819824860811906</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.350550254701503</v>
+        <v>4.13767047892685</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>3.944937176644494</v>
+        <v>4.698974497746512</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.811020039667021</v>
+        <v>4.595094086021504</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.893171205764531</v>
+        <v>3.655758367956679</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.922070716770165</v>
+        <v>4.676672208005677</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>4.921924656819499</v>
+        <v>5.697710265967885</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>5.192386618934755</v>
+        <v>5.936717377490368</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.474458081341545</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>4.578007239926421</v>
+        <v>5.298737727910243</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.502174986703146</v>
+        <v>5.136598733620779</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01969</t>
+          <t>X &gt; 0.01967</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.8630693356541883</v>
+        <v>-0.8153540008378783</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6540057178478449</v>
+        <v>0.7569209816400715</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.771542224372411</v>
+        <v>4.956772334293952</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.05858820492967</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.426501436086099</v>
+        <v>8.63426654084094</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.909763918479776</v>
+        <v>5.154836510475391</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.137815234589425</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.711455641688204</v>
+        <v>5.873015873015873</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.049239119899205</v>
+        <v>2.364581146336342</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.054101221640494</v>
+        <v>4.295802378389723</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-0.8865080615513961</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.58021816927522</v>
+        <v>-0.2539991069317793</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.852175319424227</v>
+        <v>3.176563321071988</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.482948294829484</v>
+        <v>4.746511077820699</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>3.824804997248926</v>
+        <v>4.973447605026557</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.345117845117841</v>
+        <v>6.443842532937126</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.285274782214444</v>
+        <v>5.430871212121211</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.254508152467338</v>
+        <v>4.388896197868696</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.396325459317588</v>
+        <v>5.512449334105384</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.583171269285614</v>
+        <v>5.727035779164368</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>4.966551027245508</v>
+        <v>6.06868218687454</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.811701483101068</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.165179778318461</v>
+        <v>6.237154150197632</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.015273451021123</v>
+        <v>6.984106064999089</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.02122</t>
+          <t>X &gt; 0.02119</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3799775482145691</v>
+        <v>-0.2817571628932001</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.633071740392133</v>
+        <v>3.820162088359446</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.629835300056797</v>
+        <v>8.000250595163521</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.829924758874917</v>
+        <v>6.320891874616159</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.306203299734221</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.594143950685904</v>
+        <v>5.115310818775789</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.822195266795553</v>
+        <v>4.320228806543071</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.630940343781596</v>
+        <v>5.10226488487357</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3246014387397835</v>
+        <v>0.882367707601162</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.725598806181551</v>
+        <v>2.260229255860082</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.348167638613042</v>
+        <v>-1.8153618164921</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.6339525231563528</v>
+        <v>1.168925794253994</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.945573064995877</v>
+        <v>5.488816285498864</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.898407232027552</v>
+        <v>7.414495267544019</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.240263934446993</v>
+        <v>6.732340885658964</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.921607378129124</v>
+        <v>8.380601426217765</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>6.700733719412511</v>
+        <v>7.189764492753618</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.508936493852204</v>
+        <v>5.969923865852891</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.72482787477653</v>
+        <v>6.184386092998665</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.824717163005417</v>
+        <v>5.312016016318509</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>6.456084038517652</v>
+        <v>6.91848455841604</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>8.554151120586816</v>
+        <v>9.01723507993902</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>6.654712789590604</v>
+        <v>7.086956521739133</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>6.578880536367329</v>
+        <v>6.924817527449669</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02275</t>
+          <t>X &gt; 0.02271</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.880892017002814</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>8.34321666792836</v>
+        <v>7.640037864756962</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>14.15157443049157</v>
+        <v>13.52820090572252</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>11.98934504873</v>
+        <v>11.50722727834287</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>14.5521053008204</v>
+        <v>14.08881199538639</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.94197003764242</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>9.164949303437467</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>8.860028860028848</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.034746366276011</v>
+        <v>4.702243483998679</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.160381414877207</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.637339607763764</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.257140928953447</v>
+        <v>5.330416477483801</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6.032529586735016</v>
+        <v>7.072667217175884</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>8.710001434926113</v>
+        <v>9.681576012885635</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.570850202429149</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>8.646245059288546</v>
+        <v>9.560725649820242</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.41087864694875</v>
+        <v>12.31398809523809</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.85676258080872</v>
+        <v>9.323961132933633</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>10.07265396173305</v>
+        <v>9.538423360079406</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>8.810224409382243</v>
+        <v>8.32443837656696</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>9.716953603735043</v>
+        <v>9.185565303757656</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>11.09038300464479</v>
+        <v>10.5389742103738</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>8.466306992489166</v>
+        <v>7.925465838509318</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>9.83975010158472</v>
+        <v>10.62046970136272</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1805 +5824,1805 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02163</t>
+          <t>X &lt; -0.02149</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.264035519229068</v>
+        <v>-9.256912442396313</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-8.074247849528753</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.138280641972187</v>
+        <v>-6.471799094277479</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.300510023733771</v>
+        <v>-7.064201293085702</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.839199047005678</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.9236445421578665</v>
+        <v>2.022092160580335</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.253117627232889</v>
+        <v>-1.139971139971145</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.110181169955872</v>
+        <v>-3.869185087429891</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-5.883096845992362</v>
+        <v>-4.665236582649229</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.609037203830439</v>
+        <v>-5.821572996616332</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.438511244959585</v>
+        <v>-4.669583522516191</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2354281374596496</v>
+        <v>-0.07018992568124816</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.46362462333191</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.8054813257513516</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.399868247694343</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1833242516019808</v>
+        <v>-0.5431547619047592</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>-0.6760388670663602</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.826277150138843</v>
+        <v>2.395566217222267</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>6.328422446614795</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>6.25325992465951</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.915582354807995</v>
+        <v>9.354037267080749</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>9.83975010158472</v>
+        <v>9.191898272791285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.0201</t>
+          <t>X &lt; -0.01996</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>98</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.702071603227886</v>
+        <v>-8.644667544437127</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-6.849758053610387</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.393234797547464</v>
+        <v>-7.084043992236666</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.044964327194286</v>
+        <v>-4.615221701248963</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.741694179850278</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.989884855743576</v>
+        <v>4.449827234037542</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.238344335118533</v>
+        <v>4.675153385070125</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.939724727100149</v>
+        <v>3.349824778396204</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.960803745749544</v>
+        <v>2.457345524815004</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.167479906447745</v>
+        <v>0.6408858663303576</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.400723222079058</v>
+        <v>-1.127695445595926</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.142381981896371</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.039628078305554</v>
+        <v>-0.4783531909873773</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.900181854920191</v>
+        <v>3.355045400640741</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>5.242038557339633</v>
+        <v>2.672891018755685</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.836425479282624</v>
+        <v>3.234195037575347</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>2.641283852509233</v>
+        <v>0.06909013605442027</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.516034985422742</v>
+        <v>0.9566141941581279</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>1.731926366347068</v>
+        <v>1.171076421303901</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.918772176315095</v>
+        <v>1.385662866362885</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.43745049814499</v>
+        <v>3.87944285477807</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>5.382012700001191</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>7.697303739013847</v>
+        <v>7.109139307897074</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>7.621471485790572</v>
+        <v>6.94700031360761</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01857</t>
+          <t>X &lt; -0.01844</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.840847113431963</v>
+        <v>-11.73934803958601</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.975623911781781</v>
+        <v>-10.3459106129948</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.013642960812774</v>
+        <v>-9.141588321443756</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.326596980255509</v>
+        <v>-7.274974126809354</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3376125471972102</v>
+        <v>-3.452171611170982</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.524578733294589</v>
+        <v>0.8031226505648021</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.952630049404242</v>
+        <v>3.286729162922249</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.074418604651164</v>
+        <v>1.342464457218547</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>-0.9886230265399689</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.142990110529375</v>
+        <v>-2.604346652906841</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.617049752691301</v>
+        <v>-3.151783769450049</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.261699650756697</v>
+        <v>-5.067709986216428</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.784861717612813</v>
+        <v>-4.543257841372117</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.394059405940595</v>
+        <v>-2.33247550936261</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.535916108360041</v>
+        <v>-2.194957760100124</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.330303030303028</v>
+        <v>-2.453325872428003</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.4036141066744463</v>
+        <v>-4.196550546448087</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-1.308454810495626</v>
+        <v>-3.509762520462154</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-2.692563429571301</v>
+        <v>-4.934644555611456</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.9057176196032728</v>
+        <v>-3.080713848257396</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.9517362124306956</v>
+        <v>-1.189141956195506</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.675890251021599</v>
+        <v>0.3750397841442918</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.950364963503652</v>
+        <v>-0.200997861724872</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.874532710280377</v>
+        <v>0.4565352751332057</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01704</t>
+          <t>X &lt; -0.01692</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-7.065504647678544</v>
+        <v>-8.337147276055809</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.400281446028359</v>
+        <v>-9.952917125458306</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.358848440264829</v>
+        <v>-6.413090679404675</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.701939446008936</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9829353980082658</v>
+        <v>-3.856393484065663</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.313619829185008</v>
+        <v>0.4101291630283157</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.966328679541228</v>
+        <v>3.039704685042175</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.003185727938842</v>
+        <v>2.049852734784238</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.304946882456285</v>
+        <v>-0.5619443829289139</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.216962713269105</v>
+        <v>-0.6730643712989348</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.806090848581718</v>
+        <v>-1.085760863543918</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1574784314350879</v>
+        <v>-2.732205831713848</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.089110885126914</v>
+        <v>-1.79230342861667</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.922826529228274</v>
+        <v>-0.6706744763511523</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.579751724798399</v>
+        <v>-1.352828858236208</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.17413864674139</v>
+        <v>-0.7915248394165459</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6703584960652833</v>
+        <v>-2.265268264840181</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.5655177922441013</v>
+        <v>-1.028289356303155</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.09647766631911736</v>
+        <v>-1.498758636006698</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.653186489985771</v>
+        <v>0.08569082275091944</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.850366349417001</v>
+        <v>1.573040841918129</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.7745203880079</v>
+        <v>2.867741333661478</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.733926607339271</v>
+        <v>3.111375818939855</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.658094354115995</v>
+        <v>4.319099838349018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01551</t>
+          <t>X &lt; -0.01539</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.127034958735834</v>
+        <v>-7.890452815067121</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.014297944930952</v>
+        <v>-9.223316172510124</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.242372242580728</v>
+        <v>-8.304097230923439</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.850353886332854</v>
+        <v>-8.353021168862099</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.766254856117698</v>
+        <v>-4.280753222004918</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.393087020587416</v>
+        <v>0.767484731819259</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.383569275923577</v>
+        <v>3.233272284803931</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.342926891943989</v>
+        <v>0.2109605370474839</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1744693224774707</v>
+        <v>-1.835023596746666</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.506526022131581</v>
+        <v>-1.000640309357308</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2280994764482074</v>
+        <v>-1.271883555622537</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6031361148450927</v>
+        <v>-2.635422031832967</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6213258060106099</v>
+        <v>-2.663357627544606</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.8150538810787182</v>
+        <v>-1.28115690636902</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3955756043471368</v>
+        <v>-2.506789549123646</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.1988113175958546</v>
+        <v>-1.945485530303984</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.4875920072269224</v>
+        <v>-2.592844202898554</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.0650258524878</v>
+        <v>0.5351412571572354</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.833403421257429</v>
+        <v>1.293081745172579</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.57273541907076</v>
+        <v>2.051146451101133</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.240134002485952</v>
+        <v>3.657614993198656</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.164288041076851</v>
+        <v>4.125930732112934</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>6.096221317094816</v>
+        <v>5.456521739130444</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.810444312490326</v>
+        <v>4.207426223101848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01398</t>
+          <t>X &lt; -0.01387</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.533409096903043</v>
+        <v>-7.574884792626726</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.215293333269386</v>
+        <v>-5.804662596072532</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.240089241804505</v>
+        <v>-7.462582504415721</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.953043261247245</v>
+        <v>-7.651758896772336</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.156602328835845</v>
+        <v>-4.298284778807158</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3361489812284759</v>
+        <v>-1.721996334099394</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.696431702296799</v>
+        <v>1.515179718184022</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.352104555064393</v>
+        <v>-0.4026439510310453</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1539223154914851</v>
+        <v>-1.484392460701791</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.033899201438473</v>
+        <v>-0.6675407301146663</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4815125626086498</v>
+        <v>-0.3953057155103323</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.036906262326944</v>
+        <v>-2.284790895788092</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.33362204819133</v>
+        <v>-2.996457206787248</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5114147778414235</v>
+        <v>-1.228562235962286</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.5599516602350008</v>
+        <v>-2.313942424298951</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.3787878787878753</v>
+        <v>-1.752638405479289</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.9259281562612145</v>
+        <v>-2.259744623655912</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.448569982892799</v>
+        <v>0.4299519163437751</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.490907644808871</v>
+        <v>1.450865756392773</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.677753454776898</v>
+        <v>1.665452201451757</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.614546129786071</v>
+        <v>3.517362538780702</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.365146449368716</v>
+        <v>4.65187743618025</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>6.87929058333836</v>
+        <v>5.701963534361859</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.737342627635748</v>
+        <v>4.330147120717555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01245</t>
+          <t>X &lt; -0.01234</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.474734156621338</v>
+        <v>-4.841328026811894</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.480607300486099</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.915304090380879</v>
+        <v>-6.991279613757996</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.299354455338573</v>
+        <v>-5.96030518918959</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.64178944615827</v>
+        <v>-4.937162030587636</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.199661789772996</v>
+        <v>-0.8841245284856498</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.749972242095268</v>
+        <v>2.541572680060852</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.478405315614616</v>
+        <v>-0.03607503607504015</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8554406702868036</v>
+        <v>-0.8821721004169092</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.079202735114094</v>
+        <v>-0.0548469722596252</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0243587227909714</v>
+        <v>-1.405988581031913</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.583294335142071</v>
+        <v>-2.981271834204513</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-4.096163951655285</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9341797967172027</v>
+        <v>-3.045696714387091</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.592323094297761</v>
+        <v>-3.727851096272147</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.9979361723547697</v>
+        <v>-3.166547077452485</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.7996273957109921</v>
+        <v>-2.945752164502167</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.088887382195402</v>
+        <v>-0.8059089969364948</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.637004676740993</v>
+        <v>-0.2667714451153955</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.82385048670902</v>
+        <v>0.597165649294233</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.606885714091831</v>
+        <v>2.627123745316098</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.527717493546511</v>
+        <v>3.52598719738679</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>5.798869946892353</v>
+        <v>4.743647656691145</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.729682211941508</v>
+        <v>3.282807363700378</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01092</t>
+          <t>X &lt; -0.01082</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.30397708690677</v>
+        <v>-4.466109577714825</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.516737970137221</v>
+        <v>-2.865050714210248</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.220009008558129</v>
+        <v>-5.175153787078081</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.402459049221029</v>
+        <v>-5.767555985886304</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.146737585428781</v>
+        <v>-4.460000669521257</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.164015431161637</v>
+        <v>-3.511510335290978</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5123117470169731</v>
+        <v>-1.140365434594941</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.03115168712601957</v>
+        <v>-1.44528587800356</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.050672462771004</v>
+        <v>-2.372765939295704</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.03317578692195156</v>
+        <v>-1.057999492562544</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.284276507255647</v>
+        <v>-2.368877934422585</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.828277900093568</v>
+        <v>-2.90931213163794</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.420935988169845</v>
+        <v>-3.496499763600589</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.581006907056747</v>
+        <v>-2.689324854057439</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.769654183417146</v>
+        <v>-3.899183721430632</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.910015272084237</v>
+        <v>-3.074027459866905</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.043932409061711</v>
+        <v>-3.177907871591913</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.8225131659332874</v>
+        <v>-1.463826277545067</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.07611780622912789</v>
+        <v>-0.721659564911171</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1545239856510108</v>
+        <v>-0.7709253625962518</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.159693772112398</v>
+        <v>0.5085958352314606</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.940611736432743</v>
+        <v>2.54425125522868</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.010842417084547</v>
+        <v>3.315590225995194</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.343498227521756</v>
+        <v>2.098042260729471</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.009389</t>
+          <t>X &lt; -0.009294</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.099180446765303</v>
+        <v>-5.509500434114742</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-4.306131907499768</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.913642960812773</v>
+        <v>-4.111550647072512</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.251596980255506</v>
+        <v>-5.532110195777207</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.337387452802787</v>
+        <v>-4.56543231103182</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.525421266705408</v>
+        <v>-3.787380692611386</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.214036617262423</v>
+        <v>-2.719108667577018</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.700581395348834</v>
+        <v>-3.231068448459752</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.909094213434138</v>
+        <v>-4.138336226146258</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.973676556137292</v>
+        <v>-2.035836996727909</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4912835806420333</v>
+        <v>-1.556562644649453</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7700329840900295</v>
+        <v>-1.83314459912075</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.476528384279483</v>
+        <v>-2.533958041623286</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2392739273927376</v>
+        <v>-1.332916740737545</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.4807505583066245</v>
+        <v>-1.186913772726129</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.3219696969696955</v>
+        <v>-0.4185704164323383</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1880525599922223</v>
+        <v>-0.729490165631475</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.333211856171047</v>
+        <v>1.000979766474011</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.757436570428709</v>
+        <v>1.422481331093898</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.319282380396722</v>
+        <v>1.015949763730518</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.235069545764034</v>
+        <v>1.897780624668634</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.617556917688262</v>
+        <v>3.478932802506307</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.725364963503651</v>
+        <v>4.343685300207049</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.56619937694704</v>
+        <v>2.52523160612462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.007859</t>
+          <t>X &lt; -0.00777</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.063858957763607</v>
+        <v>-4.218302403786275</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.522155214658262</v>
+        <v>-2.606101131382033</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.775741099560662</v>
+        <v>-2.847281719760105</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.503923545399346</v>
+        <v>-4.622116351000763</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.978461902887382</v>
+        <v>-3.039566382991985</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.299109929987978</v>
+        <v>-3.389389533750652</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.548215974284425</v>
+        <v>-2.664201275713111</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.8264274190375</v>
+        <v>-2.969121719121731</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.461759188053421</v>
+        <v>-3.347949566194373</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1889895849020959</v>
+        <v>-1.103460520873178</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2542747949924902</v>
+        <v>-0.6623065873499172</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3139348670097988</v>
+        <v>-0.6010507039833755</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.03679648881697517</v>
+        <v>-0.8713482268395509</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4925365633010088</v>
+        <v>-0.4439066125969902</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1728027411857553</v>
+        <v>-0.7882231566442073</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.9363944008614098</v>
+        <v>-0.05800021890563301</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.140886739349241</v>
+        <v>0.1759572072072046</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.374455510993378</v>
+        <v>0.7187487777212809</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.928756367383009</v>
+        <v>1.271048842704893</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.269578488687763</v>
+        <v>0.6410406931692805</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.588284435780949</v>
+        <v>1.931704299896651</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.189257425302472</v>
+        <v>2.701136372535963</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.9713463509825</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.049490409095945</v>
+        <v>2.613712944605957</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006329</t>
+          <t>X &lt; -0.006246</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.886388951566396</v>
+        <v>-2.794327408382699</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.163552581191929</v>
+        <v>-1.679690026399506</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.9554810952434991</v>
+        <v>-1.437785488835303</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.217131959679385</v>
+        <v>-2.438350952949648</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4953092635023779</v>
+        <v>-0.8091471882870849</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.330366321650459</v>
+        <v>-1.468540112901238</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.552864456090262</v>
+        <v>-1.855458859827834</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.968438538205973</v>
+        <v>-2.160379303236454</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.613764543104466</v>
+        <v>-2.848776924164589</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6394274718882045</v>
+        <v>-0.9237399840097709</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3653678297262815</v>
+        <v>-0.6515049694054369</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2320293210863582</v>
+        <v>-0.5199236585706188</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3936529264040161</v>
+        <v>-0.6824348236404418</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3468066586878464</v>
+        <v>0.02171206730741204</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.2381139105578356</v>
+        <v>-0.1162246275028238</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.6951381951381919</v>
+        <v>0.3090249695481333</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.9733089702486311</v>
+        <v>0.6133078231292544</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.555281453240646</v>
+        <v>1.432804670348602</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.320623383615519</v>
+        <v>2.191484584569203</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.820656006770363</v>
+        <v>1.725798920784655</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.239648300342786</v>
+        <v>2.11073537178487</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.713252888384233</v>
+        <v>2.715844958673117</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.399815512954198</v>
+        <v>3.231588287488918</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.049257985005646</v>
+        <v>3.069449293199455</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.004798</t>
+          <t>X &lt; -0.004722</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.188821527078019</v>
+        <v>-1.678941957077583</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.07554879610734844</v>
+        <v>-0.4339009759550407</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.196165141532646</v>
+        <v>0.760819192653905</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3766013139875568</v>
+        <v>-0.3640643693066039</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.06162535402752</v>
+        <v>0.4253402168986469</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2925152837994247</v>
+        <v>-0.9086739939296891</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.00458920193266</v>
+        <v>-1.810252278792859</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8549931600547183</v>
+        <v>-1.582691359049193</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.562169079744287</v>
+        <v>-2.413228903039212</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.01785642068980309</v>
+        <v>-0.7598661277580092</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3988679345094823</v>
+        <v>-0.2746385678927581</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3340222743769985</v>
+        <v>-0.3382279771031449</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6012345390716831</v>
+        <v>0.03782772227250319</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9149150209138526</v>
+        <v>0.4285712966221382</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.2567717233332942</v>
+        <v>-0.2535830852629175</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.172014260249554</v>
+        <v>0.5207134788176546</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.252000866587586</v>
+        <v>0.6298256123535637</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.640581592073964</v>
+        <v>1.135919142974707</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.815046431093229</v>
+        <v>1.137388824859563</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.9300808798608244</v>
+        <v>0.2870125436139759</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.673708345335314</v>
+        <v>0.9975233137987303</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.8122246561663</v>
+        <v>1.241849609734821</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.301061640888427</v>
+        <v>1.591980367643664</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.546772796025287</v>
+        <v>1.962322736506486</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003268</t>
+          <t>X &lt; -0.003198</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5049586116898084</v>
+        <v>-0.8153540008378783</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.989532882643303</v>
+        <v>0.5837608084799015</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.604665670399086</v>
+        <v>1.147248524770141</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.028725881873626</v>
+        <v>0.8145865857021803</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.354206433660096</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.6301731388889991</v>
+        <v>0.6093819650208374</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.004500309300922822</v>
+        <v>-0.1857000472118813</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8076461372560999</v>
+        <v>-0.8369408369408404</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.028626146942443</v>
+        <v>-1.141912360157171</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.03572851822841727</v>
+        <v>-0.2063621237747668</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3097881603903403</v>
+        <v>0.06587289082956715</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.03103875694234404</v>
+        <v>-0.1241289770616518</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4826798396925227</v>
+        <v>0.4060005505092263</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6990462825810155</v>
+        <v>0.677247008556634</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.9157936236706306</v>
+        <v>0.8608934924724494</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.335202417879579</v>
+        <v>1.249037338131927</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.026307153168084</v>
+        <v>0.9719967532467493</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.324820145721539</v>
+        <v>1.27201308098558</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.418917727308632</v>
+        <v>1.313315134971184</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.992266604761312</v>
+        <v>1.008421060549651</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.413787045033672</v>
+        <v>1.393357511549866</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.337941083624571</v>
+        <v>1.404775076174666</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.225912728621971</v>
+        <v>2.254470167513645</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.413007732190977</v>
+        <v>2.52523160612462</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001737</t>
+          <t>X &lt; -0.001673</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7038336668643836</v>
+        <v>-0.8294484335369461</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.438388827071719</v>
+        <v>1.109281799117177</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.668510013691481</v>
+        <v>1.264030967133984</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.350369710035061</v>
+        <v>1.023989585802852</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.764562901807146</v>
+        <v>1.523625244153131</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.212158577155485</v>
+        <v>0.9758372151970178</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5520618675860618</v>
+        <v>0.32169952995514</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2233086680761076</v>
+        <v>-0.4060538944259946</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4659123952523103</v>
+        <v>-0.8419022927052424</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.03958101962028593</v>
+        <v>-0.2989826815116174</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1124957018541579</v>
+        <v>-0.4495806478797917</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3912451053021542</v>
+        <v>-0.6556904388556717</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3780435357946317</v>
+        <v>-0.5725557768843217</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.2440087758775817</v>
+        <v>-0.3979568573449086</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.2342115629055002</v>
+        <v>0.04744337669674081</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2604166666666643</v>
+        <v>0.04497008755305387</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.2400248414421213</v>
+        <v>-0.05891032417195419</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.6044897129752087</v>
+        <v>0.4424550421252107</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6497853248770937</v>
+        <v>0.4455007787847407</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.4521171382314861</v>
+        <v>0.2372542428712023</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.8074739173487302</v>
+        <v>0.4450035399400818</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.5890762809574497</v>
+        <v>0.4403131814802137</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.219930180894963</v>
+        <v>1.036308484235697</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.500477115127133</v>
+        <v>1.437946797909582</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002069</t>
+          <t>X &lt; -0.0001492</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1636</v>
+        <v>1645</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1171533102727906</v>
+        <v>-0.2052480873338993</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.492176817258311</v>
+        <v>1.126514979874848</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.033165549825533</v>
+        <v>1.631529615847349</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.085081851861275</v>
+        <v>1.767282756844956</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.723857221573354</v>
+        <v>1.552404228396099</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.519950231467554</v>
+        <v>1.466619387792242</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8441596045535462</v>
+        <v>0.7062798611614696</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.809701968453723</v>
+        <v>0.7049416885482387</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6683737938784873</v>
+        <v>0.4685718732778881</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8095349002917231</v>
+        <v>0.6439836446037788</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4742100208204931</v>
+        <v>0.3090541176173431</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.1954606173724969</v>
+        <v>0.09318861730511685</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.07456311919720804</v>
+        <v>-0.1109566877594901</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.0699887173360878</v>
+        <v>0.06582442992094428</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.3868606543685758</v>
+        <v>0.3551333145811171</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.676555315494987</v>
+        <v>0.6735715167644685</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.09141898472322652</v>
+        <v>-0.1589063448694574</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1451144390467789</v>
+        <v>0.1332247290824711</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.4585965215886532</v>
+        <v>0.4084034103873293</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3155407799080265</v>
+        <v>0.2586911304918544</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.2373107845578417</v>
+        <v>0.1769782623837273</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.03921543439567898</v>
+        <v>0.07724881547708407</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.6804383131369036</v>
+        <v>0.6610281485397209</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.7879801430432067</v>
+        <v>0.8028405220314099</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001323</t>
+          <t>X &lt; 0.001375</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1934</v>
+        <v>1961</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9092814212724036</v>
+        <v>0.7532553257785679</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.219748838860887</v>
+        <v>1.981674875433114</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.890883788158426</v>
+        <v>1.540402227532383</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.185291851448035</v>
+        <v>1.964776846212722</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.776541486435114</v>
+        <v>1.718516980126985</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.78743293216116</v>
+        <v>1.701216339297964</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.303145513321773</v>
+        <v>1.088138130903289</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.106600141525838</v>
+        <v>0.8341341844396766</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.251233274961955</v>
+        <v>1.012979591068799</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.355058186857384</v>
+        <v>1.082508543914635</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.371252950215805</v>
+        <v>1.100161073793913</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7314927164428937</v>
+        <v>0.5689966345975677</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.7429361163222055</v>
+        <v>0.6251839468820251</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.6765761671577195</v>
+        <v>0.5296993762839506</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.5857356029448724</v>
+        <v>0.509459454684027</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.7675387188022569</v>
+        <v>0.7143479948886196</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.2519070491563085</v>
+        <v>0.2031356076035209</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1263412659111935</v>
+        <v>0.07025150244191991</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5280977274534919</v>
+        <v>0.4374632204227282</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.2291661013269604</v>
+        <v>0.1428846960316079</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.02406523534592964</v>
+        <v>-0.01722782978903581</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.3067364294334141</v>
+        <v>-0.2659162633908423</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.0322617169513606</v>
+        <v>0.05885742144219108</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.4089691115213299</v>
+        <v>0.5898730669924959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002854</t>
+          <t>X &lt; 0.002899</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2238</v>
+        <v>2256</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.401356351694652</v>
+        <v>1.223480950618438</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.846598310440434</v>
+        <v>1.771925394702741</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.767326358884866</v>
+        <v>1.689664166523535</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.96948842899716</v>
+        <v>1.917373669054633</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.437033998020532</v>
+        <v>1.490491182306414</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.382637504443302</v>
+        <v>1.36334065001401</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.215436285484422</v>
+        <v>1.124259343242869</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.8294988185549101</v>
+        <v>0.7308824646285856</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8709860004696139</v>
+        <v>0.8400437368431781</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9002093618662812</v>
+        <v>0.7962046310043718</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.085142444313398</v>
+        <v>0.9799440703874609</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5390133617210324</v>
+        <v>0.4821231778630732</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.3962434517276563</v>
+        <v>0.384930175456546</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2642911349958581</v>
+        <v>0.2694394768552897</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.1231653281549541</v>
+        <v>0.1182585462976817</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2271376268255523</v>
+        <v>0.2633121292991518</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1923741423568686</v>
+        <v>-0.1947072819831845</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.58306435980397</v>
+        <v>-0.5046608869234461</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.6086348581427288</v>
+        <v>-0.5115355345010073</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6634666146903641</v>
+        <v>-0.5625533391100177</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.822347791143919</v>
+        <v>-0.7315914659887568</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.8088282476379263</v>
+        <v>-0.6479168436563185</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.8024500499011822</v>
+        <v>-0.6440638785613828</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6995512932942418</v>
+        <v>-0.5142820716869352</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004384</t>
+          <t>X &lt; 0.004423</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2432</v>
+        <v>2449</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9789402945811219</v>
+        <v>0.7848824145143567</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.525398583105748</v>
+        <v>1.432921129399674</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.419417595652035</v>
+        <v>1.298235748928093</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.712125901447308</v>
+        <v>1.582751591362104</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.9905200001046666</v>
+        <v>0.9236370564116214</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9142550954412485</v>
+        <v>0.8188021744410463</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.9034497215353881</v>
+        <v>0.7389372047869358</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8950008104732206</v>
+        <v>0.823950885050678</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7142650974764564</v>
+        <v>0.6901349731126558</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6796595116778548</v>
+        <v>0.6275798104116603</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.8306674721334701</v>
+        <v>0.7775654362629396</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.428866386979152</v>
+        <v>0.4194838892895945</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2491005465381306</v>
+        <v>0.2825868818632813</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1770644660856533</v>
+        <v>-0.1286463645739033</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.07229070329362486</v>
+        <v>-0.01228415200564825</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.2165168301811775</v>
+        <v>-0.1200014534190927</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.4082118078238679</v>
+        <v>-0.3462309679173501</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.5708778084422335</v>
+        <v>-0.4791150730789511</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.6182824106723643</v>
+        <v>-0.509351051479662</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6949490211651295</v>
+        <v>-0.5802458462249263</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.8433295770429865</v>
+        <v>-0.6990769707704274</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.001412380557355</v>
+        <v>-0.7910951490713174</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8502929312331986</v>
+        <v>-0.6051464063886343</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8438883423512067</v>
+        <v>-0.5800202945539823</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.005915</t>
+          <t>X &lt; 0.005947</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2596</v>
+        <v>2620</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.033482388483741</v>
+        <v>0.8233565672576617</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.677883179057623</v>
+        <v>1.585564423272501</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.334823296855944</v>
+        <v>1.301757136725563</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.564235394121162</v>
+        <v>1.604963065930427</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9819717183407235</v>
+        <v>1.008964086641143</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7303368906842209</v>
+        <v>0.6550266968580374</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5179142275916462</v>
+        <v>0.4521856591669788</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.569155446756433</v>
+        <v>0.5115596664892337</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.6713246950977663</v>
+        <v>0.661333898534636</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5901845763249156</v>
+        <v>0.5507355640159801</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6720843414691657</v>
+        <v>0.6706476540201578</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2780390118105629</v>
+        <v>0.2798235060987579</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.0772443546393049</v>
+        <v>0.1169496673989343</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2591304480178991</v>
+        <v>-0.2074458563342532</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.04870519114015082</v>
+        <v>0.008945440524392723</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.184806542938027</v>
+        <v>-0.1311297508766245</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.2959217989821354</v>
+        <v>-0.3112296747967491</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.3394667381601053</v>
+        <v>-0.2916747555681027</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.4471438760686013</v>
+        <v>-0.2677613089101385</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6226217397418878</v>
+        <v>-0.4120138863816791</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.6032714917295507</v>
+        <v>-0.4075941102176159</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.7176382543713231</v>
+        <v>-0.4602630131197074</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.7128091505179199</v>
+        <v>-0.4611913806545758</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.5575165963451951</v>
+        <v>-0.3337287719197306</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007445</t>
+          <t>X &lt; 0.007472</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2795</v>
+        <v>2817</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7526071732987347</v>
+        <v>0.6946614074826201</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.148931248360569</v>
+        <v>1.209700275818172</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5849330448832077</v>
+        <v>0.6458182706897162</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8890725354140088</v>
+        <v>0.921457445489267</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1817165728473711</v>
+        <v>0.2769308072675898</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.003147567489435232</v>
+        <v>0.100008070432942</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.04202235701286838</v>
+        <v>-0.0383668425538275</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.0567295889592927</v>
+        <v>0.1014953581325173</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2613927648034746</v>
+        <v>0.355825029931502</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.1663222546606704</v>
+        <v>0.2325780672900635</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.369029774096937</v>
+        <v>0.433991552149358</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2664802429793198</v>
+        <v>-0.1966980510471572</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4263886530391403</v>
+        <v>-0.3554995169398509</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6831435908485517</v>
+        <v>-0.6037335783729603</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.2853544126963428</v>
+        <v>-0.2379651409239116</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4550593402789005</v>
+        <v>-0.3997886763921628</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4607569638173032</v>
+        <v>-0.4327973659343343</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4372865361119125</v>
+        <v>-0.3885021656388048</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.4861302630237674</v>
+        <v>-0.4220909661329983</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4927036760923684</v>
+        <v>-0.3994184118059465</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.6207959764105055</v>
+        <v>-0.4851540478127561</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5893458004805439</v>
+        <v>-0.3975280954083971</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.5083112440097608</v>
+        <v>-0.3103650445891191</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.4768089712938632</v>
+        <v>-0.2740989887331295</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.008976</t>
+          <t>X &lt; 0.008996</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2924</v>
+        <v>2947</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5399822543450483</v>
+        <v>0.5396944594737505</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.9376708859060798</v>
+        <v>0.953282163488943</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5047243861260071</v>
+        <v>0.5273327664343981</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5253254423372056</v>
+        <v>0.5278284266035911</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2088174484906062</v>
+        <v>0.2712444278188215</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.09564598580652728</v>
+        <v>-0.05976301639179837</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1332010132660599</v>
+        <v>-0.1260774520923249</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1535200665583787</v>
+        <v>-0.1413721738375173</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.04378581383240032</v>
+        <v>0.07340141943266332</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.05478288489884164</v>
+        <v>0.05542840865174981</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2265930383082093</v>
+        <v>0.2261749252858607</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.427071157232497</v>
+        <v>-0.3887020224195368</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4936551736455357</v>
+        <v>-0.4887091601680069</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6806508871746075</v>
+        <v>-0.6354547236308932</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.2959284194272129</v>
+        <v>-0.2826668389051434</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.3973913762454018</v>
+        <v>-0.3783400238425827</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.613508340724259</v>
+        <v>-0.6176300496501952</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.493437745649203</v>
+        <v>-0.4597938861752624</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5987430130468852</v>
+        <v>-0.5302951842488923</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.6308542316251362</v>
+        <v>-0.5330917584962123</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.7092135654989207</v>
+        <v>-0.5723039456370103</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.6281425582743694</v>
+        <v>-0.4579739076323008</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.60689999376131</v>
+        <v>-0.4317739366409015</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5257408875308442</v>
+        <v>-0.370368439119126</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01051</t>
+          <t>X &lt; 0.01052</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3023</v>
+        <v>3044</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4860848168541239</v>
+        <v>0.441697243150017</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.794112930323486</v>
+        <v>0.8341387654896764</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3612830016748916</v>
+        <v>0.3816089356011432</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4895978847872797</v>
+        <v>0.5265146271496732</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1395223265847605</v>
+        <v>0.2039199090554504</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.01575132881501418</v>
+        <v>0.05209169232330879</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1116203624573728</v>
+        <v>-0.07027881922520152</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1073875917891769</v>
+        <v>-0.0621128280702834</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.04703519595968686</v>
+        <v>0.01892418378349703</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1275670935589872</v>
+        <v>-0.08950452165194633</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1794632047189992</v>
+        <v>0.2154744353230456</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2311688231932294</v>
+        <v>-0.1920832886308972</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3322405504515871</v>
+        <v>-0.29191319259116</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.421436802433945</v>
+        <v>-0.3764275421709655</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.1696247887375861</v>
+        <v>-0.1222853551020791</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.3143027103766087</v>
+        <v>-0.262341191595219</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3956933145952348</v>
+        <v>-0.3469661586365191</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.3159160188151944</v>
+        <v>-0.2310739958719878</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3776360847892661</v>
+        <v>-0.25963689386802</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3694771174559293</v>
+        <v>-0.2226182413557964</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.4959835496314327</v>
+        <v>-0.3113637599584038</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.486093220052787</v>
+        <v>-0.268642335916411</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.3242382110995266</v>
+        <v>-0.104090811736981</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.2481268993789101</v>
+        <v>-0.04970112649536418</v>
       </c>
     </row>
     <row r="28">
@@ -7632,79 +7632,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3111</v>
+        <v>3131</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4658962550563643</v>
+        <v>0.4377094596470954</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7238645792668166</v>
+        <v>0.7482684666423864</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2947036973260211</v>
+        <v>0.304281061682083</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3673249647220942</v>
+        <v>0.3643701354857356</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1776125471972136</v>
+        <v>0.201863757850667</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.126627388864371</v>
+        <v>0.1224927424264024</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.01887171172287339</v>
+        <v>-0.05108410706685618</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.0546012544135337</v>
+        <v>-0.08375462920918153</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.005236129404700307</v>
+        <v>-0.00136769020073757</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.06277727171990222</v>
+        <v>-0.09789613295583877</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.179241357946033</v>
+        <v>0.1607970506392178</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.003385008013978563</v>
+        <v>-0.002068409566788887</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.005111637510275102</v>
+        <v>0.01528793191627642</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.06598545147689805</v>
+        <v>-0.02324956586544857</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.064121236565164</v>
+        <v>0.1095217219923867</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.05962964042477381</v>
+        <v>-0.01102149440220757</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.07827735234474886</v>
+        <v>-0.03236536010198421</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.03569253908079872</v>
+        <v>0.04485006230200383</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.1215749828447272</v>
+        <v>-0.008770517471610617</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.204594024097652</v>
+        <v>-0.06243790504615987</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.3106915332340421</v>
+        <v>-0.1325129166817618</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.2067952613458885</v>
+        <v>0.002746952154843996</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.1059332370104897</v>
+        <v>0.1057249153201312</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1304817545219379</v>
+        <v>0.05834897316086085</v>
       </c>
     </row>
     <row r="29">
@@ -7714,571 +7714,571 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3180</v>
+        <v>3204</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2941934861932722</v>
+        <v>0.2844572508171908</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4761099213953486</v>
+        <v>0.4892097715854078</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.08635703918723436</v>
+        <v>0.08855528003038415</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1409866396257016</v>
+        <v>0.1336009047165021</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.01040804438295595</v>
+        <v>0.03048124763585491</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.05864191752981185</v>
+        <v>0.04959414266318873</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1324763335744805</v>
+        <v>-0.169330201596452</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1424828037995383</v>
+        <v>-0.1772382207164824</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.01083377654708784</v>
+        <v>-0.0006367361229280277</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.08644928815524366</v>
+        <v>-0.1264813664546054</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.08045827399456584</v>
+        <v>0.0392556369819701</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1018854322893716</v>
+        <v>0.06033829695786608</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.07555821344328706</v>
+        <v>0.05200514208146956</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.02979608305658843</v>
+        <v>0.008716203124770061</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.08016195345254573</v>
+        <v>0.06073504525516427</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.05940838751377697</v>
+        <v>-0.07546008225589418</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.1119291364830346</v>
+        <v>-0.1298433769334579</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.009773077915582462</v>
+        <v>0.004869010103192295</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1205069146576321</v>
+        <v>-0.07382789754424124</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1976774185982393</v>
+        <v>-0.121411284993421</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.2189832346318212</v>
+        <v>-0.1092807918367953</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2132360846163621</v>
+        <v>-0.07237950141658445</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1086102015387951</v>
+        <v>0.03377874245405366</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.1342723211661649</v>
+        <v>-0.0162344184874712</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.0151</t>
+          <t>X &lt; 0.01509</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3225</v>
+        <v>3249</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.193461479114994</v>
+        <v>0.1859796288576163</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2757624098448375</v>
+        <v>0.2927871332200738</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.03613910873264814</v>
+        <v>-0.0279371458283677</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.02302114794971999</v>
+        <v>-0.022292452461663</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1564978444154903</v>
+        <v>-0.1278342714434686</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1372349619552509</v>
+        <v>-0.1374806000235438</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3056235760200039</v>
+        <v>-0.3337822161146207</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2576801607809358</v>
+        <v>-0.2845784469061741</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1059528117669473</v>
+        <v>-0.108680885749223</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1508950037386896</v>
+        <v>-0.1825081556976968</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.01748225191898456</v>
+        <v>-0.01531916461141947</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.0656180253866907</v>
+        <v>0.03230459243539485</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.02403815877779891</v>
+        <v>0.008688251356424814</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.05509051677965005</v>
+        <v>-0.06812810318852769</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.01631190304154728</v>
+        <v>0.004420315557275956</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1130622650882458</v>
+        <v>-0.1221551782862562</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1357923244962222</v>
+        <v>-0.1465243652743666</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.09842695534241841</v>
+        <v>-0.07696052605253811</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1427182283329032</v>
+        <v>-0.09016562929630823</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.1852468856299083</v>
+        <v>-0.1033864883928501</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2757730812495964</v>
+        <v>-0.1607710167484058</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2711813324925103</v>
+        <v>-0.1254367401029768</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1022078821256116</v>
+        <v>0.04414715719064333</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.09756031297543899</v>
+        <v>0.0233628992697632</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01663</t>
+          <t>X &lt; 0.01662</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3269</v>
+        <v>3294</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1562367261792161</v>
+        <v>0.150469443128479</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1112797649122257</v>
+        <v>0.1318524434231634</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1248891614206755</v>
+        <v>-0.1111009688734654</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1521366579691019</v>
+        <v>-0.1437771185878987</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2884215160631314</v>
+        <v>-0.2516649137593916</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2364799828599544</v>
+        <v>-0.2288920797749441</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2914356840102386</v>
+        <v>-0.3125499415036259</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3088386251814086</v>
+        <v>-0.3285770959487024</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1890881233001522</v>
+        <v>-0.1835657807770374</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2135740076552111</v>
+        <v>-0.2370106368900338</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.04376682256768305</v>
+        <v>-0.06840871306196306</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.0306115678551464</v>
+        <v>-0.05546201184296251</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1299836688323239</v>
+        <v>-0.1544778011945382</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2110641073256403</v>
+        <v>-0.2336782244025031</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1495018294068942</v>
+        <v>-0.1714619812999274</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2081772870604155</v>
+        <v>-0.2281468949578169</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2324297354900722</v>
+        <v>-0.2536321064323985</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1970044288162356</v>
+        <v>-0.1868613778888815</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2378291595651945</v>
+        <v>-0.1969942989514664</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.277303320794843</v>
+        <v>-0.2071392029184338</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3128114648309079</v>
+        <v>-0.2108556850200145</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.3398847413354815</v>
+        <v>-0.2073850129271761</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2000937520926769</v>
+        <v>-0.06716368674539552</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2577401560395955</v>
+        <v>-0.1506292664575568</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01816</t>
+          <t>X &lt; 0.01814</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3296</v>
+        <v>3320</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.01023548342292457</v>
+        <v>0.002093582987214404</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.05760100641710153</v>
+        <v>-0.01833607727945719</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2131605972312229</v>
+        <v>-0.1794144361340599</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1555475230781909</v>
+        <v>-0.1565879483466119</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3839560802537676</v>
+        <v>-0.3256833625051883</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3007682793789144</v>
+        <v>-0.3018877119768106</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2710343031463225</v>
+        <v>-0.3012093506144993</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3509437141894125</v>
+        <v>-0.3794367103719622</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2318441379282348</v>
+        <v>-0.2345738216342212</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2624479559358832</v>
+        <v>-0.2938251506499157</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.03136366525974665</v>
+        <v>-0.06442585333057593</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.05081694217145127</v>
+        <v>-0.0837491887826971</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1283149985320762</v>
+        <v>-0.1606818414508595</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2105382952088277</v>
+        <v>-0.2412039098942884</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.185112635966739</v>
+        <v>-0.2148426268202996</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.208195759043214</v>
+        <v>-0.2366644600698677</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.2030691475463797</v>
+        <v>-0.2327077697625484</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1687818849959228</v>
+        <v>-0.1674914914113543</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2074982977930517</v>
+        <v>-0.1758623542063091</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2451115589972162</v>
+        <v>-0.1842430743527501</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2544474795971894</v>
+        <v>-0.1622701289408468</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.312223757468395</v>
+        <v>-0.1895026108182449</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2319826252133623</v>
+        <v>-0.108689106214733</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2291080664186467</v>
+        <v>-0.1325423468300571</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01969</t>
+          <t>X &lt; 0.01967</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3311</v>
+        <v>3334</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.01842103293876107</v>
+        <v>0.01709921767433542</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.03022937232783107</v>
+        <v>-0.00426657930909613</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1915541252785644</v>
+        <v>-0.1699042677924822</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1974465749718135</v>
+        <v>-0.1794581292727742</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3062312966466294</v>
+        <v>-0.2893568086696803</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1925134865912668</v>
+        <v>-0.2053283842957114</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1663603352111451</v>
+        <v>-0.1781039429282103</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2170752336415944</v>
+        <v>-0.2572419288837224</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.09828543411963153</v>
+        <v>-0.1124133431992007</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1622730473653533</v>
+        <v>-0.2045777671517115</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.00886684053726583</v>
+        <v>-0.0347276340314977</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.01174479069048573</v>
+        <v>-0.05511848964112431</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1541573226700095</v>
+        <v>-0.1662821742398748</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2069041592506053</v>
+        <v>-0.2176037547151779</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1845658193508015</v>
+        <v>-0.2241158246637056</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.2349877199229411</v>
+        <v>-0.2734198575748223</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2003591337992106</v>
+        <v>-0.2399948867604493</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.16670021296774</v>
+        <v>-0.1756111510697878</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2042642739621314</v>
+        <v>-0.1830501349789913</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.210694995168879</v>
+        <v>-0.1605397968474023</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.2224339746543933</v>
+        <v>-0.1410325814257831</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2802824021628325</v>
+        <v>-0.1684598423839958</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2293451814238878</v>
+        <v>-0.1169415292353833</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2570287515136442</v>
+        <v>-0.1713719303109471</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.02122</t>
+          <t>X &lt; 0.02119</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3327</v>
+        <v>3352</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0009439313441532704</v>
+        <v>-0.001885987369853126</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1087979935972427</v>
+        <v>-0.08373214117072081</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2463789225809947</v>
+        <v>-0.2255579354955515</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2257902876950126</v>
+        <v>-0.2085836011690816</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3057825514280097</v>
+        <v>-0.2600459102795796</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1917142412943491</v>
+        <v>-0.1756193837787237</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1693795199737522</v>
+        <v>-0.1824619673932091</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1912708957975369</v>
+        <v>-0.2034255003376231</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.07284346537907993</v>
+        <v>-0.05867127691608687</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1102873513083864</v>
+        <v>-0.1248749834641032</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.001480890415848535</v>
+        <v>-0.01388885312238131</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.08026808441946542</v>
+        <v>-0.09509736657938817</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1974441022742894</v>
+        <v>-0.2116452589296287</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2510110165946173</v>
+        <v>-0.2640345930462047</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2319495990740066</v>
+        <v>-0.2444258633675886</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2792921720957651</v>
+        <v>-0.2904648263702327</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2454857323493087</v>
+        <v>-0.2577807135060013</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.212505215536126</v>
+        <v>-0.1944596957909468</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2188539457777878</v>
+        <v>-0.170925973934807</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1943396550280667</v>
+        <v>-0.1175844397109103</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2386541779596882</v>
+        <v>-0.1310197505323103</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2965939784767571</v>
+        <v>-0.1587002082308473</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2445869595732759</v>
+        <v>-0.1061476419559355</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2424495560256048</v>
+        <v>-0.1313202747709425</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02275</t>
+          <t>X &lt; 0.02271</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3350</v>
+        <v>3374</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.06835971349126169</v>
+        <v>-0.08369237426897058</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1796571264911506</v>
+        <v>-0.1371790290677026</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3261318365173125</v>
+        <v>-0.2862320839681942</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3105732413831106</v>
+        <v>-0.273225621732891</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3626545943878199</v>
+        <v>-0.2966875625269623</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2481053522161005</v>
+        <v>-0.2118015684268428</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2609131641389766</v>
+        <v>-0.253258557707575</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2548743246417615</v>
+        <v>-0.2465872377376854</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.166709369451965</v>
+        <v>-0.13146220246594</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2092096516584903</v>
+        <v>-0.2024266652938636</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.09636089256590452</v>
+        <v>-0.1199407050814685</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1497424824045268</v>
+        <v>-0.1729165745793182</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1845641871159316</v>
+        <v>-0.2073496640226793</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2392739273927376</v>
+        <v>-0.2610109509779264</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1950752581180808</v>
+        <v>-0.2164054033307465</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2380114425975037</v>
+        <v>-0.2584852988998705</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2947073446845678</v>
+        <v>-0.315411490683239</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2626860381475922</v>
+        <v>-0.2237987994416883</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2675261717471571</v>
+        <v>-0.199030662666118</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2419132069616552</v>
+        <v>-0.1446473038863871</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2598355143811162</v>
+        <v>-0.1320877272504219</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.288071562820889</v>
+        <v>-0.1304570692470506</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2345350663381893</v>
+        <v>-0.07665056360708178</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2627807225554406</v>
+        <v>-0.161984359099641</v>
       </c>
     </row>
   </sheetData>
